--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\売上\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j (1)\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j\dashboard\data\incoming\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61ECDE8F-C2AE-48F5-8384-FE4E57E2D667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B94696-653F-4F9F-A938-795ACF1FE4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -316,127 +316,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1063,1997 +943,3017 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
-        <v>46266</v>
+        <v>45992</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="7">
-        <v>279900</v>
+        <v>239400</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
-        <v>46267</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45993</v>
+      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="7">
-        <v>268650</v>
+        <v>313650</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6">
-        <v>46268</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45994</v>
+      </c>
+      <c r="B4" s="5"/>
       <c r="C4" s="7">
-        <v>295650</v>
+        <v>306000</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="6">
-        <v>46269</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45995</v>
+      </c>
+      <c r="B5" s="5"/>
       <c r="C5" s="7">
-        <v>246150</v>
+        <v>217350</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
-        <v>46270</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45996</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="7">
-        <v>335250</v>
+        <v>354600</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
-        <v>46271</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45997</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="7">
-        <v>216900</v>
+        <v>334350</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
-        <v>46272</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45998</v>
+      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="7">
-        <v>231300</v>
+        <v>214650</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="6">
-        <v>46273</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>45999</v>
+      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="7">
-        <v>156150</v>
+        <v>282600</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="6">
-        <v>46274</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>46000</v>
+      </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="7">
-        <v>218250</v>
+        <v>161550</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="6">
-        <v>46275</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>46001</v>
+      </c>
+      <c r="B11" s="5"/>
       <c r="C11" s="7">
-        <v>230850</v>
+        <v>266400</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="6">
-        <v>46276</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>46002</v>
+      </c>
+      <c r="B12" s="5"/>
       <c r="C12" s="7">
-        <v>214200</v>
+        <v>193050</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="6">
-        <v>46277</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>46003</v>
+      </c>
+      <c r="B13" s="5"/>
       <c r="C13" s="7">
-        <v>224550</v>
+        <v>193050</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="6">
-        <v>46278</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>46004</v>
+      </c>
+      <c r="B14" s="5"/>
       <c r="C14" s="7">
-        <v>247500</v>
+        <v>188100</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6">
+        <v>46005</v>
+      </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="7">
+        <v>229050</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="6"/>
+      <c r="A16" s="6">
+        <v>46006</v>
+      </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
+      <c r="C16" s="7">
+        <v>216900</v>
+      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="6"/>
+      <c r="A17" s="6">
+        <v>46007</v>
+      </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="7">
+        <v>217800</v>
+      </c>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="6"/>
+      <c r="A18" s="6">
+        <v>46008</v>
+      </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
+      <c r="C18" s="7">
+        <v>192600</v>
+      </c>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="6"/>
+      <c r="A19" s="6">
+        <v>46009</v>
+      </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
+      <c r="C19" s="7">
+        <v>177750</v>
+      </c>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="6"/>
+      <c r="A20" s="6">
+        <v>46010</v>
+      </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="7"/>
+      <c r="C20" s="7">
+        <v>269550</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="6"/>
+      <c r="A21" s="6">
+        <v>46011</v>
+      </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="7">
+        <v>225900</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="6"/>
+      <c r="A22" s="6">
+        <v>46012</v>
+      </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
+      <c r="C22" s="7">
+        <v>173300</v>
+      </c>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="6"/>
+      <c r="A23" s="6">
+        <v>46013</v>
+      </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="7">
+        <v>151200</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="6"/>
+      <c r="A24" s="6">
+        <v>46014</v>
+      </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
+      <c r="C24" s="7">
+        <v>170100</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="6"/>
+      <c r="A25" s="6">
+        <v>46015</v>
+      </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7">
+        <v>101700</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="6"/>
+      <c r="A26" s="6">
+        <v>46016</v>
+      </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="7"/>
+      <c r="C26" s="7">
+        <v>127350</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="6"/>
+      <c r="A27" s="6">
+        <v>46017</v>
+      </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="7">
+        <v>123750</v>
+      </c>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="6"/>
+      <c r="A28" s="6">
+        <v>46018</v>
+      </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="7"/>
+      <c r="C28" s="7">
+        <v>146700</v>
+      </c>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="6"/>
+      <c r="A29" s="6">
+        <v>46019</v>
+      </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="7">
+        <v>97650</v>
+      </c>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="6"/>
+      <c r="A30" s="6">
+        <v>46020</v>
+      </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="7"/>
+      <c r="C30" s="7">
+        <v>76500</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
+      <c r="A31" s="6">
+        <v>46021</v>
+      </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="7">
+        <v>69300</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
+      <c r="A32" s="6">
+        <v>46022</v>
+      </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="7"/>
+      <c r="C32" s="7">
+        <v>73350</v>
+      </c>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6">
+        <v>46023</v>
+      </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="C33" s="7">
+        <v>56250</v>
+      </c>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="6"/>
+      <c r="A34" s="6">
+        <v>46024</v>
+      </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="7"/>
+      <c r="C34" s="7">
+        <v>103950</v>
+      </c>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="6"/>
+      <c r="A35" s="6">
+        <v>46025</v>
+      </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
+      <c r="C35" s="7">
+        <v>86850</v>
+      </c>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6"/>
+      <c r="A36" s="6">
+        <v>46026</v>
+      </c>
       <c r="B36" s="5"/>
-      <c r="C36" s="7"/>
+      <c r="C36" s="7">
+        <v>114300</v>
+      </c>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6"/>
+      <c r="A37" s="6">
+        <v>46027</v>
+      </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="7">
+        <v>199350</v>
+      </c>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6"/>
+      <c r="A38" s="6">
+        <v>46028</v>
+      </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="7"/>
+      <c r="C38" s="7">
+        <v>138600</v>
+      </c>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6"/>
+      <c r="A39" s="6">
+        <v>46029</v>
+      </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
+      <c r="C39" s="7">
+        <v>139950</v>
+      </c>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6"/>
+      <c r="A40" s="6">
+        <v>46030</v>
+      </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="7"/>
+      <c r="C40" s="7">
+        <v>167850</v>
+      </c>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6"/>
+      <c r="A41" s="6">
+        <v>46031</v>
+      </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="7"/>
+      <c r="C41" s="7">
+        <v>162900</v>
+      </c>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6"/>
+      <c r="A42" s="6">
+        <v>46032</v>
+      </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="7"/>
+      <c r="C42" s="7">
+        <v>206100</v>
+      </c>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6"/>
+      <c r="A43" s="6">
+        <v>46033</v>
+      </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="7"/>
+      <c r="C43" s="7">
+        <v>243000</v>
+      </c>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6"/>
+      <c r="A44" s="6">
+        <v>46034</v>
+      </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="7"/>
+      <c r="C44" s="7">
+        <v>173700</v>
+      </c>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6"/>
+      <c r="A45" s="6">
+        <v>46035</v>
+      </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="7"/>
+      <c r="C45" s="7">
+        <v>159300</v>
+      </c>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6"/>
+      <c r="A46" s="6">
+        <v>46036</v>
+      </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="7"/>
+      <c r="C46" s="7">
+        <v>146700</v>
+      </c>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
+      <c r="A47" s="6">
+        <v>46037</v>
+      </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="7"/>
+      <c r="C47" s="7">
+        <v>292500</v>
+      </c>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
+      <c r="A48" s="6">
+        <v>46038</v>
+      </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
+      <c r="C48" s="7">
+        <v>264150</v>
+      </c>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6"/>
+      <c r="A49" s="6">
+        <v>46039</v>
+      </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="7"/>
+      <c r="C49" s="7">
+        <v>664650</v>
+      </c>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
+      <c r="A50" s="6">
+        <v>46040</v>
+      </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="7"/>
+      <c r="C50" s="7">
+        <v>408600</v>
+      </c>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6"/>
+      <c r="A51" s="6">
+        <v>46041</v>
+      </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="7"/>
+      <c r="C51" s="7">
+        <v>385650</v>
+      </c>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6"/>
+      <c r="A52" s="6">
+        <v>46042</v>
+      </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="7"/>
+      <c r="C52" s="7">
+        <v>541800</v>
+      </c>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6"/>
+      <c r="A53" s="6">
+        <v>46043</v>
+      </c>
       <c r="B53" s="5"/>
-      <c r="C53" s="7"/>
+      <c r="C53" s="7">
+        <v>351000</v>
+      </c>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6"/>
+      <c r="A54" s="6">
+        <v>46044</v>
+      </c>
       <c r="B54" s="5"/>
-      <c r="C54" s="7"/>
+      <c r="C54" s="7">
+        <v>231300</v>
+      </c>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6"/>
+      <c r="A55" s="6">
+        <v>46045</v>
+      </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="7"/>
+      <c r="C55" s="7">
+        <v>346500</v>
+      </c>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6"/>
+      <c r="A56" s="6">
+        <v>46046</v>
+      </c>
       <c r="B56" s="5"/>
-      <c r="C56" s="7"/>
+      <c r="C56" s="7">
+        <v>285300</v>
+      </c>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6"/>
+      <c r="A57" s="6">
+        <v>46047</v>
+      </c>
       <c r="B57" s="5"/>
-      <c r="C57" s="7"/>
+      <c r="C57" s="7">
+        <v>336600</v>
+      </c>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6"/>
+      <c r="A58" s="6">
+        <v>46048</v>
+      </c>
       <c r="B58" s="5"/>
-      <c r="C58" s="7"/>
+      <c r="C58" s="7">
+        <v>321750</v>
+      </c>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6"/>
+      <c r="A59" s="6">
+        <v>46049</v>
+      </c>
       <c r="B59" s="5"/>
-      <c r="C59" s="7"/>
+      <c r="C59" s="7">
+        <v>362700</v>
+      </c>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6"/>
+      <c r="A60" s="6">
+        <v>46050</v>
+      </c>
       <c r="B60" s="5"/>
-      <c r="C60" s="7"/>
+      <c r="C60" s="7">
+        <v>297900</v>
+      </c>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6"/>
+      <c r="A61" s="6">
+        <v>46051</v>
+      </c>
       <c r="B61" s="5"/>
-      <c r="C61" s="7"/>
+      <c r="C61" s="7">
+        <v>304650</v>
+      </c>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6"/>
+      <c r="A62" s="6">
+        <v>46052</v>
+      </c>
       <c r="B62" s="5"/>
-      <c r="C62" s="7"/>
+      <c r="C62" s="7">
+        <v>201150</v>
+      </c>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6"/>
+      <c r="A63" s="6">
+        <v>46053</v>
+      </c>
       <c r="B63" s="5"/>
-      <c r="C63" s="7"/>
+      <c r="C63" s="7">
+        <v>287100</v>
+      </c>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6"/>
+      <c r="A64" s="6">
+        <v>46054</v>
+      </c>
       <c r="B64" s="5"/>
-      <c r="C64" s="7"/>
+      <c r="C64" s="7">
+        <v>337500</v>
+      </c>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6"/>
+      <c r="A65" s="6">
+        <v>46055</v>
+      </c>
       <c r="B65" s="5"/>
-      <c r="C65" s="7"/>
+      <c r="C65" s="7">
+        <v>202500</v>
+      </c>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6"/>
+      <c r="A66" s="6">
+        <v>46056</v>
+      </c>
       <c r="B66" s="5"/>
-      <c r="C66" s="7"/>
+      <c r="C66" s="7">
+        <v>236250</v>
+      </c>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="6"/>
+      <c r="A67" s="6">
+        <v>46057</v>
+      </c>
       <c r="B67" s="5"/>
-      <c r="C67" s="7"/>
+      <c r="C67" s="7">
+        <v>220950</v>
+      </c>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="6"/>
+      <c r="A68" s="6">
+        <v>46058</v>
+      </c>
       <c r="B68" s="5"/>
-      <c r="C68" s="7"/>
+      <c r="C68" s="7">
+        <v>271800</v>
+      </c>
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="6"/>
+      <c r="A69" s="6">
+        <v>46059</v>
+      </c>
       <c r="B69" s="5"/>
-      <c r="C69" s="7"/>
+      <c r="C69" s="7">
+        <v>303750</v>
+      </c>
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="6"/>
+      <c r="A70" s="6">
+        <v>46060</v>
+      </c>
       <c r="B70" s="5"/>
-      <c r="C70" s="7"/>
+      <c r="C70" s="7">
+        <v>234450</v>
+      </c>
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="6"/>
+      <c r="A71" s="6">
+        <v>46061</v>
+      </c>
       <c r="B71" s="5"/>
-      <c r="C71" s="7"/>
+      <c r="C71" s="7">
+        <v>320400</v>
+      </c>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="6"/>
+      <c r="A72" s="6">
+        <v>46062</v>
+      </c>
       <c r="B72" s="5"/>
-      <c r="C72" s="7"/>
+      <c r="C72" s="7">
+        <v>239400</v>
+      </c>
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A73" s="6"/>
+      <c r="A73" s="6">
+        <v>46063</v>
+      </c>
       <c r="B73" s="5"/>
-      <c r="C73" s="7"/>
+      <c r="C73" s="7">
+        <v>154350</v>
+      </c>
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A74" s="6"/>
+      <c r="A74" s="6">
+        <v>46064</v>
+      </c>
       <c r="B74" s="5"/>
-      <c r="C74" s="7"/>
+      <c r="C74" s="7">
+        <v>343800</v>
+      </c>
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A75" s="6"/>
+      <c r="A75" s="6">
+        <v>46065</v>
+      </c>
       <c r="B75" s="5"/>
-      <c r="C75" s="7"/>
+      <c r="C75" s="7">
+        <v>193950</v>
+      </c>
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A76" s="6"/>
+      <c r="A76" s="6">
+        <v>46066</v>
+      </c>
       <c r="B76" s="5"/>
-      <c r="C76" s="7"/>
+      <c r="C76" s="7">
+        <v>182250</v>
+      </c>
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A77" s="6"/>
+      <c r="A77" s="6">
+        <v>46067</v>
+      </c>
       <c r="B77" s="5"/>
-      <c r="C77" s="7"/>
+      <c r="C77" s="7">
+        <v>171000</v>
+      </c>
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="6"/>
+      <c r="A78" s="6">
+        <v>46068</v>
+      </c>
       <c r="B78" s="5"/>
-      <c r="C78" s="7"/>
+      <c r="C78" s="7">
+        <v>243900</v>
+      </c>
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="6"/>
+      <c r="A79" s="6">
+        <v>46069</v>
+      </c>
       <c r="B79" s="5"/>
-      <c r="C79" s="7"/>
+      <c r="C79" s="7">
+        <v>117900</v>
+      </c>
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="6"/>
+      <c r="A80" s="6">
+        <v>46070</v>
+      </c>
       <c r="B80" s="5"/>
-      <c r="C80" s="7"/>
+      <c r="C80" s="7">
+        <v>212400</v>
+      </c>
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A81" s="6"/>
+      <c r="A81" s="6">
+        <v>46071</v>
+      </c>
       <c r="B81" s="5"/>
-      <c r="C81" s="7"/>
+      <c r="C81" s="7">
+        <v>310050</v>
+      </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A82" s="6"/>
+      <c r="A82" s="6">
+        <v>46072</v>
+      </c>
       <c r="B82" s="5"/>
-      <c r="C82" s="7"/>
+      <c r="C82" s="7">
+        <v>297900</v>
+      </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A83" s="6"/>
+      <c r="A83" s="6">
+        <v>46073</v>
+      </c>
       <c r="B83" s="5"/>
-      <c r="C83" s="7"/>
+      <c r="C83" s="7">
+        <v>325800</v>
+      </c>
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A84" s="6"/>
+      <c r="A84" s="6">
+        <v>46074</v>
+      </c>
       <c r="B84" s="5"/>
-      <c r="C84" s="7"/>
+      <c r="C84" s="7">
+        <v>312300</v>
+      </c>
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A85" s="6"/>
+      <c r="A85" s="6">
+        <v>46075</v>
+      </c>
       <c r="B85" s="5"/>
-      <c r="C85" s="7"/>
+      <c r="C85" s="7">
+        <v>314100</v>
+      </c>
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A86" s="6"/>
+      <c r="A86" s="6">
+        <v>46076</v>
+      </c>
       <c r="B86" s="5"/>
-      <c r="C86" s="7"/>
+      <c r="C86" s="7">
+        <v>397350</v>
+      </c>
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A87" s="6"/>
+      <c r="A87" s="6">
+        <v>46077</v>
+      </c>
       <c r="B87" s="5"/>
-      <c r="C87" s="7"/>
+      <c r="C87" s="7">
+        <v>198450</v>
+      </c>
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A88" s="6"/>
+      <c r="A88" s="6">
+        <v>46078</v>
+      </c>
       <c r="B88" s="5"/>
-      <c r="C88" s="7"/>
+      <c r="C88" s="7">
+        <v>292500</v>
+      </c>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A89" s="6"/>
+      <c r="A89" s="6">
+        <v>46079</v>
+      </c>
       <c r="B89" s="5"/>
-      <c r="C89" s="7"/>
+      <c r="C89" s="7">
+        <v>326250</v>
+      </c>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A90" s="6"/>
+      <c r="A90" s="6">
+        <v>46080</v>
+      </c>
       <c r="B90" s="5"/>
-      <c r="C90" s="7"/>
+      <c r="C90" s="7">
+        <v>241650</v>
+      </c>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A91" s="6"/>
+      <c r="A91" s="6">
+        <v>46081</v>
+      </c>
       <c r="B91" s="5"/>
-      <c r="C91" s="7"/>
+      <c r="C91" s="7">
+        <v>216000</v>
+      </c>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A92" s="6"/>
+      <c r="A92" s="6">
+        <v>46082</v>
+      </c>
       <c r="B92" s="5"/>
-      <c r="C92" s="7"/>
+      <c r="C92" s="7">
+        <v>281700</v>
+      </c>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A93" s="6"/>
+      <c r="A93" s="6">
+        <v>46083</v>
+      </c>
       <c r="B93" s="5"/>
-      <c r="C93" s="7"/>
+      <c r="C93" s="7">
+        <v>272250</v>
+      </c>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A94" s="6"/>
+      <c r="A94" s="6">
+        <v>46084</v>
+      </c>
       <c r="B94" s="5"/>
-      <c r="C94" s="7"/>
+      <c r="C94" s="7">
+        <v>245250</v>
+      </c>
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A95" s="6"/>
+      <c r="A95" s="6">
+        <v>46085</v>
+      </c>
       <c r="B95" s="5"/>
-      <c r="C95" s="7"/>
+      <c r="C95" s="7">
+        <v>261000</v>
+      </c>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A96" s="6"/>
+      <c r="A96" s="6">
+        <v>46086</v>
+      </c>
       <c r="B96" s="5"/>
-      <c r="C96" s="7"/>
+      <c r="C96" s="7">
+        <v>166950</v>
+      </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97" s="6"/>
+      <c r="A97" s="6">
+        <v>46087</v>
+      </c>
       <c r="B97" s="5"/>
-      <c r="C97" s="7"/>
+      <c r="C97" s="7">
+        <v>215550</v>
+      </c>
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A98" s="6"/>
+      <c r="A98" s="6">
+        <v>46088</v>
+      </c>
       <c r="B98" s="5"/>
-      <c r="C98" s="7"/>
+      <c r="C98" s="7">
+        <v>197550</v>
+      </c>
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A99" s="6"/>
+      <c r="A99" s="6">
+        <v>46089</v>
+      </c>
       <c r="B99" s="5"/>
-      <c r="C99" s="7"/>
+      <c r="C99" s="7">
+        <v>194850</v>
+      </c>
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A100" s="6"/>
+      <c r="A100" s="6">
+        <v>46090</v>
+      </c>
       <c r="B100" s="5"/>
-      <c r="C100" s="7"/>
+      <c r="C100" s="7">
+        <v>182700</v>
+      </c>
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A101" s="6"/>
+      <c r="A101" s="6">
+        <v>46091</v>
+      </c>
       <c r="B101" s="5"/>
-      <c r="C101" s="7"/>
+      <c r="C101" s="7">
+        <v>171000</v>
+      </c>
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A102" s="6"/>
+      <c r="A102" s="6">
+        <v>46092</v>
+      </c>
       <c r="B102" s="5"/>
-      <c r="C102" s="7"/>
+      <c r="C102" s="7">
+        <v>189450</v>
+      </c>
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A103" s="6"/>
+      <c r="A103" s="6">
+        <v>46093</v>
+      </c>
       <c r="B103" s="5"/>
-      <c r="C103" s="7"/>
+      <c r="C103" s="7">
+        <v>245700</v>
+      </c>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A104" s="6"/>
+      <c r="A104" s="6">
+        <v>46094</v>
+      </c>
       <c r="B104" s="5"/>
-      <c r="C104" s="7"/>
+      <c r="C104" s="7">
+        <v>135000</v>
+      </c>
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A105" s="6"/>
+      <c r="A105" s="6">
+        <v>46095</v>
+      </c>
       <c r="B105" s="5"/>
-      <c r="C105" s="7"/>
+      <c r="C105" s="7">
+        <v>225900</v>
+      </c>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A106" s="6"/>
+      <c r="A106" s="6">
+        <v>46096</v>
+      </c>
       <c r="B106" s="5"/>
-      <c r="C106" s="7"/>
+      <c r="C106" s="7">
+        <v>297900</v>
+      </c>
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A107" s="6"/>
+      <c r="A107" s="6">
+        <v>46097</v>
+      </c>
       <c r="B107" s="5"/>
-      <c r="C107" s="7"/>
+      <c r="C107" s="7">
+        <v>292950</v>
+      </c>
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A108" s="6"/>
+      <c r="A108" s="6">
+        <v>46098</v>
+      </c>
       <c r="B108" s="5"/>
-      <c r="C108" s="7"/>
+      <c r="C108" s="7">
+        <v>341550</v>
+      </c>
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A109" s="6"/>
+      <c r="A109" s="6">
+        <v>46099</v>
+      </c>
       <c r="B109" s="5"/>
-      <c r="C109" s="7"/>
+      <c r="C109" s="7">
+        <v>280350</v>
+      </c>
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A110" s="6"/>
+      <c r="A110" s="6">
+        <v>46100</v>
+      </c>
       <c r="B110" s="5"/>
-      <c r="C110" s="7"/>
+      <c r="C110" s="7">
+        <v>433800</v>
+      </c>
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A111" s="6"/>
+      <c r="A111" s="6">
+        <v>46101</v>
+      </c>
       <c r="B111" s="5"/>
-      <c r="C111" s="7"/>
+      <c r="C111" s="7">
+        <v>538200</v>
+      </c>
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A112" s="6"/>
+      <c r="A112" s="6">
+        <v>46102</v>
+      </c>
       <c r="B112" s="5"/>
-      <c r="C112" s="7"/>
+      <c r="C112" s="7">
+        <v>274500</v>
+      </c>
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A113" s="6"/>
+      <c r="A113" s="6">
+        <v>46103</v>
+      </c>
       <c r="B113" s="5"/>
-      <c r="C113" s="7"/>
+      <c r="C113" s="7">
+        <v>384300</v>
+      </c>
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A114" s="6"/>
+      <c r="A114" s="6">
+        <v>46104</v>
+      </c>
       <c r="B114" s="5"/>
-      <c r="C114" s="7"/>
+      <c r="C114" s="7">
+        <v>302850</v>
+      </c>
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A115" s="6"/>
+      <c r="A115" s="6">
+        <v>46105</v>
+      </c>
       <c r="B115" s="5"/>
-      <c r="C115" s="7"/>
+      <c r="C115" s="7">
+        <v>194850</v>
+      </c>
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A116" s="6"/>
+      <c r="A116" s="6">
+        <v>46106</v>
+      </c>
       <c r="B116" s="5"/>
-      <c r="C116" s="7"/>
+      <c r="C116" s="7">
+        <v>260100</v>
+      </c>
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A117" s="6"/>
+      <c r="A117" s="6">
+        <v>46107</v>
+      </c>
       <c r="B117" s="5"/>
-      <c r="C117" s="7"/>
+      <c r="C117" s="7">
+        <v>238500</v>
+      </c>
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A118" s="6"/>
+      <c r="A118" s="6">
+        <v>46108</v>
+      </c>
       <c r="B118" s="5"/>
-      <c r="C118" s="7"/>
+      <c r="C118" s="7">
+        <v>175050</v>
+      </c>
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A119" s="6"/>
+      <c r="A119" s="6">
+        <v>46109</v>
+      </c>
       <c r="B119" s="5"/>
-      <c r="C119" s="7"/>
+      <c r="C119" s="7">
+        <v>337050</v>
+      </c>
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A120" s="6"/>
+      <c r="A120" s="6">
+        <v>46110</v>
+      </c>
       <c r="B120" s="5"/>
-      <c r="C120" s="7"/>
+      <c r="C120" s="7">
+        <v>307350</v>
+      </c>
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A121" s="6"/>
+      <c r="A121" s="6">
+        <v>46111</v>
+      </c>
       <c r="B121" s="5"/>
-      <c r="C121" s="7"/>
+      <c r="C121" s="7">
+        <v>276300</v>
+      </c>
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A122" s="6"/>
+      <c r="A122" s="6">
+        <v>46112</v>
+      </c>
       <c r="B122" s="5"/>
-      <c r="C122" s="7"/>
+      <c r="C122" s="7">
+        <v>349650</v>
+      </c>
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A123" s="6"/>
+      <c r="A123" s="6">
+        <v>46113</v>
+      </c>
       <c r="B123" s="5"/>
-      <c r="C123" s="7"/>
+      <c r="C123" s="7">
+        <v>290250</v>
+      </c>
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A124" s="6"/>
+      <c r="A124" s="6">
+        <v>46114</v>
+      </c>
       <c r="B124" s="5"/>
-      <c r="C124" s="7"/>
+      <c r="C124" s="7">
+        <v>317250</v>
+      </c>
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A125" s="6"/>
+      <c r="A125" s="6">
+        <v>46115</v>
+      </c>
       <c r="B125" s="5"/>
-      <c r="C125" s="7"/>
+      <c r="C125" s="7">
+        <v>317250</v>
+      </c>
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A126" s="6"/>
+      <c r="A126" s="6">
+        <v>46116</v>
+      </c>
       <c r="B126" s="5"/>
-      <c r="C126" s="7"/>
+      <c r="C126" s="7">
+        <v>538200</v>
+      </c>
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A127" s="6"/>
+      <c r="A127" s="6">
+        <v>46117</v>
+      </c>
       <c r="B127" s="5"/>
-      <c r="C127" s="7"/>
+      <c r="C127" s="7">
+        <v>454050</v>
+      </c>
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A128" s="6"/>
+      <c r="A128" s="6">
+        <v>46118</v>
+      </c>
       <c r="B128" s="5"/>
-      <c r="C128" s="7"/>
+      <c r="C128" s="7">
+        <v>519300</v>
+      </c>
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A129" s="6"/>
+      <c r="A129" s="6">
+        <v>46119</v>
+      </c>
       <c r="B129" s="5"/>
-      <c r="C129" s="7"/>
+      <c r="C129" s="7">
+        <v>492750</v>
+      </c>
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A130" s="6"/>
+      <c r="A130" s="6">
+        <v>46120</v>
+      </c>
       <c r="B130" s="5"/>
-      <c r="C130" s="7"/>
+      <c r="C130" s="7">
+        <v>431100</v>
+      </c>
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A131" s="6"/>
+      <c r="A131" s="6">
+        <v>46121</v>
+      </c>
       <c r="B131" s="5"/>
-      <c r="C131" s="7"/>
+      <c r="C131" s="7">
+        <v>354600</v>
+      </c>
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A132" s="6"/>
+      <c r="A132" s="6">
+        <v>46122</v>
+      </c>
       <c r="B132" s="5"/>
-      <c r="C132" s="7"/>
+      <c r="C132" s="7">
+        <v>416700</v>
+      </c>
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A133" s="6"/>
+      <c r="A133" s="6">
+        <v>46123</v>
+      </c>
       <c r="B133" s="5"/>
-      <c r="C133" s="7"/>
+      <c r="C133" s="7">
+        <v>444600</v>
+      </c>
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A134" s="6"/>
+      <c r="A134" s="6">
+        <v>46124</v>
+      </c>
       <c r="B134" s="5"/>
-      <c r="C134" s="7"/>
+      <c r="C134" s="7">
+        <v>438750</v>
+      </c>
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A135" s="6"/>
+      <c r="A135" s="6">
+        <v>46125</v>
+      </c>
       <c r="B135" s="5"/>
-      <c r="C135" s="7"/>
+      <c r="C135" s="7">
+        <v>408150</v>
+      </c>
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A136" s="6"/>
+      <c r="A136" s="6">
+        <v>46126</v>
+      </c>
       <c r="B136" s="5"/>
-      <c r="C136" s="7"/>
+      <c r="C136" s="7">
+        <v>315450</v>
+      </c>
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A137" s="6"/>
+      <c r="A137" s="6">
+        <v>46127</v>
+      </c>
       <c r="B137" s="5"/>
-      <c r="C137" s="7"/>
+      <c r="C137" s="7">
+        <v>463050</v>
+      </c>
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A138" s="6"/>
+      <c r="A138" s="6">
+        <v>46128</v>
+      </c>
       <c r="B138" s="5"/>
-      <c r="C138" s="7"/>
+      <c r="C138" s="7">
+        <v>504450</v>
+      </c>
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A139" s="6"/>
+      <c r="A139" s="6">
+        <v>46129</v>
+      </c>
       <c r="B139" s="5"/>
-      <c r="C139" s="7"/>
+      <c r="C139" s="7">
+        <v>405000</v>
+      </c>
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A140" s="6"/>
+      <c r="A140" s="6">
+        <v>46130</v>
+      </c>
       <c r="B140" s="5"/>
-      <c r="C140" s="7"/>
+      <c r="C140" s="7">
+        <v>486450</v>
+      </c>
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A141" s="6"/>
+      <c r="A141" s="6">
+        <v>46131</v>
+      </c>
       <c r="B141" s="5"/>
-      <c r="C141" s="7"/>
+      <c r="C141" s="7">
+        <v>718200</v>
+      </c>
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A142" s="6"/>
+      <c r="A142" s="6">
+        <v>46132</v>
+      </c>
       <c r="B142" s="5"/>
-      <c r="C142" s="7"/>
+      <c r="C142" s="7">
+        <v>769500</v>
+      </c>
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A143" s="6"/>
+      <c r="A143" s="6">
+        <v>46133</v>
+      </c>
       <c r="B143" s="5"/>
-      <c r="C143" s="7"/>
+      <c r="C143" s="7">
+        <v>737550</v>
+      </c>
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A144" s="6"/>
+      <c r="A144" s="6">
+        <v>46134</v>
+      </c>
       <c r="B144" s="5"/>
-      <c r="C144" s="7"/>
+      <c r="C144" s="7">
+        <v>525150</v>
+      </c>
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A145" s="6"/>
+      <c r="A145" s="6">
+        <v>46135</v>
+      </c>
       <c r="B145" s="5"/>
-      <c r="C145" s="7"/>
+      <c r="C145" s="7">
+        <v>768150</v>
+      </c>
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A146" s="6"/>
+      <c r="A146" s="6">
+        <v>46136</v>
+      </c>
       <c r="B146" s="5"/>
-      <c r="C146" s="7"/>
+      <c r="C146" s="7">
+        <v>479700</v>
+      </c>
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A147" s="6"/>
+      <c r="A147" s="6">
+        <v>46137</v>
+      </c>
       <c r="B147" s="5"/>
-      <c r="C147" s="7"/>
+      <c r="C147" s="7">
+        <v>507600</v>
+      </c>
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A148" s="6"/>
+      <c r="A148" s="6">
+        <v>46138</v>
+      </c>
       <c r="B148" s="5"/>
-      <c r="C148" s="7"/>
+      <c r="C148" s="7">
+        <v>662400</v>
+      </c>
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A149" s="6"/>
+      <c r="A149" s="6">
+        <v>46139</v>
+      </c>
       <c r="B149" s="5"/>
-      <c r="C149" s="7"/>
+      <c r="C149" s="7">
+        <v>509400</v>
+      </c>
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A150" s="6"/>
+      <c r="A150" s="6">
+        <v>46140</v>
+      </c>
       <c r="B150" s="5"/>
-      <c r="C150" s="7"/>
+      <c r="C150" s="7">
+        <v>302850</v>
+      </c>
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A151" s="6"/>
+      <c r="A151" s="6">
+        <v>46141</v>
+      </c>
       <c r="B151" s="5"/>
-      <c r="C151" s="7"/>
+      <c r="C151" s="7">
+        <v>413100</v>
+      </c>
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A152" s="6"/>
+      <c r="A152" s="6">
+        <v>46142</v>
+      </c>
       <c r="B152" s="5"/>
-      <c r="C152" s="7"/>
+      <c r="C152" s="7">
+        <v>544500</v>
+      </c>
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A153" s="6"/>
+      <c r="A153" s="6">
+        <v>46143</v>
+      </c>
       <c r="B153" s="5"/>
-      <c r="C153" s="7"/>
+      <c r="C153" s="7">
+        <v>173250</v>
+      </c>
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A154" s="6"/>
+      <c r="A154" s="6">
+        <v>46144</v>
+      </c>
       <c r="B154" s="5"/>
-      <c r="C154" s="7"/>
+      <c r="C154" s="7">
+        <v>162450</v>
+      </c>
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A155" s="6"/>
+      <c r="A155" s="6">
+        <v>46145</v>
+      </c>
       <c r="B155" s="5"/>
-      <c r="C155" s="7"/>
+      <c r="C155" s="7">
+        <v>122400</v>
+      </c>
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A156" s="6"/>
+      <c r="A156" s="6">
+        <v>46146</v>
+      </c>
       <c r="B156" s="5"/>
-      <c r="C156" s="7"/>
+      <c r="C156" s="7">
+        <v>99000</v>
+      </c>
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A157" s="6"/>
+      <c r="A157" s="6">
+        <v>46147</v>
+      </c>
       <c r="B157" s="5"/>
-      <c r="C157" s="7"/>
+      <c r="C157" s="7">
+        <v>126000</v>
+      </c>
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A158" s="6"/>
+      <c r="A158" s="6">
+        <v>46148</v>
+      </c>
       <c r="B158" s="5"/>
-      <c r="C158" s="7"/>
+      <c r="C158" s="7">
+        <v>126900</v>
+      </c>
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A159" s="6"/>
+      <c r="A159" s="6">
+        <v>46149</v>
+      </c>
       <c r="B159" s="5"/>
-      <c r="C159" s="7"/>
+      <c r="C159" s="7">
+        <v>152100</v>
+      </c>
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A160" s="6"/>
+      <c r="A160" s="6">
+        <v>46150</v>
+      </c>
       <c r="B160" s="5"/>
-      <c r="C160" s="7"/>
+      <c r="C160" s="7">
+        <v>148050</v>
+      </c>
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A161" s="6"/>
+      <c r="A161" s="6">
+        <v>46151</v>
+      </c>
       <c r="B161" s="5"/>
-      <c r="C161" s="7"/>
+      <c r="C161" s="7">
+        <v>174150</v>
+      </c>
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A162" s="6"/>
+      <c r="A162" s="6">
+        <v>46152</v>
+      </c>
       <c r="B162" s="5"/>
-      <c r="C162" s="7"/>
+      <c r="C162" s="7">
+        <v>194850</v>
+      </c>
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A163" s="6"/>
+      <c r="A163" s="6">
+        <v>46153</v>
+      </c>
       <c r="B163" s="5"/>
-      <c r="C163" s="7"/>
+      <c r="C163" s="7">
+        <v>150300</v>
+      </c>
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A164" s="6"/>
+      <c r="A164" s="6">
+        <v>46154</v>
+      </c>
       <c r="B164" s="5"/>
-      <c r="C164" s="7"/>
+      <c r="C164" s="7">
+        <v>154350</v>
+      </c>
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A165" s="6"/>
+      <c r="A165" s="6">
+        <v>46155</v>
+      </c>
       <c r="B165" s="5"/>
-      <c r="C165" s="7"/>
+      <c r="C165" s="7">
+        <v>89100</v>
+      </c>
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A166" s="6"/>
+      <c r="A166" s="6">
+        <v>46156</v>
+      </c>
       <c r="B166" s="5"/>
-      <c r="C166" s="7"/>
+      <c r="C166" s="7">
+        <v>93150</v>
+      </c>
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A167" s="6"/>
+      <c r="A167" s="6">
+        <v>46157</v>
+      </c>
       <c r="B167" s="5"/>
-      <c r="C167" s="7"/>
+      <c r="C167" s="7">
+        <v>108900</v>
+      </c>
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A168" s="6"/>
+      <c r="A168" s="6">
+        <v>46158</v>
+      </c>
       <c r="B168" s="5"/>
-      <c r="C168" s="7"/>
+      <c r="C168" s="7">
+        <v>117900</v>
+      </c>
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A169" s="6"/>
+      <c r="A169" s="6">
+        <v>46159</v>
+      </c>
       <c r="B169" s="5"/>
-      <c r="C169" s="7"/>
+      <c r="C169" s="7">
+        <v>216000</v>
+      </c>
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A170" s="6"/>
+      <c r="A170" s="6">
+        <v>46160</v>
+      </c>
       <c r="B170" s="5"/>
-      <c r="C170" s="7"/>
+      <c r="C170" s="7">
+        <v>170550</v>
+      </c>
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A171" s="6"/>
+      <c r="A171" s="6">
+        <v>46161</v>
+      </c>
       <c r="B171" s="5"/>
-      <c r="C171" s="7"/>
+      <c r="C171" s="7">
+        <v>197550</v>
+      </c>
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A172" s="6"/>
+      <c r="A172" s="6">
+        <v>46162</v>
+      </c>
       <c r="B172" s="5"/>
-      <c r="C172" s="7"/>
+      <c r="C172" s="7">
+        <v>215550</v>
+      </c>
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A173" s="6"/>
+      <c r="A173" s="6">
+        <v>46163</v>
+      </c>
       <c r="B173" s="5"/>
-      <c r="C173" s="7"/>
+      <c r="C173" s="7">
+        <v>191700</v>
+      </c>
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A174" s="6"/>
+      <c r="A174" s="6">
+        <v>46164</v>
+      </c>
       <c r="B174" s="5"/>
-      <c r="C174" s="7"/>
+      <c r="C174" s="7">
+        <v>252000</v>
+      </c>
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A175" s="6"/>
+      <c r="A175" s="6">
+        <v>46165</v>
+      </c>
       <c r="B175" s="5"/>
-      <c r="C175" s="7"/>
+      <c r="C175" s="7">
+        <v>176850</v>
+      </c>
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A176" s="6"/>
+      <c r="A176" s="6">
+        <v>46166</v>
+      </c>
       <c r="B176" s="5"/>
-      <c r="C176" s="7"/>
+      <c r="C176" s="7">
+        <v>115650</v>
+      </c>
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A177" s="6"/>
+      <c r="A177" s="6">
+        <v>46167</v>
+      </c>
       <c r="B177" s="5"/>
-      <c r="C177" s="7"/>
+      <c r="C177" s="7">
+        <v>211950</v>
+      </c>
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A178" s="6"/>
+      <c r="A178" s="6">
+        <v>46168</v>
+      </c>
       <c r="B178" s="5"/>
-      <c r="C178" s="7"/>
+      <c r="C178" s="7">
+        <v>263700</v>
+      </c>
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A179" s="6"/>
+      <c r="A179" s="6">
+        <v>46169</v>
+      </c>
       <c r="B179" s="5"/>
-      <c r="C179" s="7"/>
+      <c r="C179" s="7">
+        <v>184050</v>
+      </c>
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A180" s="6"/>
+      <c r="A180" s="6">
+        <v>46170</v>
+      </c>
       <c r="B180" s="5"/>
-      <c r="C180" s="7"/>
+      <c r="C180" s="7">
+        <v>141750</v>
+      </c>
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A181" s="6"/>
+      <c r="A181" s="6">
+        <v>46171</v>
+      </c>
       <c r="B181" s="5"/>
-      <c r="C181" s="7"/>
+      <c r="C181" s="7">
+        <v>186750</v>
+      </c>
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A182" s="6"/>
+      <c r="A182" s="6">
+        <v>46172</v>
+      </c>
       <c r="B182" s="5"/>
-      <c r="C182" s="7"/>
+      <c r="C182" s="7">
+        <v>207450</v>
+      </c>
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A183" s="6"/>
+      <c r="A183" s="6">
+        <v>46173</v>
+      </c>
       <c r="B183" s="5"/>
-      <c r="C183" s="7"/>
+      <c r="C183" s="7">
+        <v>338400</v>
+      </c>
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A184" s="6"/>
+      <c r="A184" s="6">
+        <v>46174</v>
+      </c>
       <c r="B184" s="5"/>
-      <c r="C184" s="7"/>
+      <c r="C184" s="7">
+        <v>270000</v>
+      </c>
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A185" s="6"/>
+      <c r="A185" s="6">
+        <v>46175</v>
+      </c>
       <c r="B185" s="5"/>
-      <c r="C185" s="7"/>
+      <c r="C185" s="7">
+        <v>347400</v>
+      </c>
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A186" s="6"/>
+      <c r="A186" s="6">
+        <v>46176</v>
+      </c>
       <c r="B186" s="5"/>
-      <c r="C186" s="7"/>
+      <c r="C186" s="7">
+        <v>344700</v>
+      </c>
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A187" s="6"/>
+      <c r="A187" s="6">
+        <v>46177</v>
+      </c>
       <c r="B187" s="5"/>
-      <c r="C187" s="7"/>
+      <c r="C187" s="7">
+        <v>249750</v>
+      </c>
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A188" s="6"/>
+      <c r="A188" s="6">
+        <v>46178</v>
+      </c>
       <c r="B188" s="5"/>
-      <c r="C188" s="7"/>
+      <c r="C188" s="7">
+        <v>289350</v>
+      </c>
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A189" s="6"/>
+      <c r="A189" s="6">
+        <v>46179</v>
+      </c>
       <c r="B189" s="5"/>
-      <c r="C189" s="7"/>
+      <c r="C189" s="7">
+        <v>342000</v>
+      </c>
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A190" s="6"/>
+      <c r="A190" s="6">
+        <v>46180</v>
+      </c>
       <c r="B190" s="5"/>
-      <c r="C190" s="7"/>
+      <c r="C190" s="7">
+        <v>396450</v>
+      </c>
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A191" s="6"/>
+      <c r="A191" s="6">
+        <v>46181</v>
+      </c>
       <c r="B191" s="5"/>
-      <c r="C191" s="7"/>
+      <c r="C191" s="7">
+        <v>315000</v>
+      </c>
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A192" s="6"/>
+      <c r="A192" s="6">
+        <v>46182</v>
+      </c>
       <c r="B192" s="5"/>
-      <c r="C192" s="7"/>
+      <c r="C192" s="7">
+        <v>187650</v>
+      </c>
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A193" s="6"/>
+      <c r="A193" s="6">
+        <v>46183</v>
+      </c>
       <c r="B193" s="5"/>
-      <c r="C193" s="7"/>
+      <c r="C193" s="7">
+        <v>256500</v>
+      </c>
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A194" s="6"/>
+      <c r="A194" s="6">
+        <v>46184</v>
+      </c>
       <c r="B194" s="5"/>
-      <c r="C194" s="7"/>
+      <c r="C194" s="7">
+        <v>279450</v>
+      </c>
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A195" s="6"/>
+      <c r="A195" s="6">
+        <v>46185</v>
+      </c>
       <c r="B195" s="5"/>
-      <c r="C195" s="7"/>
+      <c r="C195" s="7">
+        <v>314100</v>
+      </c>
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A196" s="6"/>
+      <c r="A196" s="6">
+        <v>46186</v>
+      </c>
       <c r="B196" s="5"/>
-      <c r="C196" s="7"/>
+      <c r="C196" s="7">
+        <v>358650</v>
+      </c>
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A197" s="6"/>
+      <c r="A197" s="6">
+        <v>46187</v>
+      </c>
       <c r="B197" s="5"/>
-      <c r="C197" s="7"/>
+      <c r="C197" s="7">
+        <v>422100</v>
+      </c>
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A198" s="6"/>
+      <c r="A198" s="6">
+        <v>46188</v>
+      </c>
       <c r="B198" s="5"/>
-      <c r="C198" s="7"/>
+      <c r="C198" s="7">
+        <v>362250</v>
+      </c>
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A199" s="6"/>
+      <c r="A199" s="6">
+        <v>46189</v>
+      </c>
       <c r="B199" s="5"/>
-      <c r="C199" s="7"/>
+      <c r="C199" s="7">
+        <v>448650</v>
+      </c>
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A200" s="6"/>
+      <c r="A200" s="6">
+        <v>46190</v>
+      </c>
       <c r="B200" s="5"/>
-      <c r="C200" s="7"/>
+      <c r="C200" s="7">
+        <v>362700</v>
+      </c>
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A201" s="6"/>
+      <c r="A201" s="6">
+        <v>46191</v>
+      </c>
       <c r="B201" s="5"/>
-      <c r="C201" s="7"/>
+      <c r="C201" s="7">
+        <v>344700</v>
+      </c>
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A202" s="6"/>
+      <c r="A202" s="6">
+        <v>46192</v>
+      </c>
       <c r="B202" s="5"/>
-      <c r="C202" s="7"/>
+      <c r="C202" s="7">
+        <v>388350</v>
+      </c>
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A203" s="6"/>
+      <c r="A203" s="6">
+        <v>46193</v>
+      </c>
       <c r="B203" s="5"/>
-      <c r="C203" s="7"/>
+      <c r="C203" s="7">
+        <v>648000</v>
+      </c>
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A204" s="6"/>
+      <c r="A204" s="6">
+        <v>46194</v>
+      </c>
       <c r="B204" s="5"/>
-      <c r="C204" s="7"/>
+      <c r="C204" s="7">
+        <v>595800</v>
+      </c>
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A205" s="6"/>
+      <c r="A205" s="6">
+        <v>46195</v>
+      </c>
       <c r="B205" s="5"/>
-      <c r="C205" s="7"/>
+      <c r="C205" s="7">
+        <v>387450</v>
+      </c>
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A206" s="6"/>
+      <c r="A206" s="6">
+        <v>46196</v>
+      </c>
       <c r="B206" s="5"/>
-      <c r="C206" s="7"/>
+      <c r="C206" s="7">
+        <v>364050</v>
+      </c>
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A207" s="6"/>
+      <c r="A207" s="6">
+        <v>46197</v>
+      </c>
       <c r="B207" s="5"/>
-      <c r="C207" s="7"/>
+      <c r="C207" s="7">
+        <v>378900</v>
+      </c>
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A208" s="6"/>
+      <c r="A208" s="6">
+        <v>46198</v>
+      </c>
       <c r="B208" s="5"/>
-      <c r="C208" s="7"/>
+      <c r="C208" s="7">
+        <v>386550</v>
+      </c>
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A209" s="6"/>
+      <c r="A209" s="6">
+        <v>46199</v>
+      </c>
       <c r="B209" s="5"/>
-      <c r="C209" s="7"/>
+      <c r="C209" s="7">
+        <v>351900</v>
+      </c>
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A210" s="6"/>
+      <c r="A210" s="6">
+        <v>46200</v>
+      </c>
       <c r="B210" s="5"/>
-      <c r="C210" s="7"/>
+      <c r="C210" s="7">
+        <v>368100</v>
+      </c>
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A211" s="6"/>
+      <c r="A211" s="6">
+        <v>46201</v>
+      </c>
       <c r="B211" s="5"/>
-      <c r="C211" s="7"/>
+      <c r="C211" s="7">
+        <v>544500</v>
+      </c>
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A212" s="6"/>
+      <c r="A212" s="6">
+        <v>46202</v>
+      </c>
       <c r="B212" s="5"/>
-      <c r="C212" s="7"/>
+      <c r="C212" s="7">
+        <v>441900</v>
+      </c>
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A213" s="6"/>
+      <c r="A213" s="6">
+        <v>46203</v>
+      </c>
       <c r="B213" s="5"/>
-      <c r="C213" s="7"/>
+      <c r="C213" s="7">
+        <v>420300</v>
+      </c>
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A214" s="6"/>
+      <c r="A214" s="6">
+        <v>46204</v>
+      </c>
       <c r="B214" s="5"/>
-      <c r="C214" s="7"/>
+      <c r="C214" s="7">
+        <v>342000</v>
+      </c>
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A215" s="6"/>
+      <c r="A215" s="6">
+        <v>46205</v>
+      </c>
       <c r="B215" s="5"/>
-      <c r="C215" s="7"/>
+      <c r="C215" s="7">
+        <v>251550</v>
+      </c>
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A216" s="6"/>
+      <c r="A216" s="6">
+        <v>46206</v>
+      </c>
       <c r="B216" s="5"/>
-      <c r="C216" s="7"/>
+      <c r="C216" s="7">
+        <v>109800</v>
+      </c>
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A217" s="6"/>
+      <c r="A217" s="6">
+        <v>46207</v>
+      </c>
       <c r="B217" s="5"/>
-      <c r="C217" s="7"/>
+      <c r="C217" s="7">
+        <v>169650</v>
+      </c>
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A218" s="6"/>
+      <c r="A218" s="6">
+        <v>46208</v>
+      </c>
       <c r="B218" s="5"/>
-      <c r="C218" s="7"/>
+      <c r="C218" s="7">
+        <v>216000</v>
+      </c>
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A219" s="6"/>
+      <c r="A219" s="6">
+        <v>46209</v>
+      </c>
       <c r="B219" s="5"/>
-      <c r="C219" s="7"/>
+      <c r="C219" s="7">
+        <v>255600</v>
+      </c>
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A220" s="6"/>
+      <c r="A220" s="6">
+        <v>46210</v>
+      </c>
       <c r="B220" s="5"/>
-      <c r="C220" s="7"/>
+      <c r="C220" s="7">
+        <v>154800</v>
+      </c>
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A221" s="6"/>
+      <c r="A221" s="6">
+        <v>46211</v>
+      </c>
       <c r="B221" s="5"/>
-      <c r="C221" s="7"/>
+      <c r="C221" s="7">
+        <v>121050</v>
+      </c>
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A222" s="6"/>
+      <c r="A222" s="6">
+        <v>46212</v>
+      </c>
       <c r="B222" s="5"/>
-      <c r="C222" s="7"/>
+      <c r="C222" s="7">
+        <v>215100</v>
+      </c>
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A223" s="6"/>
+      <c r="A223" s="6">
+        <v>46213</v>
+      </c>
       <c r="B223" s="5"/>
-      <c r="C223" s="7"/>
+      <c r="C223" s="7">
+        <v>220050</v>
+      </c>
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A224" s="6"/>
+      <c r="A224" s="6">
+        <v>46214</v>
+      </c>
       <c r="B224" s="5"/>
-      <c r="C224" s="7"/>
+      <c r="C224" s="7">
+        <v>215100</v>
+      </c>
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A225" s="6"/>
+      <c r="A225" s="6">
+        <v>46215</v>
+      </c>
       <c r="B225" s="5"/>
-      <c r="C225" s="7"/>
+      <c r="C225" s="7">
+        <v>169650</v>
+      </c>
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A226" s="6"/>
+      <c r="A226" s="6">
+        <v>46216</v>
+      </c>
       <c r="B226" s="5"/>
-      <c r="C226" s="7"/>
+      <c r="C226" s="7">
+        <v>193050</v>
+      </c>
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A227" s="6"/>
+      <c r="A227" s="6">
+        <v>46217</v>
+      </c>
       <c r="B227" s="5"/>
-      <c r="C227" s="7"/>
+      <c r="C227" s="7">
+        <v>468000</v>
+      </c>
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A228" s="6"/>
+      <c r="A228" s="6">
+        <v>46218</v>
+      </c>
       <c r="B228" s="5"/>
-      <c r="C228" s="7"/>
+      <c r="C228" s="7">
+        <v>306000</v>
+      </c>
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A229" s="6"/>
+      <c r="A229" s="6">
+        <v>46219</v>
+      </c>
       <c r="B229" s="5"/>
-      <c r="C229" s="7"/>
+      <c r="C229" s="7">
+        <v>263250</v>
+      </c>
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A230" s="6"/>
+      <c r="A230" s="6">
+        <v>46220</v>
+      </c>
       <c r="B230" s="5"/>
-      <c r="C230" s="7"/>
+      <c r="C230" s="7">
+        <v>296550</v>
+      </c>
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A231" s="6"/>
+      <c r="A231" s="6">
+        <v>46221</v>
+      </c>
       <c r="B231" s="5"/>
-      <c r="C231" s="7"/>
+      <c r="C231" s="7">
+        <v>370800</v>
+      </c>
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A232" s="6"/>
+      <c r="A232" s="6">
+        <v>46222</v>
+      </c>
       <c r="B232" s="5"/>
-      <c r="C232" s="7"/>
+      <c r="C232" s="7">
+        <v>379800</v>
+      </c>
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A233" s="6"/>
+      <c r="A233" s="6">
+        <v>46223</v>
+      </c>
       <c r="B233" s="5"/>
-      <c r="C233" s="7"/>
+      <c r="C233" s="7">
+        <v>497250</v>
+      </c>
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A234" s="6"/>
+      <c r="A234" s="6">
+        <v>46224</v>
+      </c>
       <c r="B234" s="5"/>
-      <c r="C234" s="7"/>
+      <c r="C234" s="7">
+        <v>344250</v>
+      </c>
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A235" s="6"/>
+      <c r="A235" s="6">
+        <v>46225</v>
+      </c>
       <c r="B235" s="5"/>
-      <c r="C235" s="7"/>
+      <c r="C235" s="7">
+        <v>327150</v>
+      </c>
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A236" s="6"/>
+      <c r="A236" s="6">
+        <v>46226</v>
+      </c>
       <c r="B236" s="5"/>
-      <c r="C236" s="7"/>
+      <c r="C236" s="7">
+        <v>421650</v>
+      </c>
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A237" s="6"/>
+      <c r="A237" s="6">
+        <v>46227</v>
+      </c>
       <c r="B237" s="5"/>
-      <c r="C237" s="7"/>
+      <c r="C237" s="7">
+        <v>373500</v>
+      </c>
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A238" s="6"/>
+      <c r="A238" s="6">
+        <v>46228</v>
+      </c>
       <c r="B238" s="5"/>
-      <c r="C238" s="7"/>
+      <c r="C238" s="7">
+        <v>490950</v>
+      </c>
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A239" s="6"/>
+      <c r="A239" s="6">
+        <v>46229</v>
+      </c>
       <c r="B239" s="5"/>
-      <c r="C239" s="7"/>
+      <c r="C239" s="7">
+        <v>536400</v>
+      </c>
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A240" s="6"/>
+      <c r="A240" s="6">
+        <v>46230</v>
+      </c>
       <c r="B240" s="5"/>
-      <c r="C240" s="7"/>
+      <c r="C240" s="7">
+        <v>297000</v>
+      </c>
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A241" s="6"/>
+      <c r="A241" s="6">
+        <v>46231</v>
+      </c>
       <c r="B241" s="5"/>
-      <c r="C241" s="7"/>
+      <c r="C241" s="7">
+        <v>265050</v>
+      </c>
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A242" s="6"/>
+      <c r="A242" s="6">
+        <v>46232</v>
+      </c>
       <c r="B242" s="5"/>
-      <c r="C242" s="7"/>
+      <c r="C242" s="7">
+        <v>365850</v>
+      </c>
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A243" s="6"/>
+      <c r="A243" s="6">
+        <v>46233</v>
+      </c>
       <c r="B243" s="5"/>
-      <c r="C243" s="7"/>
+      <c r="C243" s="7">
+        <v>323100</v>
+      </c>
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A244" s="6"/>
+      <c r="A244" s="6">
+        <v>46234</v>
+      </c>
       <c r="B244" s="5"/>
-      <c r="C244" s="7"/>
+      <c r="C244" s="7">
+        <v>428850</v>
+      </c>
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A245" s="6"/>
+      <c r="A245" s="6">
+        <v>46235</v>
+      </c>
       <c r="B245" s="5"/>
-      <c r="C245" s="7"/>
+      <c r="C245" s="7">
+        <v>397350</v>
+      </c>
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A246" s="6"/>
+      <c r="A246" s="6">
+        <v>46236</v>
+      </c>
       <c r="B246" s="5"/>
-      <c r="C246" s="7"/>
+      <c r="C246" s="7">
+        <v>560700</v>
+      </c>
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A247" s="6"/>
+      <c r="A247" s="6">
+        <v>46237</v>
+      </c>
       <c r="B247" s="5"/>
-      <c r="C247" s="7"/>
+      <c r="C247" s="7">
+        <v>454950</v>
+      </c>
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A248" s="6"/>
+      <c r="A248" s="6">
+        <v>46238</v>
+      </c>
       <c r="B248" s="5"/>
-      <c r="C248" s="7"/>
+      <c r="C248" s="7">
+        <v>575100</v>
+      </c>
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A249" s="6"/>
+      <c r="A249" s="6">
+        <v>46239</v>
+      </c>
       <c r="B249" s="5"/>
-      <c r="C249" s="7"/>
+      <c r="C249" s="7">
+        <v>382500</v>
+      </c>
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A250" s="6"/>
+      <c r="A250" s="6">
+        <v>46240</v>
+      </c>
       <c r="B250" s="5"/>
-      <c r="C250" s="7"/>
+      <c r="C250" s="7">
+        <v>333450</v>
+      </c>
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A251" s="6"/>
+      <c r="A251" s="6">
+        <v>46241</v>
+      </c>
       <c r="B251" s="5"/>
-      <c r="C251" s="7"/>
+      <c r="C251" s="7">
+        <v>360450</v>
+      </c>
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A252" s="6"/>
+      <c r="A252" s="6">
+        <v>46242</v>
+      </c>
       <c r="B252" s="5"/>
-      <c r="C252" s="7"/>
+      <c r="C252" s="7">
+        <v>312750</v>
+      </c>
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A253" s="6"/>
+      <c r="A253" s="6">
+        <v>46243</v>
+      </c>
       <c r="B253" s="5"/>
-      <c r="C253" s="7"/>
+      <c r="C253" s="7">
+        <v>292050</v>
+      </c>
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A254" s="6"/>
+      <c r="A254" s="6">
+        <v>46244</v>
+      </c>
       <c r="B254" s="5"/>
-      <c r="C254" s="7"/>
+      <c r="C254" s="7">
+        <v>250200</v>
+      </c>
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A255" s="6"/>
+      <c r="A255" s="6">
+        <v>46245</v>
+      </c>
       <c r="B255" s="5"/>
-      <c r="C255" s="7"/>
+      <c r="C255" s="7">
+        <v>324900</v>
+      </c>
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A256" s="6"/>
+      <c r="A256" s="6">
+        <v>46246</v>
+      </c>
       <c r="B256" s="5"/>
-      <c r="C256" s="7"/>
+      <c r="C256" s="7">
+        <v>251100</v>
+      </c>
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A257" s="6"/>
+      <c r="A257" s="6">
+        <v>46247</v>
+      </c>
       <c r="B257" s="5"/>
-      <c r="C257" s="7"/>
+      <c r="C257" s="7">
+        <v>251100</v>
+      </c>
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A258" s="6"/>
+      <c r="A258" s="6">
+        <v>46248</v>
+      </c>
       <c r="B258" s="5"/>
-      <c r="C258" s="7"/>
+      <c r="C258" s="7">
+        <v>185850</v>
+      </c>
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A259" s="6"/>
+      <c r="A259" s="6">
+        <v>46249</v>
+      </c>
       <c r="B259" s="5"/>
-      <c r="C259" s="7"/>
+      <c r="C259" s="7">
+        <v>242100</v>
+      </c>
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A260" s="6"/>
+      <c r="A260" s="6">
+        <v>46250</v>
+      </c>
       <c r="B260" s="5"/>
-      <c r="C260" s="7"/>
+      <c r="C260" s="7">
+        <v>177750</v>
+      </c>
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A261" s="6"/>
+      <c r="A261" s="6">
+        <v>46251</v>
+      </c>
       <c r="B261" s="5"/>
-      <c r="C261" s="7"/>
+      <c r="C261" s="7">
+        <v>192150</v>
+      </c>
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A262" s="6"/>
+      <c r="A262" s="6">
+        <v>46252</v>
+      </c>
       <c r="B262" s="5"/>
-      <c r="C262" s="7"/>
+      <c r="C262" s="7">
+        <v>265050</v>
+      </c>
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A263" s="6"/>
+      <c r="A263" s="6">
+        <v>46253</v>
+      </c>
       <c r="B263" s="5"/>
-      <c r="C263" s="7"/>
+      <c r="C263" s="7">
+        <v>297000</v>
+      </c>
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A264" s="6"/>
+      <c r="A264" s="6">
+        <v>46254</v>
+      </c>
       <c r="B264" s="5"/>
-      <c r="C264" s="7"/>
+      <c r="C264" s="7">
+        <v>405900</v>
+      </c>
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A265" s="6"/>
+      <c r="A265" s="6">
+        <v>46255</v>
+      </c>
       <c r="B265" s="5"/>
-      <c r="C265" s="7"/>
+      <c r="C265" s="7">
+        <v>290700</v>
+      </c>
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A266" s="6"/>
+      <c r="A266" s="6">
+        <v>46256</v>
+      </c>
       <c r="B266" s="5"/>
-      <c r="C266" s="7"/>
+      <c r="C266" s="7">
+        <v>309600</v>
+      </c>
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A267" s="6"/>
+      <c r="A267" s="6">
+        <v>46257</v>
+      </c>
       <c r="B267" s="5"/>
-      <c r="C267" s="7"/>
+      <c r="C267" s="7">
+        <v>243000</v>
+      </c>
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A268" s="6"/>
+      <c r="A268" s="6">
+        <v>46258</v>
+      </c>
       <c r="B268" s="5"/>
-      <c r="C268" s="7"/>
+      <c r="C268" s="7">
+        <v>261900</v>
+      </c>
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A269" s="6"/>
+      <c r="A269" s="6">
+        <v>46259</v>
+      </c>
       <c r="B269" s="5"/>
-      <c r="C269" s="7"/>
+      <c r="C269" s="7">
+        <v>306000</v>
+      </c>
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A270" s="6"/>
+      <c r="A270" s="6">
+        <v>46260</v>
+      </c>
       <c r="B270" s="5"/>
-      <c r="C270" s="7"/>
+      <c r="C270" s="7">
+        <v>286200</v>
+      </c>
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A271" s="6"/>
+      <c r="A271" s="6">
+        <v>46261</v>
+      </c>
       <c r="B271" s="5"/>
-      <c r="C271" s="7"/>
+      <c r="C271" s="7">
+        <v>224100</v>
+      </c>
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A272" s="6"/>
+      <c r="A272" s="6">
+        <v>46262</v>
+      </c>
       <c r="B272" s="5"/>
-      <c r="C272" s="7"/>
+      <c r="C272" s="7">
+        <v>256500</v>
+      </c>
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A273" s="6"/>
+      <c r="A273" s="6">
+        <v>46263</v>
+      </c>
       <c r="B273" s="5"/>
-      <c r="C273" s="7"/>
+      <c r="C273" s="7">
+        <v>211500</v>
+      </c>
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A274" s="6"/>
+      <c r="A274" s="6">
+        <v>46264</v>
+      </c>
       <c r="B274" s="5"/>
-      <c r="C274" s="7"/>
+      <c r="C274" s="7">
+        <v>338400</v>
+      </c>
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A275" s="6"/>
+      <c r="A275" s="6">
+        <v>46265</v>
+      </c>
       <c r="B275" s="5"/>
-      <c r="C275" s="7"/>
+      <c r="C275" s="7">
+        <v>359100</v>
+      </c>
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B94696-653F-4F9F-A938-795ACF1FE4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61187052-136E-4B36-B59F-82558ADAEE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -915,7 +915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E801"/>
+  <dimension ref="A1:E852"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -943,3374 +943,4004 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
-        <v>45992</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="7">
-        <v>239400</v>
+      <c r="C2">
+        <v>279900</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
-        <v>45993</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7">
-        <v>313650</v>
+        <v>46267</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3">
+        <v>268650</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6">
-        <v>45994</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="7">
-        <v>306000</v>
+        <v>46268</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4">
+        <v>295650</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="6">
-        <v>45995</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="7">
-        <v>217350</v>
+        <v>46269</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5">
+        <v>246150</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
-        <v>45996</v>
-      </c>
-      <c r="B6" s="5"/>
+        <v>46270</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C6" s="7">
-        <v>354600</v>
+        <v>335250</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
-        <v>45997</v>
-      </c>
-      <c r="B7" s="5"/>
+        <v>46271</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C7" s="7">
-        <v>334350</v>
+        <v>216900</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
-        <v>45998</v>
-      </c>
-      <c r="B8" s="5"/>
+        <v>46272</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C8" s="7">
-        <v>214650</v>
+        <v>231300</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="6">
-        <v>45999</v>
-      </c>
-      <c r="B9" s="5"/>
+        <v>46273</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C9" s="7">
-        <v>282600</v>
+        <v>156150</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="6">
-        <v>46000</v>
-      </c>
-      <c r="B10" s="5"/>
+        <v>46274</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C10" s="7">
-        <v>161550</v>
+        <v>218250</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="6">
-        <v>46001</v>
-      </c>
-      <c r="B11" s="5"/>
+        <v>46275</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C11" s="7">
-        <v>266400</v>
+        <v>230850</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="6">
-        <v>46002</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>46276</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C12" s="7">
-        <v>193050</v>
+        <v>214200</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="6">
-        <v>46003</v>
-      </c>
-      <c r="B13" s="5"/>
+        <v>46277</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C13" s="7">
-        <v>193050</v>
+        <v>224550</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="6">
-        <v>46004</v>
-      </c>
-      <c r="B14" s="5"/>
+        <v>46278</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C14" s="7">
-        <v>188100</v>
+        <v>247500</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="6">
-        <v>46005</v>
-      </c>
-      <c r="B15" s="5"/>
+        <v>46279</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C15" s="7">
-        <v>229050</v>
+        <v>196650</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="6">
-        <v>46006</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="7">
-        <v>216900</v>
-      </c>
+      <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="6">
-        <v>46007</v>
-      </c>
+      <c r="A17" s="6"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="7">
-        <v>217800</v>
-      </c>
+      <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="6">
-        <v>46008</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="7">
-        <v>192600</v>
-      </c>
+      <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="6">
-        <v>46009</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="7">
-        <v>177750</v>
-      </c>
+      <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="6">
-        <v>46010</v>
-      </c>
+      <c r="A20" s="6"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="7">
-        <v>269550</v>
-      </c>
+      <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="6">
-        <v>46011</v>
-      </c>
+      <c r="A21" s="6"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="7">
-        <v>225900</v>
-      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="6">
-        <v>46012</v>
-      </c>
+      <c r="A22" s="6"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="7">
-        <v>173300</v>
-      </c>
+      <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="6">
-        <v>46013</v>
-      </c>
+      <c r="A23" s="6"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7">
-        <v>151200</v>
-      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="6">
-        <v>46014</v>
-      </c>
+      <c r="A24" s="6"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="7">
-        <v>170100</v>
-      </c>
+      <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="6">
-        <v>46015</v>
-      </c>
+      <c r="A25" s="6"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7">
-        <v>101700</v>
-      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="6">
-        <v>46016</v>
-      </c>
+      <c r="A26" s="6"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="7">
-        <v>127350</v>
-      </c>
+      <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="6">
-        <v>46017</v>
-      </c>
+      <c r="A27" s="6"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7">
-        <v>123750</v>
-      </c>
+      <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="6">
-        <v>46018</v>
-      </c>
+      <c r="A28" s="6"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="7">
-        <v>146700</v>
-      </c>
+      <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="6">
-        <v>46019</v>
-      </c>
+      <c r="A29" s="6"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7">
-        <v>97650</v>
-      </c>
+      <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="6">
-        <v>46020</v>
-      </c>
+      <c r="A30" s="6"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="7">
-        <v>76500</v>
-      </c>
+      <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="6">
-        <v>46021</v>
-      </c>
+      <c r="A31" s="6"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7">
-        <v>69300</v>
-      </c>
+      <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="6">
-        <v>46022</v>
-      </c>
+      <c r="A32" s="6"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="7">
-        <v>73350</v>
-      </c>
+      <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6">
-        <v>46023</v>
-      </c>
+      <c r="A33" s="6"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7">
-        <v>56250</v>
-      </c>
+      <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="6">
-        <v>46024</v>
-      </c>
+      <c r="A34" s="6"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="7">
-        <v>103950</v>
-      </c>
+      <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="6">
-        <v>46025</v>
-      </c>
+      <c r="A35" s="6"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7">
-        <v>86850</v>
-      </c>
+      <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>46026</v>
-      </c>
+      <c r="A36" s="6"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="7">
-        <v>114300</v>
-      </c>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>46027</v>
-      </c>
+      <c r="A37" s="6"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7">
-        <v>199350</v>
-      </c>
+      <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>46028</v>
-      </c>
+      <c r="A38" s="6"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="7">
-        <v>138600</v>
-      </c>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>46029</v>
-      </c>
+      <c r="A39" s="6"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="7">
-        <v>139950</v>
-      </c>
+      <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>46030</v>
-      </c>
+      <c r="A40" s="6"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="7">
-        <v>167850</v>
-      </c>
+      <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>46031</v>
-      </c>
+      <c r="A41" s="6"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="7">
-        <v>162900</v>
-      </c>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>46032</v>
-      </c>
+      <c r="A42" s="6"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="7">
-        <v>206100</v>
-      </c>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>46033</v>
-      </c>
+      <c r="A43" s="6"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="7">
-        <v>243000</v>
-      </c>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>46034</v>
-      </c>
+      <c r="A44" s="6"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="7">
-        <v>173700</v>
-      </c>
+      <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>46035</v>
-      </c>
+      <c r="A45" s="6"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="7">
-        <v>159300</v>
-      </c>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>46036</v>
-      </c>
+      <c r="A46" s="6"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="7">
-        <v>146700</v>
-      </c>
+      <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>46037</v>
-      </c>
+      <c r="A47" s="6"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="7">
-        <v>292500</v>
-      </c>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>46038</v>
-      </c>
+      <c r="A48" s="6"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="7">
-        <v>264150</v>
-      </c>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>46039</v>
-      </c>
+      <c r="A49" s="6"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="7">
-        <v>664650</v>
-      </c>
+      <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>46040</v>
-      </c>
+      <c r="A50" s="6"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="7">
-        <v>408600</v>
-      </c>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>46041</v>
-      </c>
+      <c r="A51" s="6"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="7">
-        <v>385650</v>
-      </c>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>46042</v>
-      </c>
+      <c r="A52" s="6"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="7">
-        <v>541800</v>
-      </c>
+      <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="6">
-        <v>46043</v>
-      </c>
-      <c r="B53" s="5"/>
+        <v>45992</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C53" s="7">
-        <v>351000</v>
+        <v>239400</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="6">
-        <v>46044</v>
-      </c>
-      <c r="B54" s="5"/>
+        <v>45993</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C54" s="7">
-        <v>231300</v>
+        <v>313650</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="6">
-        <v>46045</v>
-      </c>
-      <c r="B55" s="5"/>
+        <v>45994</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C55" s="7">
-        <v>346500</v>
+        <v>306000</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="6">
-        <v>46046</v>
-      </c>
-      <c r="B56" s="5"/>
+        <v>45995</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C56" s="7">
-        <v>285300</v>
+        <v>217350</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="6">
-        <v>46047</v>
-      </c>
-      <c r="B57" s="5"/>
+        <v>45996</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C57" s="7">
-        <v>336600</v>
+        <v>354600</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="6">
-        <v>46048</v>
-      </c>
-      <c r="B58" s="5"/>
+        <v>45997</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C58" s="7">
-        <v>321750</v>
+        <v>334350</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="6">
-        <v>46049</v>
-      </c>
-      <c r="B59" s="5"/>
+        <v>45998</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C59" s="7">
-        <v>362700</v>
+        <v>214650</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B60" s="5"/>
+        <v>45999</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C60" s="7">
-        <v>297900</v>
+        <v>282600</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="6">
-        <v>46051</v>
-      </c>
-      <c r="B61" s="5"/>
+        <v>46000</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C61" s="7">
-        <v>304650</v>
+        <v>161550</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="6">
-        <v>46052</v>
-      </c>
-      <c r="B62" s="5"/>
+        <v>46001</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C62" s="7">
-        <v>201150</v>
+        <v>266400</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="6">
-        <v>46053</v>
-      </c>
-      <c r="B63" s="5"/>
+        <v>46002</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C63" s="7">
-        <v>287100</v>
+        <v>193050</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B64" s="5"/>
+        <v>46003</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C64" s="7">
-        <v>337500</v>
+        <v>193050</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="6">
-        <v>46055</v>
-      </c>
-      <c r="B65" s="5"/>
+        <v>46004</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C65" s="7">
-        <v>202500</v>
+        <v>188100</v>
       </c>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B66" s="5"/>
+        <v>46005</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C66" s="7">
-        <v>236250</v>
+        <v>229050</v>
       </c>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="6">
-        <v>46057</v>
-      </c>
-      <c r="B67" s="5"/>
+        <v>46006</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C67" s="7">
-        <v>220950</v>
+        <v>216900</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="6">
-        <v>46058</v>
-      </c>
-      <c r="B68" s="5"/>
+        <v>46007</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C68" s="7">
-        <v>271800</v>
+        <v>217800</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="6">
-        <v>46059</v>
-      </c>
-      <c r="B69" s="5"/>
+        <v>46008</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C69" s="7">
-        <v>303750</v>
+        <v>192600</v>
       </c>
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="6">
-        <v>46060</v>
-      </c>
-      <c r="B70" s="5"/>
+        <v>46009</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C70" s="7">
-        <v>234450</v>
+        <v>177750</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="6">
-        <v>46061</v>
-      </c>
-      <c r="B71" s="5"/>
+        <v>46010</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C71" s="7">
-        <v>320400</v>
+        <v>269550</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="6">
-        <v>46062</v>
-      </c>
-      <c r="B72" s="5"/>
+        <v>46011</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C72" s="7">
-        <v>239400</v>
+        <v>225900</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="6">
-        <v>46063</v>
-      </c>
-      <c r="B73" s="5"/>
+        <v>46012</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C73" s="7">
-        <v>154350</v>
+        <v>173300</v>
       </c>
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="6">
-        <v>46064</v>
-      </c>
-      <c r="B74" s="5"/>
+        <v>46013</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C74" s="7">
-        <v>343800</v>
+        <v>151200</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="6">
-        <v>46065</v>
-      </c>
-      <c r="B75" s="5"/>
+        <v>46014</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C75" s="7">
-        <v>193950</v>
+        <v>170100</v>
       </c>
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="6">
-        <v>46066</v>
-      </c>
-      <c r="B76" s="5"/>
+        <v>46015</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C76" s="7">
-        <v>182250</v>
+        <v>101700</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="6">
-        <v>46067</v>
-      </c>
-      <c r="B77" s="5"/>
+        <v>46016</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C77" s="7">
-        <v>171000</v>
+        <v>127350</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="6">
-        <v>46068</v>
-      </c>
-      <c r="B78" s="5"/>
+        <v>46017</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C78" s="7">
-        <v>243900</v>
+        <v>123750</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="6">
-        <v>46069</v>
-      </c>
-      <c r="B79" s="5"/>
+        <v>46018</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C79" s="7">
-        <v>117900</v>
+        <v>146700</v>
       </c>
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="6">
-        <v>46070</v>
-      </c>
-      <c r="B80" s="5"/>
+        <v>46019</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C80" s="7">
-        <v>212400</v>
+        <v>97650</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A81" s="6">
-        <v>46071</v>
-      </c>
-      <c r="B81" s="5"/>
+        <v>46020</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C81" s="7">
-        <v>310050</v>
+        <v>76500</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="6">
-        <v>46072</v>
-      </c>
-      <c r="B82" s="5"/>
+        <v>46021</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C82" s="7">
-        <v>297900</v>
+        <v>69300</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="6">
-        <v>46073</v>
-      </c>
-      <c r="B83" s="5"/>
+        <v>46022</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C83" s="7">
-        <v>325800</v>
+        <v>73350</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="6">
-        <v>46074</v>
-      </c>
-      <c r="B84" s="5"/>
+        <v>46023</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C84" s="7">
-        <v>312300</v>
+        <v>56250</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="6">
-        <v>46075</v>
-      </c>
-      <c r="B85" s="5"/>
+        <v>46024</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C85" s="7">
-        <v>314100</v>
+        <v>103950</v>
       </c>
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="6">
-        <v>46076</v>
-      </c>
-      <c r="B86" s="5"/>
+        <v>46025</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C86" s="7">
-        <v>397350</v>
+        <v>86850</v>
       </c>
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="6">
-        <v>46077</v>
-      </c>
-      <c r="B87" s="5"/>
+        <v>46026</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C87" s="7">
-        <v>198450</v>
+        <v>114300</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="6">
-        <v>46078</v>
-      </c>
-      <c r="B88" s="5"/>
+        <v>46027</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C88" s="7">
-        <v>292500</v>
+        <v>199350</v>
       </c>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="6">
-        <v>46079</v>
-      </c>
-      <c r="B89" s="5"/>
+        <v>46028</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C89" s="7">
-        <v>326250</v>
+        <v>138600</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="6">
-        <v>46080</v>
-      </c>
-      <c r="B90" s="5"/>
+        <v>46029</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C90" s="7">
-        <v>241650</v>
+        <v>139950</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="6">
-        <v>46081</v>
-      </c>
-      <c r="B91" s="5"/>
+        <v>46030</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C91" s="7">
-        <v>216000</v>
+        <v>167850</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="6">
-        <v>46082</v>
-      </c>
-      <c r="B92" s="5"/>
+        <v>46031</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C92" s="7">
-        <v>281700</v>
+        <v>162900</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="6">
-        <v>46083</v>
-      </c>
-      <c r="B93" s="5"/>
+        <v>46032</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C93" s="7">
-        <v>272250</v>
+        <v>206100</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="6">
-        <v>46084</v>
-      </c>
-      <c r="B94" s="5"/>
+        <v>46033</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C94" s="7">
-        <v>245250</v>
+        <v>243000</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="6">
-        <v>46085</v>
-      </c>
-      <c r="B95" s="5"/>
+        <v>46034</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C95" s="7">
-        <v>261000</v>
+        <v>173700</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="6">
-        <v>46086</v>
-      </c>
-      <c r="B96" s="5"/>
+        <v>46035</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C96" s="7">
-        <v>166950</v>
+        <v>159300</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="6">
-        <v>46087</v>
-      </c>
-      <c r="B97" s="5"/>
+        <v>46036</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C97" s="7">
-        <v>215550</v>
+        <v>146700</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="6">
-        <v>46088</v>
-      </c>
-      <c r="B98" s="5"/>
+        <v>46037</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C98" s="7">
-        <v>197550</v>
+        <v>292500</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="6">
-        <v>46089</v>
-      </c>
-      <c r="B99" s="5"/>
+        <v>46038</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C99" s="7">
-        <v>194850</v>
+        <v>264150</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="6">
-        <v>46090</v>
-      </c>
-      <c r="B100" s="5"/>
+        <v>46039</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C100" s="7">
-        <v>182700</v>
+        <v>664650</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="6">
-        <v>46091</v>
-      </c>
-      <c r="B101" s="5"/>
+        <v>46040</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C101" s="7">
-        <v>171000</v>
+        <v>408600</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="6">
-        <v>46092</v>
-      </c>
-      <c r="B102" s="5"/>
+        <v>46041</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C102" s="7">
-        <v>189450</v>
+        <v>385650</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="6">
-        <v>46093</v>
-      </c>
-      <c r="B103" s="5"/>
+        <v>46042</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C103" s="7">
-        <v>245700</v>
+        <v>541800</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="6">
-        <v>46094</v>
-      </c>
-      <c r="B104" s="5"/>
+        <v>46043</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C104" s="7">
-        <v>135000</v>
+        <v>351000</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="6">
-        <v>46095</v>
-      </c>
-      <c r="B105" s="5"/>
+        <v>46044</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C105" s="7">
-        <v>225900</v>
+        <v>231300</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="6">
-        <v>46096</v>
-      </c>
-      <c r="B106" s="5"/>
+        <v>46045</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C106" s="7">
-        <v>297900</v>
+        <v>346500</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="6">
-        <v>46097</v>
-      </c>
-      <c r="B107" s="5"/>
+        <v>46046</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C107" s="7">
-        <v>292950</v>
+        <v>285300</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="6">
-        <v>46098</v>
-      </c>
-      <c r="B108" s="5"/>
+        <v>46047</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C108" s="7">
-        <v>341550</v>
+        <v>336600</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="6">
-        <v>46099</v>
-      </c>
-      <c r="B109" s="5"/>
+        <v>46048</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C109" s="7">
-        <v>280350</v>
+        <v>321750</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="6">
-        <v>46100</v>
-      </c>
-      <c r="B110" s="5"/>
+        <v>46049</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C110" s="7">
-        <v>433800</v>
+        <v>362700</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="6">
-        <v>46101</v>
-      </c>
-      <c r="B111" s="5"/>
+        <v>46050</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C111" s="7">
-        <v>538200</v>
+        <v>297900</v>
       </c>
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="6">
-        <v>46102</v>
-      </c>
-      <c r="B112" s="5"/>
+        <v>46051</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C112" s="7">
-        <v>274500</v>
+        <v>304650</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="6">
-        <v>46103</v>
-      </c>
-      <c r="B113" s="5"/>
+        <v>46052</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C113" s="7">
-        <v>384300</v>
+        <v>201150</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="6">
-        <v>46104</v>
-      </c>
-      <c r="B114" s="5"/>
+        <v>46053</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C114" s="7">
-        <v>302850</v>
+        <v>287100</v>
       </c>
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="6">
-        <v>46105</v>
-      </c>
-      <c r="B115" s="5"/>
+        <v>46054</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C115" s="7">
-        <v>194850</v>
+        <v>337500</v>
       </c>
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="6">
-        <v>46106</v>
-      </c>
-      <c r="B116" s="5"/>
+        <v>46055</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C116" s="7">
-        <v>260100</v>
+        <v>202500</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="6">
-        <v>46107</v>
-      </c>
-      <c r="B117" s="5"/>
+        <v>46056</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C117" s="7">
-        <v>238500</v>
+        <v>236250</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="6">
-        <v>46108</v>
-      </c>
-      <c r="B118" s="5"/>
+        <v>46057</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C118" s="7">
-        <v>175050</v>
+        <v>220950</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="6">
-        <v>46109</v>
-      </c>
-      <c r="B119" s="5"/>
+        <v>46058</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C119" s="7">
-        <v>337050</v>
+        <v>271800</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="6">
-        <v>46110</v>
-      </c>
-      <c r="B120" s="5"/>
+        <v>46059</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C120" s="7">
-        <v>307350</v>
+        <v>303750</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="6">
-        <v>46111</v>
-      </c>
-      <c r="B121" s="5"/>
+        <v>46060</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C121" s="7">
-        <v>276300</v>
+        <v>234450</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="6">
-        <v>46112</v>
-      </c>
-      <c r="B122" s="5"/>
+        <v>46061</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C122" s="7">
-        <v>349650</v>
+        <v>320400</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B123" s="5"/>
+        <v>46062</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C123" s="7">
-        <v>290250</v>
+        <v>239400</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A124" s="6">
-        <v>46114</v>
-      </c>
-      <c r="B124" s="5"/>
+        <v>46063</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C124" s="7">
-        <v>317250</v>
+        <v>154350</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A125" s="6">
-        <v>46115</v>
-      </c>
-      <c r="B125" s="5"/>
+        <v>46064</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C125" s="7">
-        <v>317250</v>
+        <v>343800</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="6">
-        <v>46116</v>
-      </c>
-      <c r="B126" s="5"/>
+        <v>46065</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C126" s="7">
-        <v>538200</v>
+        <v>193950</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="6">
-        <v>46117</v>
-      </c>
-      <c r="B127" s="5"/>
+        <v>46066</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C127" s="7">
-        <v>454050</v>
+        <v>182250</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="6">
-        <v>46118</v>
-      </c>
-      <c r="B128" s="5"/>
+        <v>46067</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C128" s="7">
-        <v>519300</v>
+        <v>171000</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A129" s="6">
-        <v>46119</v>
-      </c>
-      <c r="B129" s="5"/>
+        <v>46068</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C129" s="7">
-        <v>492750</v>
+        <v>243900</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="6">
-        <v>46120</v>
-      </c>
-      <c r="B130" s="5"/>
+        <v>46069</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C130" s="7">
-        <v>431100</v>
+        <v>117900</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="6">
-        <v>46121</v>
-      </c>
-      <c r="B131" s="5"/>
+        <v>46070</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C131" s="7">
-        <v>354600</v>
+        <v>212400</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="6">
-        <v>46122</v>
-      </c>
-      <c r="B132" s="5"/>
+        <v>46071</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C132" s="7">
-        <v>416700</v>
+        <v>310050</v>
       </c>
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="6">
-        <v>46123</v>
-      </c>
-      <c r="B133" s="5"/>
+        <v>46072</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C133" s="7">
-        <v>444600</v>
+        <v>297900</v>
       </c>
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="6">
-        <v>46124</v>
-      </c>
-      <c r="B134" s="5"/>
+        <v>46073</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C134" s="7">
-        <v>438750</v>
+        <v>325800</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="6">
-        <v>46125</v>
-      </c>
-      <c r="B135" s="5"/>
+        <v>46074</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C135" s="7">
-        <v>408150</v>
+        <v>312300</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="6">
-        <v>46126</v>
-      </c>
-      <c r="B136" s="5"/>
+        <v>46075</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C136" s="7">
-        <v>315450</v>
+        <v>314100</v>
       </c>
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="6">
-        <v>46127</v>
-      </c>
-      <c r="B137" s="5"/>
+        <v>46076</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C137" s="7">
-        <v>463050</v>
+        <v>397350</v>
       </c>
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="6">
-        <v>46128</v>
-      </c>
-      <c r="B138" s="5"/>
+        <v>46077</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C138" s="7">
-        <v>504450</v>
+        <v>198450</v>
       </c>
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="6">
-        <v>46129</v>
-      </c>
-      <c r="B139" s="5"/>
+        <v>46078</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C139" s="7">
-        <v>405000</v>
+        <v>292500</v>
       </c>
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="6">
-        <v>46130</v>
-      </c>
-      <c r="B140" s="5"/>
+        <v>46079</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C140" s="7">
-        <v>486450</v>
+        <v>326250</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="6">
-        <v>46131</v>
-      </c>
-      <c r="B141" s="5"/>
+        <v>46080</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C141" s="7">
-        <v>718200</v>
+        <v>241650</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="6">
-        <v>46132</v>
-      </c>
-      <c r="B142" s="5"/>
+        <v>46081</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C142" s="7">
-        <v>769500</v>
+        <v>216000</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="6">
-        <v>46133</v>
-      </c>
-      <c r="B143" s="5"/>
+        <v>46082</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C143" s="7">
-        <v>737550</v>
+        <v>281700</v>
       </c>
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A144" s="6">
-        <v>46134</v>
-      </c>
-      <c r="B144" s="5"/>
+        <v>46083</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C144" s="7">
-        <v>525150</v>
+        <v>272250</v>
       </c>
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A145" s="6">
-        <v>46135</v>
-      </c>
-      <c r="B145" s="5"/>
+        <v>46084</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C145" s="7">
-        <v>768150</v>
+        <v>245250</v>
       </c>
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="6">
-        <v>46136</v>
-      </c>
-      <c r="B146" s="5"/>
+        <v>46085</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C146" s="7">
-        <v>479700</v>
+        <v>261000</v>
       </c>
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="6">
-        <v>46137</v>
-      </c>
-      <c r="B147" s="5"/>
+        <v>46086</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C147" s="7">
-        <v>507600</v>
+        <v>166950</v>
       </c>
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="6">
-        <v>46138</v>
-      </c>
-      <c r="B148" s="5"/>
+        <v>46087</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C148" s="7">
-        <v>662400</v>
+        <v>215550</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="6">
-        <v>46139</v>
-      </c>
-      <c r="B149" s="5"/>
+        <v>46088</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C149" s="7">
-        <v>509400</v>
+        <v>197550</v>
       </c>
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A150" s="6">
-        <v>46140</v>
-      </c>
-      <c r="B150" s="5"/>
+        <v>46089</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C150" s="7">
-        <v>302850</v>
+        <v>194850</v>
       </c>
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A151" s="6">
-        <v>46141</v>
-      </c>
-      <c r="B151" s="5"/>
+        <v>46090</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C151" s="7">
-        <v>413100</v>
+        <v>182700</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A152" s="6">
-        <v>46142</v>
-      </c>
-      <c r="B152" s="5"/>
+        <v>46091</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C152" s="7">
-        <v>544500</v>
+        <v>171000</v>
       </c>
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A153" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B153" s="5"/>
+        <v>46092</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C153" s="7">
-        <v>173250</v>
+        <v>189450</v>
       </c>
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A154" s="6">
-        <v>46144</v>
-      </c>
-      <c r="B154" s="5"/>
+        <v>46093</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C154" s="7">
-        <v>162450</v>
+        <v>245700</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A155" s="6">
-        <v>46145</v>
-      </c>
-      <c r="B155" s="5"/>
+        <v>46094</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C155" s="7">
-        <v>122400</v>
+        <v>135000</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A156" s="6">
-        <v>46146</v>
-      </c>
-      <c r="B156" s="5"/>
+        <v>46095</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C156" s="7">
-        <v>99000</v>
+        <v>225900</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A157" s="6">
-        <v>46147</v>
-      </c>
-      <c r="B157" s="5"/>
+        <v>46096</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C157" s="7">
-        <v>126000</v>
+        <v>297900</v>
       </c>
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A158" s="6">
-        <v>46148</v>
-      </c>
-      <c r="B158" s="5"/>
+        <v>46097</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C158" s="7">
-        <v>126900</v>
+        <v>292950</v>
       </c>
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A159" s="6">
-        <v>46149</v>
-      </c>
-      <c r="B159" s="5"/>
+        <v>46098</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C159" s="7">
-        <v>152100</v>
+        <v>341550</v>
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A160" s="6">
-        <v>46150</v>
-      </c>
-      <c r="B160" s="5"/>
+        <v>46099</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C160" s="7">
-        <v>148050</v>
+        <v>280350</v>
       </c>
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A161" s="6">
-        <v>46151</v>
-      </c>
-      <c r="B161" s="5"/>
+        <v>46100</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C161" s="7">
-        <v>174150</v>
+        <v>433800</v>
       </c>
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A162" s="6">
-        <v>46152</v>
-      </c>
-      <c r="B162" s="5"/>
+        <v>46101</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C162" s="7">
-        <v>194850</v>
+        <v>538200</v>
       </c>
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A163" s="6">
-        <v>46153</v>
-      </c>
-      <c r="B163" s="5"/>
+        <v>46102</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C163" s="7">
-        <v>150300</v>
+        <v>274500</v>
       </c>
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A164" s="6">
-        <v>46154</v>
-      </c>
-      <c r="B164" s="5"/>
+        <v>46103</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C164" s="7">
-        <v>154350</v>
+        <v>384300</v>
       </c>
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A165" s="6">
-        <v>46155</v>
-      </c>
-      <c r="B165" s="5"/>
+        <v>46104</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C165" s="7">
-        <v>89100</v>
+        <v>302850</v>
       </c>
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A166" s="6">
-        <v>46156</v>
-      </c>
-      <c r="B166" s="5"/>
+        <v>46105</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C166" s="7">
-        <v>93150</v>
+        <v>194850</v>
       </c>
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A167" s="6">
-        <v>46157</v>
-      </c>
-      <c r="B167" s="5"/>
+        <v>46106</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C167" s="7">
-        <v>108900</v>
+        <v>260100</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A168" s="6">
-        <v>46158</v>
-      </c>
-      <c r="B168" s="5"/>
+        <v>46107</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C168" s="7">
-        <v>117900</v>
+        <v>238500</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A169" s="6">
-        <v>46159</v>
-      </c>
-      <c r="B169" s="5"/>
+        <v>46108</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C169" s="7">
-        <v>216000</v>
+        <v>175050</v>
       </c>
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A170" s="6">
-        <v>46160</v>
-      </c>
-      <c r="B170" s="5"/>
+        <v>46109</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C170" s="7">
-        <v>170550</v>
+        <v>337050</v>
       </c>
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A171" s="6">
-        <v>46161</v>
-      </c>
-      <c r="B171" s="5"/>
+        <v>46110</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C171" s="7">
-        <v>197550</v>
+        <v>307350</v>
       </c>
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A172" s="6">
-        <v>46162</v>
-      </c>
-      <c r="B172" s="5"/>
+        <v>46111</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C172" s="7">
-        <v>215550</v>
+        <v>276300</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A173" s="6">
-        <v>46163</v>
-      </c>
-      <c r="B173" s="5"/>
+        <v>46112</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C173" s="7">
-        <v>191700</v>
+        <v>349650</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A174" s="6">
-        <v>46164</v>
-      </c>
-      <c r="B174" s="5"/>
+        <v>46113</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C174" s="7">
-        <v>252000</v>
+        <v>290250</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A175" s="6">
-        <v>46165</v>
-      </c>
-      <c r="B175" s="5"/>
+        <v>46114</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C175" s="7">
-        <v>176850</v>
+        <v>317250</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A176" s="6">
-        <v>46166</v>
-      </c>
-      <c r="B176" s="5"/>
+        <v>46115</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C176" s="7">
-        <v>115650</v>
+        <v>317250</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A177" s="6">
-        <v>46167</v>
-      </c>
-      <c r="B177" s="5"/>
+        <v>46116</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C177" s="7">
-        <v>211950</v>
+        <v>538200</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A178" s="6">
-        <v>46168</v>
-      </c>
-      <c r="B178" s="5"/>
+        <v>46117</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C178" s="7">
-        <v>263700</v>
+        <v>454050</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A179" s="6">
-        <v>46169</v>
-      </c>
-      <c r="B179" s="5"/>
+        <v>46118</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C179" s="7">
-        <v>184050</v>
+        <v>519300</v>
       </c>
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A180" s="6">
-        <v>46170</v>
-      </c>
-      <c r="B180" s="5"/>
+        <v>46119</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C180" s="7">
-        <v>141750</v>
+        <v>492750</v>
       </c>
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A181" s="6">
-        <v>46171</v>
-      </c>
-      <c r="B181" s="5"/>
+        <v>46120</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C181" s="7">
-        <v>186750</v>
+        <v>431100</v>
       </c>
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A182" s="6">
-        <v>46172</v>
-      </c>
-      <c r="B182" s="5"/>
+        <v>46121</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C182" s="7">
-        <v>207450</v>
+        <v>354600</v>
       </c>
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A183" s="6">
-        <v>46173</v>
-      </c>
-      <c r="B183" s="5"/>
+        <v>46122</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C183" s="7">
-        <v>338400</v>
+        <v>416700</v>
       </c>
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A184" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B184" s="5"/>
+        <v>46123</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C184" s="7">
-        <v>270000</v>
+        <v>444600</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A185" s="6">
-        <v>46175</v>
-      </c>
-      <c r="B185" s="5"/>
+        <v>46124</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C185" s="7">
-        <v>347400</v>
+        <v>438750</v>
       </c>
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A186" s="6">
-        <v>46176</v>
-      </c>
-      <c r="B186" s="5"/>
+        <v>46125</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C186" s="7">
-        <v>344700</v>
+        <v>408150</v>
       </c>
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A187" s="6">
-        <v>46177</v>
-      </c>
-      <c r="B187" s="5"/>
+        <v>46126</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C187" s="7">
-        <v>249750</v>
+        <v>315450</v>
       </c>
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A188" s="6">
-        <v>46178</v>
-      </c>
-      <c r="B188" s="5"/>
+        <v>46127</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C188" s="7">
-        <v>289350</v>
+        <v>463050</v>
       </c>
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A189" s="6">
-        <v>46179</v>
-      </c>
-      <c r="B189" s="5"/>
+        <v>46128</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C189" s="7">
-        <v>342000</v>
+        <v>504450</v>
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A190" s="6">
-        <v>46180</v>
-      </c>
-      <c r="B190" s="5"/>
+        <v>46129</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C190" s="7">
-        <v>396450</v>
+        <v>405000</v>
       </c>
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A191" s="6">
-        <v>46181</v>
-      </c>
-      <c r="B191" s="5"/>
+        <v>46130</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C191" s="7">
-        <v>315000</v>
+        <v>486450</v>
       </c>
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A192" s="6">
-        <v>46182</v>
-      </c>
-      <c r="B192" s="5"/>
+        <v>46131</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C192" s="7">
-        <v>187650</v>
+        <v>718200</v>
       </c>
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="6">
-        <v>46183</v>
-      </c>
-      <c r="B193" s="5"/>
+        <v>46132</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C193" s="7">
-        <v>256500</v>
+        <v>769500</v>
       </c>
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="6">
-        <v>46184</v>
-      </c>
-      <c r="B194" s="5"/>
+        <v>46133</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C194" s="7">
-        <v>279450</v>
+        <v>737550</v>
       </c>
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="6">
-        <v>46185</v>
-      </c>
-      <c r="B195" s="5"/>
+        <v>46134</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C195" s="7">
-        <v>314100</v>
+        <v>525150</v>
       </c>
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="6">
-        <v>46186</v>
-      </c>
-      <c r="B196" s="5"/>
+        <v>46135</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C196" s="7">
-        <v>358650</v>
+        <v>768150</v>
       </c>
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="6">
-        <v>46187</v>
-      </c>
-      <c r="B197" s="5"/>
+        <v>46136</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C197" s="7">
-        <v>422100</v>
+        <v>479700</v>
       </c>
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="6">
-        <v>46188</v>
-      </c>
-      <c r="B198" s="5"/>
+        <v>46137</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C198" s="7">
-        <v>362250</v>
+        <v>507600</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="6">
-        <v>46189</v>
-      </c>
-      <c r="B199" s="5"/>
+        <v>46138</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C199" s="7">
-        <v>448650</v>
+        <v>662400</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="6">
-        <v>46190</v>
-      </c>
-      <c r="B200" s="5"/>
+        <v>46139</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C200" s="7">
-        <v>362700</v>
+        <v>509400</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="6">
-        <v>46191</v>
-      </c>
-      <c r="B201" s="5"/>
+        <v>46140</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C201" s="7">
-        <v>344700</v>
+        <v>302850</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A202" s="6">
-        <v>46192</v>
-      </c>
-      <c r="B202" s="5"/>
+        <v>46141</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C202" s="7">
-        <v>388350</v>
+        <v>413100</v>
       </c>
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A203" s="6">
-        <v>46193</v>
-      </c>
-      <c r="B203" s="5"/>
+        <v>46142</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C203" s="7">
-        <v>648000</v>
+        <v>544500</v>
       </c>
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A204" s="6">
-        <v>46194</v>
-      </c>
-      <c r="B204" s="5"/>
+        <v>46143</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C204" s="7">
-        <v>595800</v>
+        <v>173250</v>
       </c>
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A205" s="6">
-        <v>46195</v>
-      </c>
-      <c r="B205" s="5"/>
+        <v>46144</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C205" s="7">
-        <v>387450</v>
+        <v>162450</v>
       </c>
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A206" s="6">
-        <v>46196</v>
-      </c>
-      <c r="B206" s="5"/>
+        <v>46145</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C206" s="7">
-        <v>364050</v>
+        <v>122400</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A207" s="6">
-        <v>46197</v>
-      </c>
-      <c r="B207" s="5"/>
+        <v>46146</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C207" s="7">
-        <v>378900</v>
+        <v>99000</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A208" s="6">
-        <v>46198</v>
-      </c>
-      <c r="B208" s="5"/>
+        <v>46147</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C208" s="7">
-        <v>386550</v>
+        <v>126000</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A209" s="6">
-        <v>46199</v>
-      </c>
-      <c r="B209" s="5"/>
+        <v>46148</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C209" s="7">
-        <v>351900</v>
+        <v>126900</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A210" s="6">
-        <v>46200</v>
-      </c>
-      <c r="B210" s="5"/>
+        <v>46149</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C210" s="7">
-        <v>368100</v>
+        <v>152100</v>
       </c>
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A211" s="6">
-        <v>46201</v>
-      </c>
-      <c r="B211" s="5"/>
+        <v>46150</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C211" s="7">
-        <v>544500</v>
+        <v>148050</v>
       </c>
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A212" s="6">
-        <v>46202</v>
-      </c>
-      <c r="B212" s="5"/>
+        <v>46151</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C212" s="7">
-        <v>441900</v>
+        <v>174150</v>
       </c>
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A213" s="6">
-        <v>46203</v>
-      </c>
-      <c r="B213" s="5"/>
+        <v>46152</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C213" s="7">
-        <v>420300</v>
+        <v>194850</v>
       </c>
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A214" s="6">
-        <v>46204</v>
-      </c>
-      <c r="B214" s="5"/>
+        <v>46153</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C214" s="7">
-        <v>342000</v>
+        <v>150300</v>
       </c>
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A215" s="6">
-        <v>46205</v>
-      </c>
-      <c r="B215" s="5"/>
+        <v>46154</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C215" s="7">
-        <v>251550</v>
+        <v>154350</v>
       </c>
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A216" s="6">
-        <v>46206</v>
-      </c>
-      <c r="B216" s="5"/>
+        <v>46155</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C216" s="7">
-        <v>109800</v>
+        <v>89100</v>
       </c>
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A217" s="6">
-        <v>46207</v>
-      </c>
-      <c r="B217" s="5"/>
+        <v>46156</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C217" s="7">
-        <v>169650</v>
+        <v>93150</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A218" s="6">
-        <v>46208</v>
-      </c>
-      <c r="B218" s="5"/>
+        <v>46157</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C218" s="7">
-        <v>216000</v>
+        <v>108900</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A219" s="6">
-        <v>46209</v>
-      </c>
-      <c r="B219" s="5"/>
+        <v>46158</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C219" s="7">
-        <v>255600</v>
+        <v>117900</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A220" s="6">
-        <v>46210</v>
-      </c>
-      <c r="B220" s="5"/>
+        <v>46159</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C220" s="7">
-        <v>154800</v>
+        <v>216000</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A221" s="6">
-        <v>46211</v>
-      </c>
-      <c r="B221" s="5"/>
+        <v>46160</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C221" s="7">
-        <v>121050</v>
+        <v>170550</v>
       </c>
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A222" s="6">
-        <v>46212</v>
-      </c>
-      <c r="B222" s="5"/>
+        <v>46161</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C222" s="7">
-        <v>215100</v>
+        <v>197550</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A223" s="6">
-        <v>46213</v>
-      </c>
-      <c r="B223" s="5"/>
+        <v>46162</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C223" s="7">
-        <v>220050</v>
+        <v>215550</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A224" s="6">
-        <v>46214</v>
-      </c>
-      <c r="B224" s="5"/>
+        <v>46163</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C224" s="7">
-        <v>215100</v>
+        <v>191700</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A225" s="6">
-        <v>46215</v>
-      </c>
-      <c r="B225" s="5"/>
+        <v>46164</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C225" s="7">
-        <v>169650</v>
+        <v>252000</v>
       </c>
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A226" s="6">
-        <v>46216</v>
-      </c>
-      <c r="B226" s="5"/>
+        <v>46165</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C226" s="7">
-        <v>193050</v>
+        <v>176850</v>
       </c>
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A227" s="6">
-        <v>46217</v>
-      </c>
-      <c r="B227" s="5"/>
+        <v>46166</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C227" s="7">
-        <v>468000</v>
+        <v>115650</v>
       </c>
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A228" s="6">
-        <v>46218</v>
-      </c>
-      <c r="B228" s="5"/>
+        <v>46167</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C228" s="7">
-        <v>306000</v>
+        <v>211950</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A229" s="6">
-        <v>46219</v>
-      </c>
-      <c r="B229" s="5"/>
+        <v>46168</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C229" s="7">
-        <v>263250</v>
+        <v>263700</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A230" s="6">
-        <v>46220</v>
-      </c>
-      <c r="B230" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C230" s="7">
-        <v>296550</v>
+        <v>184050</v>
       </c>
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A231" s="6">
-        <v>46221</v>
-      </c>
-      <c r="B231" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C231" s="7">
-        <v>370800</v>
+        <v>141750</v>
       </c>
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A232" s="6">
-        <v>46222</v>
-      </c>
-      <c r="B232" s="5"/>
+        <v>46171</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C232" s="7">
-        <v>379800</v>
+        <v>186750</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A233" s="6">
-        <v>46223</v>
-      </c>
-      <c r="B233" s="5"/>
+        <v>46172</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C233" s="7">
-        <v>497250</v>
+        <v>207450</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A234" s="6">
-        <v>46224</v>
-      </c>
-      <c r="B234" s="5"/>
+        <v>46173</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C234" s="7">
-        <v>344250</v>
+        <v>338400</v>
       </c>
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A235" s="6">
-        <v>46225</v>
-      </c>
-      <c r="B235" s="5"/>
+        <v>46174</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C235" s="7">
-        <v>327150</v>
+        <v>270000</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A236" s="6">
-        <v>46226</v>
-      </c>
-      <c r="B236" s="5"/>
+        <v>46175</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C236" s="7">
-        <v>421650</v>
+        <v>347400</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A237" s="6">
-        <v>46227</v>
-      </c>
-      <c r="B237" s="5"/>
+        <v>46176</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C237" s="7">
-        <v>373500</v>
+        <v>344700</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A238" s="6">
-        <v>46228</v>
-      </c>
-      <c r="B238" s="5"/>
+        <v>46177</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C238" s="7">
-        <v>490950</v>
+        <v>249750</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A239" s="6">
-        <v>46229</v>
-      </c>
-      <c r="B239" s="5"/>
+        <v>46178</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C239" s="7">
-        <v>536400</v>
+        <v>289350</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A240" s="6">
-        <v>46230</v>
-      </c>
-      <c r="B240" s="5"/>
+        <v>46179</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C240" s="7">
-        <v>297000</v>
+        <v>342000</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A241" s="6">
-        <v>46231</v>
-      </c>
-      <c r="B241" s="5"/>
+        <v>46180</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C241" s="7">
-        <v>265050</v>
+        <v>396450</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A242" s="6">
-        <v>46232</v>
-      </c>
-      <c r="B242" s="5"/>
+        <v>46181</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C242" s="7">
-        <v>365850</v>
+        <v>315000</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A243" s="6">
-        <v>46233</v>
-      </c>
-      <c r="B243" s="5"/>
+        <v>46182</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C243" s="7">
-        <v>323100</v>
+        <v>187650</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A244" s="6">
-        <v>46234</v>
-      </c>
-      <c r="B244" s="5"/>
+        <v>46183</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C244" s="7">
-        <v>428850</v>
+        <v>256500</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A245" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B245" s="5"/>
+        <v>46184</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C245" s="7">
-        <v>397350</v>
+        <v>279450</v>
       </c>
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A246" s="6">
-        <v>46236</v>
-      </c>
-      <c r="B246" s="5"/>
+        <v>46185</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C246" s="7">
-        <v>560700</v>
+        <v>314100</v>
       </c>
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A247" s="6">
-        <v>46237</v>
-      </c>
-      <c r="B247" s="5"/>
+        <v>46186</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C247" s="7">
-        <v>454950</v>
+        <v>358650</v>
       </c>
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A248" s="6">
-        <v>46238</v>
-      </c>
-      <c r="B248" s="5"/>
+        <v>46187</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C248" s="7">
-        <v>575100</v>
+        <v>422100</v>
       </c>
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A249" s="6">
-        <v>46239</v>
-      </c>
-      <c r="B249" s="5"/>
+        <v>46188</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C249" s="7">
-        <v>382500</v>
+        <v>362250</v>
       </c>
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A250" s="6">
-        <v>46240</v>
-      </c>
-      <c r="B250" s="5"/>
+        <v>46189</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C250" s="7">
-        <v>333450</v>
+        <v>448650</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A251" s="6">
-        <v>46241</v>
-      </c>
-      <c r="B251" s="5"/>
+        <v>46190</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C251" s="7">
-        <v>360450</v>
+        <v>362700</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A252" s="6">
-        <v>46242</v>
-      </c>
-      <c r="B252" s="5"/>
+        <v>46191</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C252" s="7">
-        <v>312750</v>
+        <v>344700</v>
       </c>
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A253" s="6">
-        <v>46243</v>
-      </c>
-      <c r="B253" s="5"/>
+        <v>46192</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C253" s="7">
-        <v>292050</v>
+        <v>388350</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A254" s="6">
-        <v>46244</v>
-      </c>
-      <c r="B254" s="5"/>
+        <v>46193</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C254" s="7">
-        <v>250200</v>
+        <v>648000</v>
       </c>
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A255" s="6">
-        <v>46245</v>
-      </c>
-      <c r="B255" s="5"/>
+        <v>46194</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C255" s="7">
-        <v>324900</v>
+        <v>595800</v>
       </c>
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A256" s="6">
-        <v>46246</v>
-      </c>
-      <c r="B256" s="5"/>
+        <v>46195</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C256" s="7">
-        <v>251100</v>
+        <v>387450</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A257" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B257" s="5"/>
+        <v>46196</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C257" s="7">
-        <v>251100</v>
+        <v>364050</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A258" s="6">
-        <v>46248</v>
-      </c>
-      <c r="B258" s="5"/>
+        <v>46197</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C258" s="7">
-        <v>185850</v>
+        <v>378900</v>
       </c>
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A259" s="6">
-        <v>46249</v>
-      </c>
-      <c r="B259" s="5"/>
+        <v>46198</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C259" s="7">
-        <v>242100</v>
+        <v>386550</v>
       </c>
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A260" s="6">
-        <v>46250</v>
-      </c>
-      <c r="B260" s="5"/>
+        <v>46199</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C260" s="7">
-        <v>177750</v>
+        <v>351900</v>
       </c>
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A261" s="6">
-        <v>46251</v>
-      </c>
-      <c r="B261" s="5"/>
+        <v>46200</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C261" s="7">
-        <v>192150</v>
+        <v>368100</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A262" s="6">
-        <v>46252</v>
-      </c>
-      <c r="B262" s="5"/>
+        <v>46201</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C262" s="7">
-        <v>265050</v>
+        <v>544500</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A263" s="6">
-        <v>46253</v>
-      </c>
-      <c r="B263" s="5"/>
+        <v>46202</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C263" s="7">
-        <v>297000</v>
+        <v>441900</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A264" s="6">
-        <v>46254</v>
-      </c>
-      <c r="B264" s="5"/>
+        <v>46203</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C264" s="7">
-        <v>405900</v>
+        <v>420300</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A265" s="6">
-        <v>46255</v>
-      </c>
-      <c r="B265" s="5"/>
+        <v>46204</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C265" s="7">
-        <v>290700</v>
+        <v>342000</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A266" s="6">
-        <v>46256</v>
-      </c>
-      <c r="B266" s="5"/>
+        <v>46205</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C266" s="7">
-        <v>309600</v>
+        <v>251550</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A267" s="6">
-        <v>46257</v>
-      </c>
-      <c r="B267" s="5"/>
+        <v>46206</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C267" s="7">
-        <v>243000</v>
+        <v>109800</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A268" s="6">
-        <v>46258</v>
-      </c>
-      <c r="B268" s="5"/>
+        <v>46207</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C268" s="7">
-        <v>261900</v>
+        <v>169650</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A269" s="6">
-        <v>46259</v>
-      </c>
-      <c r="B269" s="5"/>
+        <v>46208</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C269" s="7">
-        <v>306000</v>
+        <v>216000</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A270" s="6">
-        <v>46260</v>
-      </c>
-      <c r="B270" s="5"/>
+        <v>46209</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C270" s="7">
-        <v>286200</v>
+        <v>255600</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A271" s="6">
-        <v>46261</v>
-      </c>
-      <c r="B271" s="5"/>
+        <v>46210</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C271" s="7">
-        <v>224100</v>
+        <v>154800</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A272" s="6">
-        <v>46262</v>
-      </c>
-      <c r="B272" s="5"/>
+        <v>46211</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C272" s="7">
-        <v>256500</v>
+        <v>121050</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A273" s="6">
-        <v>46263</v>
-      </c>
-      <c r="B273" s="5"/>
+        <v>46212</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C273" s="7">
-        <v>211500</v>
+        <v>215100</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A274" s="6">
-        <v>46264</v>
-      </c>
-      <c r="B274" s="5"/>
+        <v>46213</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C274" s="7">
-        <v>338400</v>
+        <v>220050</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A275" s="6">
-        <v>46265</v>
-      </c>
-      <c r="B275" s="5"/>
+        <v>46214</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="C275" s="7">
-        <v>359100</v>
+        <v>215100</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A276" s="6"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="7"/>
+      <c r="A276" s="6">
+        <v>46215</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C276" s="7">
+        <v>169650</v>
+      </c>
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A277" s="6"/>
-      <c r="B277" s="5"/>
-      <c r="C277" s="7"/>
+      <c r="A277" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C277" s="7">
+        <v>193050</v>
+      </c>
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A278" s="6"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="7"/>
+      <c r="A278" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C278" s="7">
+        <v>468000</v>
+      </c>
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A279" s="6"/>
-      <c r="B279" s="5"/>
-      <c r="C279" s="7"/>
+      <c r="A279" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C279" s="7">
+        <v>306000</v>
+      </c>
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A280" s="6"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="7"/>
+      <c r="A280" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C280" s="7">
+        <v>263250</v>
+      </c>
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A281" s="6"/>
-      <c r="B281" s="5"/>
-      <c r="C281" s="7"/>
+      <c r="A281" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C281" s="7">
+        <v>296550</v>
+      </c>
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A282" s="6"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="7"/>
+      <c r="A282" s="6">
+        <v>46221</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C282" s="7">
+        <v>370800</v>
+      </c>
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A283" s="6"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="7"/>
+      <c r="A283" s="6">
+        <v>46222</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C283" s="7">
+        <v>379800</v>
+      </c>
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A284" s="6"/>
-      <c r="B284" s="5"/>
-      <c r="C284" s="7"/>
+      <c r="A284" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C284" s="7">
+        <v>497250</v>
+      </c>
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A285" s="6"/>
-      <c r="B285" s="5"/>
-      <c r="C285" s="7"/>
+      <c r="A285" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C285" s="7">
+        <v>344250</v>
+      </c>
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A286" s="6"/>
-      <c r="B286" s="5"/>
-      <c r="C286" s="7"/>
+      <c r="A286" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C286" s="7">
+        <v>327150</v>
+      </c>
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A287" s="6"/>
-      <c r="B287" s="5"/>
-      <c r="C287" s="7"/>
+      <c r="A287" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C287" s="7">
+        <v>421650</v>
+      </c>
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A288" s="6"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="7"/>
+      <c r="A288" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C288" s="7">
+        <v>373500</v>
+      </c>
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A289" s="6"/>
-      <c r="B289" s="5"/>
-      <c r="C289" s="7"/>
+      <c r="A289" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C289" s="7">
+        <v>490950</v>
+      </c>
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A290" s="6"/>
-      <c r="B290" s="5"/>
-      <c r="C290" s="7"/>
+      <c r="A290" s="6">
+        <v>46229</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C290" s="7">
+        <v>536400</v>
+      </c>
       <c r="D290" s="7"/>
       <c r="E290" s="5"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A291" s="6"/>
-      <c r="B291" s="5"/>
-      <c r="C291" s="7"/>
+      <c r="A291" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C291" s="7">
+        <v>297000</v>
+      </c>
       <c r="D291" s="7"/>
       <c r="E291" s="5"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A292" s="6"/>
-      <c r="B292" s="5"/>
-      <c r="C292" s="7"/>
+      <c r="A292" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C292" s="7">
+        <v>265050</v>
+      </c>
       <c r="D292" s="7"/>
       <c r="E292" s="5"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A293" s="6"/>
-      <c r="B293" s="5"/>
-      <c r="C293" s="7"/>
+      <c r="A293" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C293" s="7">
+        <v>365850</v>
+      </c>
       <c r="D293" s="7"/>
       <c r="E293" s="5"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A294" s="6"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="7"/>
+      <c r="A294" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C294" s="7">
+        <v>323100</v>
+      </c>
       <c r="D294" s="7"/>
       <c r="E294" s="5"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A295" s="6"/>
-      <c r="B295" s="5"/>
-      <c r="C295" s="7"/>
+      <c r="A295" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C295" s="7">
+        <v>428850</v>
+      </c>
       <c r="D295" s="7"/>
       <c r="E295" s="5"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A296" s="6"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="7"/>
+      <c r="A296" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C296" s="7">
+        <v>397350</v>
+      </c>
       <c r="D296" s="7"/>
       <c r="E296" s="5"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A297" s="6"/>
-      <c r="B297" s="5"/>
-      <c r="C297" s="7"/>
+      <c r="A297" s="6">
+        <v>46236</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C297" s="7">
+        <v>560700</v>
+      </c>
       <c r="D297" s="7"/>
       <c r="E297" s="5"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A298" s="6"/>
-      <c r="B298" s="5"/>
-      <c r="C298" s="7"/>
+      <c r="A298" s="6">
+        <v>46237</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C298" s="7">
+        <v>454950</v>
+      </c>
       <c r="D298" s="7"/>
       <c r="E298" s="5"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A299" s="6"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="7"/>
+      <c r="A299" s="6">
+        <v>46238</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C299" s="7">
+        <v>575100</v>
+      </c>
       <c r="D299" s="7"/>
       <c r="E299" s="5"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A300" s="6"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="7"/>
+      <c r="A300" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C300" s="7">
+        <v>382500</v>
+      </c>
       <c r="D300" s="7"/>
       <c r="E300" s="5"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A301" s="6"/>
-      <c r="B301" s="5"/>
-      <c r="C301" s="7"/>
+      <c r="A301" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C301" s="7">
+        <v>333450</v>
+      </c>
       <c r="D301" s="7"/>
       <c r="E301" s="5"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A302" s="6"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="7"/>
+      <c r="A302" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C302" s="7">
+        <v>360450</v>
+      </c>
       <c r="D302" s="7"/>
       <c r="E302" s="5"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A303" s="6"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="7"/>
+      <c r="A303" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C303" s="7">
+        <v>312750</v>
+      </c>
       <c r="D303" s="7"/>
       <c r="E303" s="5"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A304" s="6"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="7"/>
+      <c r="A304" s="6">
+        <v>46243</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C304" s="7">
+        <v>292050</v>
+      </c>
       <c r="D304" s="7"/>
       <c r="E304" s="5"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A305" s="6"/>
-      <c r="B305" s="5"/>
-      <c r="C305" s="7"/>
+      <c r="A305" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C305" s="7">
+        <v>250200</v>
+      </c>
       <c r="D305" s="7"/>
       <c r="E305" s="5"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A306" s="6"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="7"/>
+      <c r="A306" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C306" s="7">
+        <v>324900</v>
+      </c>
       <c r="D306" s="7"/>
       <c r="E306" s="5"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A307" s="6"/>
-      <c r="B307" s="5"/>
-      <c r="C307" s="7"/>
+      <c r="A307" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C307" s="7">
+        <v>251100</v>
+      </c>
       <c r="D307" s="7"/>
       <c r="E307" s="5"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A308" s="6"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="7"/>
+      <c r="A308" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C308" s="7">
+        <v>251100</v>
+      </c>
       <c r="D308" s="7"/>
       <c r="E308" s="5"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A309" s="6"/>
-      <c r="B309" s="5"/>
-      <c r="C309" s="7"/>
+      <c r="A309" s="6">
+        <v>46248</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C309" s="7">
+        <v>185850</v>
+      </c>
       <c r="D309" s="7"/>
       <c r="E309" s="5"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A310" s="6"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="7"/>
+      <c r="A310" s="6">
+        <v>46249</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C310" s="7">
+        <v>242100</v>
+      </c>
       <c r="D310" s="7"/>
       <c r="E310" s="5"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A311" s="6"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="7"/>
+      <c r="A311" s="6">
+        <v>46250</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C311" s="7">
+        <v>177750</v>
+      </c>
       <c r="D311" s="7"/>
       <c r="E311" s="5"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A312" s="6"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="7"/>
+      <c r="A312" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C312" s="7">
+        <v>192150</v>
+      </c>
       <c r="D312" s="7"/>
       <c r="E312" s="5"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A313" s="6"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="7"/>
+      <c r="A313" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C313" s="7">
+        <v>265050</v>
+      </c>
       <c r="D313" s="7"/>
       <c r="E313" s="5"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A314" s="6"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="7"/>
+      <c r="A314" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C314" s="7">
+        <v>297000</v>
+      </c>
       <c r="D314" s="7"/>
       <c r="E314" s="5"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A315" s="6"/>
-      <c r="B315" s="5"/>
-      <c r="C315" s="7"/>
+      <c r="A315" s="6">
+        <v>46254</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C315" s="7">
+        <v>405900</v>
+      </c>
       <c r="D315" s="7"/>
       <c r="E315" s="5"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A316" s="6"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="7"/>
+      <c r="A316" s="6">
+        <v>46255</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C316" s="7">
+        <v>290700</v>
+      </c>
       <c r="D316" s="7"/>
       <c r="E316" s="5"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A317" s="6"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="7"/>
+      <c r="A317" s="6">
+        <v>46256</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C317" s="7">
+        <v>309600</v>
+      </c>
       <c r="D317" s="7"/>
       <c r="E317" s="5"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A318" s="6"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="7"/>
+      <c r="A318" s="6">
+        <v>46257</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C318" s="7">
+        <v>243000</v>
+      </c>
       <c r="D318" s="7"/>
       <c r="E318" s="5"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A319" s="6"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="7"/>
+      <c r="A319" s="6">
+        <v>46258</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C319" s="7">
+        <v>261900</v>
+      </c>
       <c r="D319" s="7"/>
       <c r="E319" s="5"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A320" s="6"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="7"/>
+      <c r="A320" s="6">
+        <v>46259</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C320" s="7">
+        <v>306000</v>
+      </c>
       <c r="D320" s="7"/>
       <c r="E320" s="5"/>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A321" s="6"/>
-      <c r="B321" s="5"/>
-      <c r="C321" s="7"/>
+      <c r="A321" s="6">
+        <v>46260</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C321" s="7">
+        <v>286200</v>
+      </c>
       <c r="D321" s="7"/>
       <c r="E321" s="5"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A322" s="6"/>
-      <c r="B322" s="5"/>
-      <c r="C322" s="7"/>
+      <c r="A322" s="6">
+        <v>46261</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C322" s="7">
+        <v>224100</v>
+      </c>
       <c r="D322" s="7"/>
       <c r="E322" s="5"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A323" s="6"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="7"/>
+      <c r="A323" s="6">
+        <v>46262</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C323" s="7">
+        <v>256500</v>
+      </c>
       <c r="D323" s="7"/>
       <c r="E323" s="5"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A324" s="6"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="7"/>
+      <c r="A324" s="6">
+        <v>46263</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C324" s="7">
+        <v>211500</v>
+      </c>
       <c r="D324" s="7"/>
       <c r="E324" s="5"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A325" s="6"/>
-      <c r="B325" s="5"/>
-      <c r="C325" s="7"/>
+      <c r="A325" s="6">
+        <v>46264</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C325" s="7">
+        <v>338400</v>
+      </c>
       <c r="D325" s="7"/>
       <c r="E325" s="5"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A326" s="6"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="7"/>
+      <c r="A326" s="6">
+        <v>46265</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C326" s="7">
+        <v>359100</v>
+      </c>
       <c r="D326" s="7"/>
       <c r="E326" s="5"/>
     </row>
@@ -7638,6 +8268,363 @@
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
       <c r="E801" s="5"/>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A802" s="6"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="7"/>
+      <c r="D802" s="7"/>
+      <c r="E802" s="5"/>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A803" s="6"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="7"/>
+      <c r="D803" s="7"/>
+      <c r="E803" s="5"/>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A804" s="6"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="7"/>
+      <c r="D804" s="7"/>
+      <c r="E804" s="5"/>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A805" s="6"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="7"/>
+      <c r="D805" s="7"/>
+      <c r="E805" s="5"/>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A806" s="6"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="7"/>
+      <c r="D806" s="7"/>
+      <c r="E806" s="5"/>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A807" s="6"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="7"/>
+      <c r="D807" s="7"/>
+      <c r="E807" s="5"/>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A808" s="6"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="7"/>
+      <c r="D808" s="7"/>
+      <c r="E808" s="5"/>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A809" s="6"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="7"/>
+      <c r="D809" s="7"/>
+      <c r="E809" s="5"/>
+    </row>
+    <row r="810" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A810" s="6"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="7"/>
+      <c r="D810" s="7"/>
+      <c r="E810" s="5"/>
+    </row>
+    <row r="811" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A811" s="6"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="7"/>
+      <c r="D811" s="7"/>
+      <c r="E811" s="5"/>
+    </row>
+    <row r="812" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A812" s="6"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="7"/>
+      <c r="D812" s="7"/>
+      <c r="E812" s="5"/>
+    </row>
+    <row r="813" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A813" s="6"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="7"/>
+      <c r="D813" s="7"/>
+      <c r="E813" s="5"/>
+    </row>
+    <row r="814" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A814" s="6"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="7"/>
+      <c r="D814" s="7"/>
+      <c r="E814" s="5"/>
+    </row>
+    <row r="815" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A815" s="6"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="7"/>
+      <c r="D815" s="7"/>
+      <c r="E815" s="5"/>
+    </row>
+    <row r="816" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A816" s="6"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="7"/>
+      <c r="D816" s="7"/>
+      <c r="E816" s="5"/>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A817" s="6"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="7"/>
+      <c r="D817" s="7"/>
+      <c r="E817" s="5"/>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A818" s="6"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="7"/>
+      <c r="D818" s="7"/>
+      <c r="E818" s="5"/>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A819" s="6"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="7"/>
+      <c r="D819" s="7"/>
+      <c r="E819" s="5"/>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A820" s="6"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="7"/>
+      <c r="D820" s="7"/>
+      <c r="E820" s="5"/>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A821" s="6"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="7"/>
+      <c r="D821" s="7"/>
+      <c r="E821" s="5"/>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A822" s="6"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="7"/>
+      <c r="D822" s="7"/>
+      <c r="E822" s="5"/>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A823" s="6"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="7"/>
+      <c r="D823" s="7"/>
+      <c r="E823" s="5"/>
+    </row>
+    <row r="824" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A824" s="6"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="7"/>
+      <c r="D824" s="7"/>
+      <c r="E824" s="5"/>
+    </row>
+    <row r="825" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A825" s="6"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="7"/>
+      <c r="D825" s="7"/>
+      <c r="E825" s="5"/>
+    </row>
+    <row r="826" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A826" s="6"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="7"/>
+      <c r="D826" s="7"/>
+      <c r="E826" s="5"/>
+    </row>
+    <row r="827" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A827" s="6"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="7"/>
+      <c r="D827" s="7"/>
+      <c r="E827" s="5"/>
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A828" s="6"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="7"/>
+      <c r="D828" s="7"/>
+      <c r="E828" s="5"/>
+    </row>
+    <row r="829" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A829" s="6"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="7"/>
+      <c r="D829" s="7"/>
+      <c r="E829" s="5"/>
+    </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A830" s="6"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="7"/>
+      <c r="D830" s="7"/>
+      <c r="E830" s="5"/>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A831" s="6"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="7"/>
+      <c r="D831" s="7"/>
+      <c r="E831" s="5"/>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A832" s="6"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="7"/>
+      <c r="D832" s="7"/>
+      <c r="E832" s="5"/>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A833" s="6"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="7"/>
+      <c r="D833" s="7"/>
+      <c r="E833" s="5"/>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A834" s="6"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="7"/>
+      <c r="D834" s="7"/>
+      <c r="E834" s="5"/>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A835" s="6"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="7"/>
+      <c r="D835" s="7"/>
+      <c r="E835" s="5"/>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A836" s="6"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="7"/>
+      <c r="D836" s="7"/>
+      <c r="E836" s="5"/>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A837" s="6"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="7"/>
+      <c r="D837" s="7"/>
+      <c r="E837" s="5"/>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A838" s="6"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="7"/>
+      <c r="D838" s="7"/>
+      <c r="E838" s="5"/>
+    </row>
+    <row r="839" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A839" s="6"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="7"/>
+      <c r="D839" s="7"/>
+      <c r="E839" s="5"/>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A840" s="6"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="7"/>
+      <c r="D840" s="7"/>
+      <c r="E840" s="5"/>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A841" s="6"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="7"/>
+      <c r="D841" s="7"/>
+      <c r="E841" s="5"/>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A842" s="6"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="7"/>
+      <c r="D842" s="7"/>
+      <c r="E842" s="5"/>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A843" s="6"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="7"/>
+      <c r="D843" s="7"/>
+      <c r="E843" s="5"/>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A844" s="6"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="7"/>
+      <c r="D844" s="7"/>
+      <c r="E844" s="5"/>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A845" s="6"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="7"/>
+      <c r="D845" s="7"/>
+      <c r="E845" s="5"/>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A846" s="6"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="7"/>
+      <c r="D846" s="7"/>
+      <c r="E846" s="5"/>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A847" s="6"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="7"/>
+      <c r="D847" s="7"/>
+      <c r="E847" s="5"/>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A848" s="6"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="7"/>
+      <c r="D848" s="7"/>
+      <c r="E848" s="5"/>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A849" s="6"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="7"/>
+      <c r="D849" s="7"/>
+      <c r="E849" s="5"/>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A850" s="6"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="7"/>
+      <c r="D850" s="7"/>
+      <c r="E850" s="5"/>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A851" s="6"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="7"/>
+      <c r="D851" s="7"/>
+      <c r="E851" s="5"/>
+    </row>
+    <row r="852" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A852" s="6"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="7"/>
+      <c r="D852" s="7"/>
+      <c r="E852" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
@@ -7649,7 +8636,7 @@
           <x14:formula1>
             <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B801</xm:sqref>
+          <xm:sqref>B2:B852</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$290</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -204,20 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -225,7 +211,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,9 +249,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,40 +309,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,7 +325,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -311,30 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,6 +398,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -398,7 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,97 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +494,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,6 +587,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -597,6 +612,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,37 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5268,9 +5268,20 @@
         <v>330750</v>
       </c>
     </row>
+    <row r="291" spans="1:3">
+      <c r="A291" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B291" t="s">
+        <v>39</v>
+      </c>
+      <c r="C291">
+        <v>271350</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E289">
-    <sortState ref="A1:E289">
+  <autoFilter ref="A1:E290">
+    <sortState ref="A1:E290">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$292</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,21 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -234,7 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,67 +227,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,18 +240,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,6 +274,74 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,11 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -599,7 +605,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,30 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -668,22 +650,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5290,9 +5290,20 @@
         <v>248850</v>
       </c>
     </row>
+    <row r="293" spans="1:3">
+      <c r="A293" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B293" t="s">
+        <v>39</v>
+      </c>
+      <c r="C293">
+        <v>250200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E291">
-    <sortState ref="A1:E291">
+  <autoFilter ref="A1:E292">
+    <sortState ref="A1:E292">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$293</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -203,6 +203,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,11 +218,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,8 +271,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,30 +281,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,47 +297,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,17 +324,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +452,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,45 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -621,21 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +606,60 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5301,9 +5301,20 @@
         <v>250200</v>
       </c>
     </row>
+    <row r="294" spans="1:3">
+      <c r="A294" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B294" t="s">
+        <v>39</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E292">
-    <sortState ref="A1:E292">
+  <autoFilter ref="A1:E293">
+    <sortState ref="A1:E293">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$294</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -205,39 +205,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,55 +234,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,8 +248,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,8 +302,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,63 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,15 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -620,199 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5312,9 +5312,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="295" spans="1:3">
+      <c r="A295" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B295" t="s">
+        <v>39</v>
+      </c>
+      <c r="C295">
+        <v>458100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E293">
-    <sortState ref="A1:E293">
+  <autoFilter ref="A1:E294">
+    <sortState ref="A1:E294">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$295</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,30 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,6 +210,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -250,9 +227,54 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,8 +286,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,33 +301,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,15 +323,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,16 +333,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +446,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,109 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,8 +603,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,32 +640,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -668,151 +653,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5309,7 +5309,7 @@
         <v>39</v>
       </c>
       <c r="C294">
-        <v>0</v>
+        <v>268650</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -5323,9 +5323,20 @@
         <v>458100</v>
       </c>
     </row>
+    <row r="296" spans="1:3">
+      <c r="A296" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B296" t="s">
+        <v>39</v>
+      </c>
+      <c r="C296">
+        <v>271800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E294">
-    <sortState ref="A1:E294">
+  <autoFilter ref="A1:E295">
+    <sortState ref="A1:E295">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$296</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,45 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,8 +255,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,47 +301,26 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,61 +332,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +392,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,43 +458,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,44 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -620,6 +582,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,6 +627,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E296"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5334,9 +5334,20 @@
         <v>271800</v>
       </c>
     </row>
+    <row r="297" spans="1:3">
+      <c r="A297" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B297" t="s">
+        <v>39</v>
+      </c>
+      <c r="C297">
+        <v>190800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E295">
-    <sortState ref="A1:E295">
+  <autoFilter ref="A1:E296">
+    <sortState ref="A1:E296">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$297</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,17 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,20 +226,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -248,8 +233,31 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,16 +271,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,21 +297,6 @@
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,26 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,28 +586,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,20 +619,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,151 +657,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E298"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5345,9 +5345,20 @@
         <v>190800</v>
       </c>
     </row>
+    <row r="298" spans="1:3">
+      <c r="A298" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B298" t="s">
+        <v>39</v>
+      </c>
+      <c r="C298">
+        <v>239400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E296">
-    <sortState ref="A1:E296">
+  <autoFilter ref="A1:E297">
+    <sortState ref="A1:E297">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$298</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,23 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,25 +226,18 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,6 +265,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -286,39 +280,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,9 +311,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +322,28 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,85 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,20 +595,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,36 +620,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -668,151 +644,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5356,9 +5356,20 @@
         <v>239400</v>
       </c>
     </row>
+    <row r="299" spans="1:3">
+      <c r="A299" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B299" t="s">
+        <v>39</v>
+      </c>
+      <c r="C299">
+        <v>215550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E297">
-    <sortState ref="A1:E297">
+  <autoFilter ref="A1:E298">
+    <sortState ref="A1:E298">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$298</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$299</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,11 +203,33 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,6 +240,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,16 +309,24 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,93 +340,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,175 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,56 +596,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -668,151 +618,201 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5367,9 +5367,20 @@
         <v>215550</v>
       </c>
     </row>
+    <row r="300" spans="1:3">
+      <c r="A300" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B300" t="s">
+        <v>39</v>
+      </c>
+      <c r="C300">
+        <v>295650</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E298">
-    <sortState ref="A1:E298">
+  <autoFilter ref="A1:E299">
+    <sortState ref="A1:E299">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$300</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,47 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,10 +257,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -233,24 +294,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,14 +311,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,6 +324,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -294,54 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +464,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,41 +645,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,164 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5378,9 +5378,20 @@
         <v>295650</v>
       </c>
     </row>
+    <row r="301" spans="1:3">
+      <c r="A301" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B301" t="s">
+        <v>39</v>
+      </c>
+      <c r="C301">
+        <v>262800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E299">
-    <sortState ref="A1:E299">
+  <autoFilter ref="A1:E300">
+    <sortState ref="A1:E300">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$301</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,7 +203,13 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -212,7 +218,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,44 +257,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,8 +285,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,48 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +386,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,67 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,25 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,41 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -621,6 +586,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -632,6 +606,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +645,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E302"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5389,9 +5389,20 @@
         <v>262800</v>
       </c>
     </row>
+    <row r="302" spans="1:3">
+      <c r="A302" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B302" t="s">
+        <v>39</v>
+      </c>
+      <c r="C302">
+        <v>324450</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E300">
-    <sortState ref="A1:E300">
+  <autoFilter ref="A1:E301">
+    <sortState ref="A1:E301">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$302</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,60 +226,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,22 +255,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -309,7 +263,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,6 +292,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -332,8 +309,24 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,9 +334,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +434,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,145 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,15 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -612,11 +603,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,21 +615,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +638,33 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5400,9 +5400,20 @@
         <v>324450</v>
       </c>
     </row>
+    <row r="303" spans="1:3">
+      <c r="A303" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B303" t="s">
+        <v>39</v>
+      </c>
+      <c r="C303">
+        <v>227250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E301">
-    <sortState ref="A1:E301">
+  <autoFilter ref="A1:E302">
+    <sortState ref="A1:E302">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$303</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,17 +232,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,16 +264,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,8 +286,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -284,19 +315,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,39 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,121 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,6 +488,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -530,19 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -601,11 +619,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,30 +660,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5411,9 +5411,20 @@
         <v>227250</v>
       </c>
     </row>
+    <row r="304" spans="1:3">
+      <c r="A304" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B304" t="s">
+        <v>39</v>
+      </c>
+      <c r="C304">
+        <v>259200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E302">
-    <sortState ref="A1:E302">
+  <autoFilter ref="A1:E303">
+    <sortState ref="A1:E303">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$304</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,9 +210,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,6 +220,21 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,25 +255,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,51 +294,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,6 +308,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -340,8 +325,23 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +416,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -590,31 +614,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5422,9 +5422,17 @@
         <v>259200</v>
       </c>
     </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B305" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E303">
-    <sortState ref="A1:E303">
+  <autoFilter ref="A1:E304">
+    <sortState ref="A1:E304">
       <sortCondition ref="A2:A852"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40B268F-44D8-4B11-9532-B618C48B431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,9 +18,20 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$305</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -162,15 +179,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,171 +196,38 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,194 +240,8 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -570,264 +264,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -839,61 +291,17 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1178,317 +586,315 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:1">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="9"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="9"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -1496,7 +902,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -1513,7 +919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>45992</v>
       </c>
@@ -1526,7 +932,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>45993</v>
       </c>
@@ -1539,7 +945,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>45994</v>
       </c>
@@ -1552,7 +958,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>45995</v>
       </c>
@@ -1565,7 +971,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>45996</v>
       </c>
@@ -1578,7 +984,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>45997</v>
       </c>
@@ -1591,7 +997,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>45998</v>
       </c>
@@ -1604,7 +1010,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>45999</v>
       </c>
@@ -1617,7 +1023,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>46000</v>
       </c>
@@ -1630,7 +1036,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>46001</v>
       </c>
@@ -1643,7 +1049,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>46002</v>
       </c>
@@ -1656,7 +1062,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>46003</v>
       </c>
@@ -1669,7 +1075,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>46004</v>
       </c>
@@ -1682,7 +1088,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>46005</v>
       </c>
@@ -1695,7 +1101,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>46006</v>
       </c>
@@ -1708,7 +1114,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>46007</v>
       </c>
@@ -1721,7 +1127,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>46008</v>
       </c>
@@ -1734,7 +1140,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>46009</v>
       </c>
@@ -1747,7 +1153,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>46010</v>
       </c>
@@ -1760,7 +1166,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>46011</v>
       </c>
@@ -1773,7 +1179,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>46012</v>
       </c>
@@ -1786,7 +1192,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>46013</v>
       </c>
@@ -1799,7 +1205,7 @@
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>46014</v>
       </c>
@@ -1812,7 +1218,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>46015</v>
       </c>
@@ -1825,7 +1231,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>46016</v>
       </c>
@@ -1838,7 +1244,7 @@
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>46017</v>
       </c>
@@ -1851,7 +1257,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>46018</v>
       </c>
@@ -1864,7 +1270,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>46019</v>
       </c>
@@ -1877,7 +1283,7 @@
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>46020</v>
       </c>
@@ -1890,7 +1296,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>46021</v>
       </c>
@@ -1903,7 +1309,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>46022</v>
       </c>
@@ -1916,7 +1322,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="4">
         <v>46023</v>
       </c>
@@ -1929,7 +1335,7 @@
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="4">
         <v>46024</v>
       </c>
@@ -1942,7 +1348,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>46025</v>
       </c>
@@ -1955,7 +1361,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>46026</v>
       </c>
@@ -1968,7 +1374,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>46027</v>
       </c>
@@ -1981,7 +1387,7 @@
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>46028</v>
       </c>
@@ -1994,7 +1400,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>46029</v>
       </c>
@@ -2007,7 +1413,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>46030</v>
       </c>
@@ -2020,7 +1426,7 @@
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>46031</v>
       </c>
@@ -2033,7 +1439,7 @@
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>46032</v>
       </c>
@@ -2046,7 +1452,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
         <v>46033</v>
       </c>
@@ -2059,7 +1465,7 @@
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>46034</v>
       </c>
@@ -2072,7 +1478,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
         <v>46035</v>
       </c>
@@ -2085,7 +1491,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
         <v>46036</v>
       </c>
@@ -2098,7 +1504,7 @@
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
         <v>46037</v>
       </c>
@@ -2111,7 +1517,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>46038</v>
       </c>
@@ -2124,7 +1530,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
         <v>46039</v>
       </c>
@@ -2137,7 +1543,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
         <v>46040</v>
       </c>
@@ -2150,7 +1556,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>46041</v>
       </c>
@@ -2163,7 +1569,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
         <v>46042</v>
       </c>
@@ -2176,7 +1582,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
         <v>46043</v>
       </c>
@@ -2189,7 +1595,7 @@
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
         <v>46044</v>
       </c>
@@ -2202,7 +1608,7 @@
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
         <v>46045</v>
       </c>
@@ -2215,7 +1621,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>46046</v>
       </c>
@@ -2228,7 +1634,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
         <v>46047</v>
       </c>
@@ -2241,7 +1647,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>46048</v>
       </c>
@@ -2254,7 +1660,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
         <v>46049</v>
       </c>
@@ -2267,7 +1673,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>46050</v>
       </c>
@@ -2280,7 +1686,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
         <v>46051</v>
       </c>
@@ -2293,7 +1699,7 @@
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
         <v>46052</v>
       </c>
@@ -2306,7 +1712,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
         <v>46053</v>
       </c>
@@ -2319,7 +1725,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>46054</v>
       </c>
@@ -2332,7 +1738,7 @@
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
         <v>46055</v>
       </c>
@@ -2345,7 +1751,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="4">
         <v>46056</v>
       </c>
@@ -2358,7 +1764,7 @@
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="4">
         <v>46057</v>
       </c>
@@ -2371,7 +1777,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="4">
         <v>46058</v>
       </c>
@@ -2384,7 +1790,7 @@
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="4">
         <v>46059</v>
       </c>
@@ -2397,7 +1803,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="4">
         <v>46060</v>
       </c>
@@ -2410,7 +1816,7 @@
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="4">
         <v>46061</v>
       </c>
@@ -2423,7 +1829,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="4">
         <v>46062</v>
       </c>
@@ -2436,7 +1842,7 @@
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="4">
         <v>46063</v>
       </c>
@@ -2449,7 +1855,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="4">
         <v>46064</v>
       </c>
@@ -2462,7 +1868,7 @@
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="4">
         <v>46065</v>
       </c>
@@ -2475,7 +1881,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="4">
         <v>46066</v>
       </c>
@@ -2488,7 +1894,7 @@
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="4">
         <v>46067</v>
       </c>
@@ -2501,7 +1907,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="4">
         <v>46068</v>
       </c>
@@ -2514,7 +1920,7 @@
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="4">
         <v>46069</v>
       </c>
@@ -2527,7 +1933,7 @@
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="4">
         <v>46070</v>
       </c>
@@ -2540,7 +1946,7 @@
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A81" s="4">
         <v>46071</v>
       </c>
@@ -2553,7 +1959,7 @@
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="4">
         <v>46072</v>
       </c>
@@ -2566,7 +1972,7 @@
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="4">
         <v>46073</v>
       </c>
@@ -2579,7 +1985,7 @@
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="4">
         <v>46074</v>
       </c>
@@ -2592,7 +1998,7 @@
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="4">
         <v>46075</v>
       </c>
@@ -2605,7 +2011,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="4">
         <v>46076</v>
       </c>
@@ -2618,7 +2024,7 @@
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="4">
         <v>46077</v>
       </c>
@@ -2631,7 +2037,7 @@
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="4">
         <v>46078</v>
       </c>
@@ -2644,7 +2050,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="4">
         <v>46079</v>
       </c>
@@ -2657,7 +2063,7 @@
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="4">
         <v>46080</v>
       </c>
@@ -2670,7 +2076,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="4">
         <v>46081</v>
       </c>
@@ -2683,7 +2089,7 @@
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="4">
         <v>46082</v>
       </c>
@@ -2696,7 +2102,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="4">
         <v>46083</v>
       </c>
@@ -2709,7 +2115,7 @@
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="4">
         <v>46084</v>
       </c>
@@ -2722,7 +2128,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>46085</v>
       </c>
@@ -2735,7 +2141,7 @@
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="4">
         <v>46086</v>
       </c>
@@ -2748,7 +2154,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="4">
         <v>46087</v>
       </c>
@@ -2761,7 +2167,7 @@
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="4">
         <v>46088</v>
       </c>
@@ -2774,7 +2180,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="4">
         <v>46089</v>
       </c>
@@ -2787,7 +2193,7 @@
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
         <v>46090</v>
       </c>
@@ -2800,7 +2206,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="4">
         <v>46091</v>
       </c>
@@ -2813,7 +2219,7 @@
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="4">
         <v>46092</v>
       </c>
@@ -2826,7 +2232,7 @@
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="4">
         <v>46093</v>
       </c>
@@ -2839,7 +2245,7 @@
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="4">
         <v>46094</v>
       </c>
@@ -2852,7 +2258,7 @@
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="4">
         <v>46095</v>
       </c>
@@ -2865,7 +2271,7 @@
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="4">
         <v>46096</v>
       </c>
@@ -2878,7 +2284,7 @@
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="4">
         <v>46097</v>
       </c>
@@ -2891,7 +2297,7 @@
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="4">
         <v>46098</v>
       </c>
@@ -2904,7 +2310,7 @@
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="4">
         <v>46099</v>
       </c>
@@ -2917,7 +2323,7 @@
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="4">
         <v>46100</v>
       </c>
@@ -2930,7 +2336,7 @@
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="4">
         <v>46101</v>
       </c>
@@ -2943,7 +2349,7 @@
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="4">
         <v>46102</v>
       </c>
@@ -2956,7 +2362,7 @@
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="4">
         <v>46103</v>
       </c>
@@ -2969,7 +2375,7 @@
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="4">
         <v>46104</v>
       </c>
@@ -2982,7 +2388,7 @@
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="4">
         <v>46105</v>
       </c>
@@ -2995,7 +2401,7 @@
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="4">
         <v>46106</v>
       </c>
@@ -3008,7 +2414,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="4">
         <v>46107</v>
       </c>
@@ -3021,7 +2427,7 @@
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="4">
         <v>46108</v>
       </c>
@@ -3034,7 +2440,7 @@
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="4">
         <v>46109</v>
       </c>
@@ -3047,7 +2453,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="4">
         <v>46110</v>
       </c>
@@ -3060,7 +2466,7 @@
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="4">
         <v>46111</v>
       </c>
@@ -3073,7 +2479,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="4">
         <v>46112</v>
       </c>
@@ -3086,7 +2492,7 @@
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="4">
         <v>46113</v>
       </c>
@@ -3099,7 +2505,7 @@
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A124" s="4">
         <v>46114</v>
       </c>
@@ -3112,7 +2518,7 @@
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A125" s="4">
         <v>46115</v>
       </c>
@@ -3125,7 +2531,7 @@
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="4">
         <v>46116</v>
       </c>
@@ -3138,7 +2544,7 @@
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="4">
         <v>46117</v>
       </c>
@@ -3151,7 +2557,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="4">
         <v>46118</v>
       </c>
@@ -3164,7 +2570,7 @@
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A129" s="4">
         <v>46119</v>
       </c>
@@ -3177,7 +2583,7 @@
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="4">
         <v>46120</v>
       </c>
@@ -3190,7 +2596,7 @@
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="4">
         <v>46121</v>
       </c>
@@ -3203,7 +2609,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="4">
         <v>46122</v>
       </c>
@@ -3216,7 +2622,7 @@
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="4">
         <v>46123</v>
       </c>
@@ -3229,7 +2635,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="4">
         <v>46124</v>
       </c>
@@ -3242,7 +2648,7 @@
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="4">
         <v>46125</v>
       </c>
@@ -3255,7 +2661,7 @@
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="4">
         <v>46126</v>
       </c>
@@ -3268,7 +2674,7 @@
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="4">
         <v>46127</v>
       </c>
@@ -3281,7 +2687,7 @@
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="4">
         <v>46128</v>
       </c>
@@ -3294,7 +2700,7 @@
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="4">
         <v>46129</v>
       </c>
@@ -3307,7 +2713,7 @@
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="4">
         <v>46130</v>
       </c>
@@ -3320,7 +2726,7 @@
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="4">
         <v>46131</v>
       </c>
@@ -3333,7 +2739,7 @@
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="4">
         <v>46132</v>
       </c>
@@ -3346,7 +2752,7 @@
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="4">
         <v>46133</v>
       </c>
@@ -3359,7 +2765,7 @@
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A144" s="4">
         <v>46134</v>
       </c>
@@ -3372,7 +2778,7 @@
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A145" s="4">
         <v>46135</v>
       </c>
@@ -3385,7 +2791,7 @@
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="4">
         <v>46136</v>
       </c>
@@ -3398,7 +2804,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="4">
         <v>46137</v>
       </c>
@@ -3411,7 +2817,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="4">
         <v>46138</v>
       </c>
@@ -3424,7 +2830,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="4">
         <v>46139</v>
       </c>
@@ -3437,7 +2843,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A150" s="4">
         <v>46140</v>
       </c>
@@ -3450,7 +2856,7 @@
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A151" s="4">
         <v>46141</v>
       </c>
@@ -3463,7 +2869,7 @@
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A152" s="4">
         <v>46142</v>
       </c>
@@ -3476,7 +2882,7 @@
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A153" s="4">
         <v>46143</v>
       </c>
@@ -3489,7 +2895,7 @@
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A154" s="4">
         <v>46144</v>
       </c>
@@ -3502,7 +2908,7 @@
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A155" s="4">
         <v>46145</v>
       </c>
@@ -3515,7 +2921,7 @@
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A156" s="4">
         <v>46146</v>
       </c>
@@ -3528,7 +2934,7 @@
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A157" s="4">
         <v>46147</v>
       </c>
@@ -3541,7 +2947,7 @@
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A158" s="4">
         <v>46148</v>
       </c>
@@ -3554,7 +2960,7 @@
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A159" s="4">
         <v>46149</v>
       </c>
@@ -3567,7 +2973,7 @@
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A160" s="4">
         <v>46150</v>
       </c>
@@ -3580,7 +2986,7 @@
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A161" s="4">
         <v>46151</v>
       </c>
@@ -3593,7 +2999,7 @@
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A162" s="4">
         <v>46152</v>
       </c>
@@ -3606,7 +3012,7 @@
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A163" s="4">
         <v>46153</v>
       </c>
@@ -3619,7 +3025,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A164" s="4">
         <v>46154</v>
       </c>
@@ -3632,7 +3038,7 @@
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A165" s="4">
         <v>46155</v>
       </c>
@@ -3645,7 +3051,7 @@
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A166" s="4">
         <v>46156</v>
       </c>
@@ -3658,7 +3064,7 @@
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A167" s="4">
         <v>46157</v>
       </c>
@@ -3671,7 +3077,7 @@
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A168" s="4">
         <v>46158</v>
       </c>
@@ -3684,7 +3090,7 @@
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A169" s="4">
         <v>46159</v>
       </c>
@@ -3697,7 +3103,7 @@
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A170" s="4">
         <v>46160</v>
       </c>
@@ -3710,7 +3116,7 @@
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A171" s="4">
         <v>46161</v>
       </c>
@@ -3723,7 +3129,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A172" s="4">
         <v>46162</v>
       </c>
@@ -3736,7 +3142,7 @@
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A173" s="4">
         <v>46163</v>
       </c>
@@ -3749,7 +3155,7 @@
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A174" s="4">
         <v>46164</v>
       </c>
@@ -3762,7 +3168,7 @@
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A175" s="4">
         <v>46165</v>
       </c>
@@ -3775,7 +3181,7 @@
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A176" s="4">
         <v>46166</v>
       </c>
@@ -3788,7 +3194,7 @@
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A177" s="4">
         <v>46167</v>
       </c>
@@ -3801,7 +3207,7 @@
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A178" s="4">
         <v>46168</v>
       </c>
@@ -3814,7 +3220,7 @@
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A179" s="4">
         <v>46169</v>
       </c>
@@ -3827,7 +3233,7 @@
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A180" s="4">
         <v>46170</v>
       </c>
@@ -3840,7 +3246,7 @@
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A181" s="4">
         <v>46171</v>
       </c>
@@ -3853,7 +3259,7 @@
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A182" s="4">
         <v>46172</v>
       </c>
@@ -3866,7 +3272,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A183" s="4">
         <v>46173</v>
       </c>
@@ -3879,7 +3285,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A184" s="4">
         <v>46174</v>
       </c>
@@ -3892,7 +3298,7 @@
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A185" s="4">
         <v>46175</v>
       </c>
@@ -3905,7 +3311,7 @@
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A186" s="4">
         <v>46176</v>
       </c>
@@ -3918,7 +3324,7 @@
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A187" s="4">
         <v>46177</v>
       </c>
@@ -3931,7 +3337,7 @@
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A188" s="4">
         <v>46178</v>
       </c>
@@ -3944,7 +3350,7 @@
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A189" s="4">
         <v>46179</v>
       </c>
@@ -3957,7 +3363,7 @@
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A190" s="4">
         <v>46180</v>
       </c>
@@ -3970,7 +3376,7 @@
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A191" s="4">
         <v>46181</v>
       </c>
@@ -3983,7 +3389,7 @@
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A192" s="4">
         <v>46182</v>
       </c>
@@ -3996,7 +3402,7 @@
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="4">
         <v>46183</v>
       </c>
@@ -4009,7 +3415,7 @@
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="4">
         <v>46184</v>
       </c>
@@ -4022,7 +3428,7 @@
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="4">
         <v>46185</v>
       </c>
@@ -4035,7 +3441,7 @@
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="4">
         <v>46186</v>
       </c>
@@ -4048,7 +3454,7 @@
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="4">
         <v>46187</v>
       </c>
@@ -4061,7 +3467,7 @@
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="4">
         <v>46188</v>
       </c>
@@ -4074,7 +3480,7 @@
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="4">
         <v>46189</v>
       </c>
@@ -4087,7 +3493,7 @@
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="4">
         <v>46190</v>
       </c>
@@ -4100,7 +3506,7 @@
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="4">
         <v>46191</v>
       </c>
@@ -4113,7 +3519,7 @@
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A202" s="4">
         <v>46192</v>
       </c>
@@ -4126,7 +3532,7 @@
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A203" s="4">
         <v>46193</v>
       </c>
@@ -4139,7 +3545,7 @@
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A204" s="4">
         <v>46194</v>
       </c>
@@ -4152,7 +3558,7 @@
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A205" s="4">
         <v>46195</v>
       </c>
@@ -4165,7 +3571,7 @@
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A206" s="4">
         <v>46196</v>
       </c>
@@ -4178,7 +3584,7 @@
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A207" s="4">
         <v>46197</v>
       </c>
@@ -4191,7 +3597,7 @@
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A208" s="4">
         <v>46198</v>
       </c>
@@ -4204,7 +3610,7 @@
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A209" s="4">
         <v>46199</v>
       </c>
@@ -4217,7 +3623,7 @@
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A210" s="4">
         <v>46200</v>
       </c>
@@ -4230,7 +3636,7 @@
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A211" s="4">
         <v>46201</v>
       </c>
@@ -4243,7 +3649,7 @@
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A212" s="4">
         <v>46202</v>
       </c>
@@ -4256,7 +3662,7 @@
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A213" s="4">
         <v>46203</v>
       </c>
@@ -4269,7 +3675,7 @@
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A214" s="4">
         <v>46204</v>
       </c>
@@ -4282,7 +3688,7 @@
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A215" s="4">
         <v>46205</v>
       </c>
@@ -4295,7 +3701,7 @@
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A216" s="4">
         <v>46206</v>
       </c>
@@ -4308,7 +3714,7 @@
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A217" s="4">
         <v>46207</v>
       </c>
@@ -4321,7 +3727,7 @@
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A218" s="4">
         <v>46208</v>
       </c>
@@ -4334,7 +3740,7 @@
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A219" s="4">
         <v>46209</v>
       </c>
@@ -4347,7 +3753,7 @@
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A220" s="4">
         <v>46210</v>
       </c>
@@ -4360,7 +3766,7 @@
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A221" s="4">
         <v>46211</v>
       </c>
@@ -4373,7 +3779,7 @@
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A222" s="4">
         <v>46212</v>
       </c>
@@ -4386,7 +3792,7 @@
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A223" s="4">
         <v>46213</v>
       </c>
@@ -4399,7 +3805,7 @@
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A224" s="4">
         <v>46214</v>
       </c>
@@ -4412,7 +3818,7 @@
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A225" s="4">
         <v>46215</v>
       </c>
@@ -4425,7 +3831,7 @@
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A226" s="4">
         <v>46216</v>
       </c>
@@ -4438,7 +3844,7 @@
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A227" s="4">
         <v>46217</v>
       </c>
@@ -4451,7 +3857,7 @@
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A228" s="4">
         <v>46218</v>
       </c>
@@ -4464,7 +3870,7 @@
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A229" s="4">
         <v>46219</v>
       </c>
@@ -4477,7 +3883,7 @@
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A230" s="4">
         <v>46220</v>
       </c>
@@ -4490,7 +3896,7 @@
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A231" s="4">
         <v>46221</v>
       </c>
@@ -4503,7 +3909,7 @@
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A232" s="4">
         <v>46222</v>
       </c>
@@ -4516,7 +3922,7 @@
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A233" s="4">
         <v>46223</v>
       </c>
@@ -4529,7 +3935,7 @@
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A234" s="4">
         <v>46224</v>
       </c>
@@ -4542,7 +3948,7 @@
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A235" s="4">
         <v>46225</v>
       </c>
@@ -4555,7 +3961,7 @@
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A236" s="4">
         <v>46226</v>
       </c>
@@ -4568,7 +3974,7 @@
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A237" s="4">
         <v>46227</v>
       </c>
@@ -4581,7 +3987,7 @@
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A238" s="4">
         <v>46228</v>
       </c>
@@ -4594,7 +4000,7 @@
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A239" s="4">
         <v>46229</v>
       </c>
@@ -4607,7 +4013,7 @@
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A240" s="4">
         <v>46230</v>
       </c>
@@ -4620,7 +4026,7 @@
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A241" s="4">
         <v>46231</v>
       </c>
@@ -4633,7 +4039,7 @@
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A242" s="4">
         <v>46232</v>
       </c>
@@ -4646,7 +4052,7 @@
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A243" s="4">
         <v>46233</v>
       </c>
@@ -4659,7 +4065,7 @@
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A244" s="4">
         <v>46234</v>
       </c>
@@ -4672,7 +4078,7 @@
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A245" s="4">
         <v>46235</v>
       </c>
@@ -4685,7 +4091,7 @@
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A246" s="4">
         <v>46236</v>
       </c>
@@ -4698,7 +4104,7 @@
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A247" s="4">
         <v>46237</v>
       </c>
@@ -4711,7 +4117,7 @@
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A248" s="4">
         <v>46238</v>
       </c>
@@ -4724,7 +4130,7 @@
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A249" s="4">
         <v>46239</v>
       </c>
@@ -4737,7 +4143,7 @@
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A250" s="4">
         <v>46240</v>
       </c>
@@ -4750,7 +4156,7 @@
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A251" s="4">
         <v>46241</v>
       </c>
@@ -4763,7 +4169,7 @@
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A252" s="4">
         <v>46242</v>
       </c>
@@ -4776,7 +4182,7 @@
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A253" s="4">
         <v>46243</v>
       </c>
@@ -4789,7 +4195,7 @@
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A254" s="4">
         <v>46244</v>
       </c>
@@ -4802,7 +4208,7 @@
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A255" s="4">
         <v>46245</v>
       </c>
@@ -4815,7 +4221,7 @@
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A256" s="4">
         <v>46246</v>
       </c>
@@ -4828,7 +4234,7 @@
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A257" s="4">
         <v>46247</v>
       </c>
@@ -4841,7 +4247,7 @@
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A258" s="4">
         <v>46248</v>
       </c>
@@ -4854,7 +4260,7 @@
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A259" s="4">
         <v>46249</v>
       </c>
@@ -4867,7 +4273,7 @@
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A260" s="4">
         <v>46250</v>
       </c>
@@ -4880,7 +4286,7 @@
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A261" s="4">
         <v>46251</v>
       </c>
@@ -4893,7 +4299,7 @@
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A262" s="4">
         <v>46252</v>
       </c>
@@ -4906,7 +4312,7 @@
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A263" s="4">
         <v>46253</v>
       </c>
@@ -4919,7 +4325,7 @@
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A264" s="4">
         <v>46254</v>
       </c>
@@ -4932,7 +4338,7 @@
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A265" s="4">
         <v>46255</v>
       </c>
@@ -4945,7 +4351,7 @@
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A266" s="4">
         <v>46256</v>
       </c>
@@ -4958,7 +4364,7 @@
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A267" s="4">
         <v>46257</v>
       </c>
@@ -4971,7 +4377,7 @@
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A268" s="4">
         <v>46258</v>
       </c>
@@ -4984,7 +4390,7 @@
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A269" s="4">
         <v>46259</v>
       </c>
@@ -4997,7 +4403,7 @@
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A270" s="4">
         <v>46260</v>
       </c>
@@ -5010,7 +4416,7 @@
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A271" s="4">
         <v>46261</v>
       </c>
@@ -5023,7 +4429,7 @@
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A272" s="4">
         <v>46262</v>
       </c>
@@ -5036,7 +4442,7 @@
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A273" s="4">
         <v>46263</v>
       </c>
@@ -5049,7 +4455,7 @@
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A274" s="4">
         <v>46264</v>
       </c>
@@ -5062,7 +4468,7 @@
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A275" s="4">
         <v>46265</v>
       </c>
@@ -5075,7 +4481,7 @@
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A276" s="4">
         <v>46266</v>
       </c>
@@ -5088,7 +4494,7 @@
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A277" s="4">
         <v>46267</v>
       </c>
@@ -5101,7 +4507,7 @@
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A278" s="4">
         <v>46268</v>
       </c>
@@ -5114,7 +4520,7 @@
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A279" s="4">
         <v>46269</v>
       </c>
@@ -5127,7 +4533,7 @@
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A280" s="4">
         <v>46270</v>
       </c>
@@ -5140,7 +4546,7 @@
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A281" s="4">
         <v>46271</v>
       </c>
@@ -5153,7 +4559,7 @@
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A282" s="4">
         <v>46272</v>
       </c>
@@ -5166,7 +4572,7 @@
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A283" s="4">
         <v>46273</v>
       </c>
@@ -5179,7 +4585,7 @@
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A284" s="4">
         <v>46274</v>
       </c>
@@ -5192,7 +4598,7 @@
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A285" s="4">
         <v>46275</v>
       </c>
@@ -5205,7 +4611,7 @@
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A286" s="4">
         <v>46276</v>
       </c>
@@ -5218,7 +4624,7 @@
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A287" s="4">
         <v>46277</v>
       </c>
@@ -5231,7 +4637,7 @@
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A288" s="4">
         <v>46278</v>
       </c>
@@ -5244,7 +4650,7 @@
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A289" s="4">
         <v>46279</v>
       </c>
@@ -5257,7 +4663,7 @@
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>46280</v>
       </c>
@@ -5268,7 +4674,7 @@
         <v>330750</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>46281</v>
       </c>
@@ -5279,7 +4685,7 @@
         <v>271350</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>46282</v>
       </c>
@@ -5290,7 +4696,7 @@
         <v>248850</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>46283</v>
       </c>
@@ -5301,7 +4707,7 @@
         <v>250200</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>46284</v>
       </c>
@@ -5312,7 +4718,7 @@
         <v>268650</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>46285</v>
       </c>
@@ -5323,7 +4729,7 @@
         <v>458100</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>46286</v>
       </c>
@@ -5334,7 +4740,7 @@
         <v>271800</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>46287</v>
       </c>
@@ -5345,7 +4751,7 @@
         <v>190800</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>46288</v>
       </c>
@@ -5356,7 +4762,7 @@
         <v>239400</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>46289</v>
       </c>
@@ -5367,7 +4773,7 @@
         <v>215550</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>46290</v>
       </c>
@@ -5378,7 +4784,7 @@
         <v>295650</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>46291</v>
       </c>
@@ -5389,7 +4795,7 @@
         <v>262800</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>46292</v>
       </c>
@@ -5400,7 +4806,7 @@
         <v>324450</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>46293</v>
       </c>
@@ -5411,7 +4817,7 @@
         <v>227250</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>46294</v>
       </c>
@@ -5422,27 +4828,32 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>46295</v>
       </c>
       <c r="B305" t="s">
         <v>39</v>
       </c>
+      <c r="C305">
+        <v>241650</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E304">
-    <sortState ref="A1:E304">
-      <sortCondition ref="A2:A852"/>
-    </sortState>
-    <extLst/>
-  </autoFilter>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B289">
-      <formula1>店舗マスタ!$A$2:$A$31</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:E305" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B289</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40B268F-44D8-4B11-9532-B618C48B431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -20,23 +14,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$305</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -179,11 +162,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,38 +183,171 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,8 +360,194 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -264,20 +570,262 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -291,17 +839,61 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -586,315 +1178,317 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="1" ht="17.25" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="9"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="9"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E306"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -902,7 +1496,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -919,7 +1513,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="4">
         <v>45992</v>
       </c>
@@ -932,7 +1526,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="4">
         <v>45993</v>
       </c>
@@ -945,7 +1539,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="4">
         <v>45994</v>
       </c>
@@ -958,7 +1552,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5">
       <c r="A5" s="4">
         <v>45995</v>
       </c>
@@ -971,7 +1565,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5">
       <c r="A6" s="4">
         <v>45996</v>
       </c>
@@ -984,7 +1578,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="4">
         <v>45997</v>
       </c>
@@ -997,7 +1591,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5">
       <c r="A8" s="4">
         <v>45998</v>
       </c>
@@ -1010,7 +1604,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5">
       <c r="A9" s="4">
         <v>45999</v>
       </c>
@@ -1023,7 +1617,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5">
       <c r="A10" s="4">
         <v>46000</v>
       </c>
@@ -1036,7 +1630,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5">
       <c r="A11" s="4">
         <v>46001</v>
       </c>
@@ -1049,7 +1643,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5">
       <c r="A12" s="4">
         <v>46002</v>
       </c>
@@ -1062,7 +1656,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5">
       <c r="A13" s="4">
         <v>46003</v>
       </c>
@@ -1075,7 +1669,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5">
       <c r="A14" s="4">
         <v>46004</v>
       </c>
@@ -1088,7 +1682,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5">
       <c r="A15" s="4">
         <v>46005</v>
       </c>
@@ -1101,7 +1695,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5">
       <c r="A16" s="4">
         <v>46006</v>
       </c>
@@ -1114,7 +1708,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5">
       <c r="A17" s="4">
         <v>46007</v>
       </c>
@@ -1127,7 +1721,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5">
       <c r="A18" s="4">
         <v>46008</v>
       </c>
@@ -1140,7 +1734,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5">
       <c r="A19" s="4">
         <v>46009</v>
       </c>
@@ -1153,7 +1747,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5">
       <c r="A20" s="4">
         <v>46010</v>
       </c>
@@ -1166,7 +1760,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5">
       <c r="A21" s="4">
         <v>46011</v>
       </c>
@@ -1179,7 +1773,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5">
       <c r="A22" s="4">
         <v>46012</v>
       </c>
@@ -1192,7 +1786,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5">
       <c r="A23" s="4">
         <v>46013</v>
       </c>
@@ -1205,7 +1799,7 @@
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5">
       <c r="A24" s="4">
         <v>46014</v>
       </c>
@@ -1218,7 +1812,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5">
       <c r="A25" s="4">
         <v>46015</v>
       </c>
@@ -1231,7 +1825,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5">
       <c r="A26" s="4">
         <v>46016</v>
       </c>
@@ -1244,7 +1838,7 @@
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5">
       <c r="A27" s="4">
         <v>46017</v>
       </c>
@@ -1257,7 +1851,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5">
       <c r="A28" s="4">
         <v>46018</v>
       </c>
@@ -1270,7 +1864,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5">
       <c r="A29" s="4">
         <v>46019</v>
       </c>
@@ -1283,7 +1877,7 @@
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5">
       <c r="A30" s="4">
         <v>46020</v>
       </c>
@@ -1296,7 +1890,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5">
       <c r="A31" s="4">
         <v>46021</v>
       </c>
@@ -1309,7 +1903,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5">
       <c r="A32" s="4">
         <v>46022</v>
       </c>
@@ -1322,7 +1916,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5">
       <c r="A33" s="4">
         <v>46023</v>
       </c>
@@ -1335,7 +1929,7 @@
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5">
       <c r="A34" s="4">
         <v>46024</v>
       </c>
@@ -1348,7 +1942,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5">
       <c r="A35" s="4">
         <v>46025</v>
       </c>
@@ -1361,7 +1955,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5">
       <c r="A36" s="4">
         <v>46026</v>
       </c>
@@ -1374,7 +1968,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5">
       <c r="A37" s="4">
         <v>46027</v>
       </c>
@@ -1387,7 +1981,7 @@
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5">
       <c r="A38" s="4">
         <v>46028</v>
       </c>
@@ -1400,7 +1994,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5">
       <c r="A39" s="4">
         <v>46029</v>
       </c>
@@ -1413,7 +2007,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5">
       <c r="A40" s="4">
         <v>46030</v>
       </c>
@@ -1426,7 +2020,7 @@
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5">
       <c r="A41" s="4">
         <v>46031</v>
       </c>
@@ -1439,7 +2033,7 @@
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5">
       <c r="A42" s="4">
         <v>46032</v>
       </c>
@@ -1452,7 +2046,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5">
       <c r="A43" s="4">
         <v>46033</v>
       </c>
@@ -1465,7 +2059,7 @@
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5">
       <c r="A44" s="4">
         <v>46034</v>
       </c>
@@ -1478,7 +2072,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5">
       <c r="A45" s="4">
         <v>46035</v>
       </c>
@@ -1491,7 +2085,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5">
       <c r="A46" s="4">
         <v>46036</v>
       </c>
@@ -1504,7 +2098,7 @@
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5">
       <c r="A47" s="4">
         <v>46037</v>
       </c>
@@ -1517,7 +2111,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5">
       <c r="A48" s="4">
         <v>46038</v>
       </c>
@@ -1530,7 +2124,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5">
       <c r="A49" s="4">
         <v>46039</v>
       </c>
@@ -1543,7 +2137,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5">
       <c r="A50" s="4">
         <v>46040</v>
       </c>
@@ -1556,7 +2150,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5">
       <c r="A51" s="4">
         <v>46041</v>
       </c>
@@ -1569,7 +2163,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5">
       <c r="A52" s="4">
         <v>46042</v>
       </c>
@@ -1582,7 +2176,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5">
       <c r="A53" s="4">
         <v>46043</v>
       </c>
@@ -1595,7 +2189,7 @@
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5">
       <c r="A54" s="4">
         <v>46044</v>
       </c>
@@ -1608,7 +2202,7 @@
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5">
       <c r="A55" s="4">
         <v>46045</v>
       </c>
@@ -1621,7 +2215,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5">
       <c r="A56" s="4">
         <v>46046</v>
       </c>
@@ -1634,7 +2228,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5">
       <c r="A57" s="4">
         <v>46047</v>
       </c>
@@ -1647,7 +2241,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5">
       <c r="A58" s="4">
         <v>46048</v>
       </c>
@@ -1660,7 +2254,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5">
       <c r="A59" s="4">
         <v>46049</v>
       </c>
@@ -1673,7 +2267,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5">
       <c r="A60" s="4">
         <v>46050</v>
       </c>
@@ -1686,7 +2280,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5">
       <c r="A61" s="4">
         <v>46051</v>
       </c>
@@ -1699,7 +2293,7 @@
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5">
       <c r="A62" s="4">
         <v>46052</v>
       </c>
@@ -1712,7 +2306,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5">
       <c r="A63" s="4">
         <v>46053</v>
       </c>
@@ -1725,7 +2319,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5">
       <c r="A64" s="4">
         <v>46054</v>
       </c>
@@ -1738,7 +2332,7 @@
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5">
       <c r="A65" s="4">
         <v>46055</v>
       </c>
@@ -1751,7 +2345,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5">
       <c r="A66" s="4">
         <v>46056</v>
       </c>
@@ -1764,7 +2358,7 @@
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5">
       <c r="A67" s="4">
         <v>46057</v>
       </c>
@@ -1777,7 +2371,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:5">
       <c r="A68" s="4">
         <v>46058</v>
       </c>
@@ -1790,7 +2384,7 @@
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:5">
       <c r="A69" s="4">
         <v>46059</v>
       </c>
@@ -1803,7 +2397,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:5">
       <c r="A70" s="4">
         <v>46060</v>
       </c>
@@ -1816,7 +2410,7 @@
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:5">
       <c r="A71" s="4">
         <v>46061</v>
       </c>
@@ -1829,7 +2423,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:5">
       <c r="A72" s="4">
         <v>46062</v>
       </c>
@@ -1842,7 +2436,7 @@
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:5">
       <c r="A73" s="4">
         <v>46063</v>
       </c>
@@ -1855,7 +2449,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:5">
       <c r="A74" s="4">
         <v>46064</v>
       </c>
@@ -1868,7 +2462,7 @@
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:5">
       <c r="A75" s="4">
         <v>46065</v>
       </c>
@@ -1881,7 +2475,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:5">
       <c r="A76" s="4">
         <v>46066</v>
       </c>
@@ -1894,7 +2488,7 @@
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:5">
       <c r="A77" s="4">
         <v>46067</v>
       </c>
@@ -1907,7 +2501,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:5">
       <c r="A78" s="4">
         <v>46068</v>
       </c>
@@ -1920,7 +2514,7 @@
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:5">
       <c r="A79" s="4">
         <v>46069</v>
       </c>
@@ -1933,7 +2527,7 @@
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:5">
       <c r="A80" s="4">
         <v>46070</v>
       </c>
@@ -1946,7 +2540,7 @@
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:5">
       <c r="A81" s="4">
         <v>46071</v>
       </c>
@@ -1959,7 +2553,7 @@
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:5">
       <c r="A82" s="4">
         <v>46072</v>
       </c>
@@ -1972,7 +2566,7 @@
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:5">
       <c r="A83" s="4">
         <v>46073</v>
       </c>
@@ -1985,7 +2579,7 @@
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:5">
       <c r="A84" s="4">
         <v>46074</v>
       </c>
@@ -1998,7 +2592,7 @@
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:5">
       <c r="A85" s="4">
         <v>46075</v>
       </c>
@@ -2011,7 +2605,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:5">
       <c r="A86" s="4">
         <v>46076</v>
       </c>
@@ -2024,7 +2618,7 @@
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5">
       <c r="A87" s="4">
         <v>46077</v>
       </c>
@@ -2037,7 +2631,7 @@
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:5">
       <c r="A88" s="4">
         <v>46078</v>
       </c>
@@ -2050,7 +2644,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:5">
       <c r="A89" s="4">
         <v>46079</v>
       </c>
@@ -2063,7 +2657,7 @@
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:5">
       <c r="A90" s="4">
         <v>46080</v>
       </c>
@@ -2076,7 +2670,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:5">
       <c r="A91" s="4">
         <v>46081</v>
       </c>
@@ -2089,7 +2683,7 @@
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:5">
       <c r="A92" s="4">
         <v>46082</v>
       </c>
@@ -2102,7 +2696,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:5">
       <c r="A93" s="4">
         <v>46083</v>
       </c>
@@ -2115,7 +2709,7 @@
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5">
       <c r="A94" s="4">
         <v>46084</v>
       </c>
@@ -2128,7 +2722,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:5">
       <c r="A95" s="4">
         <v>46085</v>
       </c>
@@ -2141,7 +2735,7 @@
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:5">
       <c r="A96" s="4">
         <v>46086</v>
       </c>
@@ -2154,7 +2748,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:5">
       <c r="A97" s="4">
         <v>46087</v>
       </c>
@@ -2167,7 +2761,7 @@
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:5">
       <c r="A98" s="4">
         <v>46088</v>
       </c>
@@ -2180,7 +2774,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:5">
       <c r="A99" s="4">
         <v>46089</v>
       </c>
@@ -2193,7 +2787,7 @@
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:5">
       <c r="A100" s="4">
         <v>46090</v>
       </c>
@@ -2206,7 +2800,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:5">
       <c r="A101" s="4">
         <v>46091</v>
       </c>
@@ -2219,7 +2813,7 @@
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:5">
       <c r="A102" s="4">
         <v>46092</v>
       </c>
@@ -2232,7 +2826,7 @@
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:5">
       <c r="A103" s="4">
         <v>46093</v>
       </c>
@@ -2245,7 +2839,7 @@
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:5">
       <c r="A104" s="4">
         <v>46094</v>
       </c>
@@ -2258,7 +2852,7 @@
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:5">
       <c r="A105" s="4">
         <v>46095</v>
       </c>
@@ -2271,7 +2865,7 @@
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:5">
       <c r="A106" s="4">
         <v>46096</v>
       </c>
@@ -2284,7 +2878,7 @@
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:5">
       <c r="A107" s="4">
         <v>46097</v>
       </c>
@@ -2297,7 +2891,7 @@
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:5">
       <c r="A108" s="4">
         <v>46098</v>
       </c>
@@ -2310,7 +2904,7 @@
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:5">
       <c r="A109" s="4">
         <v>46099</v>
       </c>
@@ -2323,7 +2917,7 @@
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:5">
       <c r="A110" s="4">
         <v>46100</v>
       </c>
@@ -2336,7 +2930,7 @@
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:5">
       <c r="A111" s="4">
         <v>46101</v>
       </c>
@@ -2349,7 +2943,7 @@
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:5">
       <c r="A112" s="4">
         <v>46102</v>
       </c>
@@ -2362,7 +2956,7 @@
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:5">
       <c r="A113" s="4">
         <v>46103</v>
       </c>
@@ -2375,7 +2969,7 @@
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:5">
       <c r="A114" s="4">
         <v>46104</v>
       </c>
@@ -2388,7 +2982,7 @@
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:5">
       <c r="A115" s="4">
         <v>46105</v>
       </c>
@@ -2401,7 +2995,7 @@
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:5">
       <c r="A116" s="4">
         <v>46106</v>
       </c>
@@ -2414,7 +3008,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:5">
       <c r="A117" s="4">
         <v>46107</v>
       </c>
@@ -2427,7 +3021,7 @@
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:5">
       <c r="A118" s="4">
         <v>46108</v>
       </c>
@@ -2440,7 +3034,7 @@
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:5">
       <c r="A119" s="4">
         <v>46109</v>
       </c>
@@ -2453,7 +3047,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:5">
       <c r="A120" s="4">
         <v>46110</v>
       </c>
@@ -2466,7 +3060,7 @@
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:5">
       <c r="A121" s="4">
         <v>46111</v>
       </c>
@@ -2479,7 +3073,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:5">
       <c r="A122" s="4">
         <v>46112</v>
       </c>
@@ -2492,7 +3086,7 @@
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:5">
       <c r="A123" s="4">
         <v>46113</v>
       </c>
@@ -2505,7 +3099,7 @@
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:5">
       <c r="A124" s="4">
         <v>46114</v>
       </c>
@@ -2518,7 +3112,7 @@
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:5">
       <c r="A125" s="4">
         <v>46115</v>
       </c>
@@ -2531,7 +3125,7 @@
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:5">
       <c r="A126" s="4">
         <v>46116</v>
       </c>
@@ -2544,7 +3138,7 @@
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:5">
       <c r="A127" s="4">
         <v>46117</v>
       </c>
@@ -2557,7 +3151,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:5">
       <c r="A128" s="4">
         <v>46118</v>
       </c>
@@ -2570,7 +3164,7 @@
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:5">
       <c r="A129" s="4">
         <v>46119</v>
       </c>
@@ -2583,7 +3177,7 @@
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:5">
       <c r="A130" s="4">
         <v>46120</v>
       </c>
@@ -2596,7 +3190,7 @@
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:5">
       <c r="A131" s="4">
         <v>46121</v>
       </c>
@@ -2609,7 +3203,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:5">
       <c r="A132" s="4">
         <v>46122</v>
       </c>
@@ -2622,7 +3216,7 @@
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:5">
       <c r="A133" s="4">
         <v>46123</v>
       </c>
@@ -2635,7 +3229,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:5">
       <c r="A134" s="4">
         <v>46124</v>
       </c>
@@ -2648,7 +3242,7 @@
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:5">
       <c r="A135" s="4">
         <v>46125</v>
       </c>
@@ -2661,7 +3255,7 @@
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:5">
       <c r="A136" s="4">
         <v>46126</v>
       </c>
@@ -2674,7 +3268,7 @@
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:5">
       <c r="A137" s="4">
         <v>46127</v>
       </c>
@@ -2687,7 +3281,7 @@
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:5">
       <c r="A138" s="4">
         <v>46128</v>
       </c>
@@ -2700,7 +3294,7 @@
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:5">
       <c r="A139" s="4">
         <v>46129</v>
       </c>
@@ -2713,7 +3307,7 @@
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:5">
       <c r="A140" s="4">
         <v>46130</v>
       </c>
@@ -2726,7 +3320,7 @@
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:5">
       <c r="A141" s="4">
         <v>46131</v>
       </c>
@@ -2739,7 +3333,7 @@
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:5">
       <c r="A142" s="4">
         <v>46132</v>
       </c>
@@ -2752,7 +3346,7 @@
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:5">
       <c r="A143" s="4">
         <v>46133</v>
       </c>
@@ -2765,7 +3359,7 @@
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:5">
       <c r="A144" s="4">
         <v>46134</v>
       </c>
@@ -2778,7 +3372,7 @@
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:5">
       <c r="A145" s="4">
         <v>46135</v>
       </c>
@@ -2791,7 +3385,7 @@
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:5">
       <c r="A146" s="4">
         <v>46136</v>
       </c>
@@ -2804,7 +3398,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:5">
       <c r="A147" s="4">
         <v>46137</v>
       </c>
@@ -2817,7 +3411,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:5">
       <c r="A148" s="4">
         <v>46138</v>
       </c>
@@ -2830,7 +3424,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:5">
       <c r="A149" s="4">
         <v>46139</v>
       </c>
@@ -2843,7 +3437,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:5">
       <c r="A150" s="4">
         <v>46140</v>
       </c>
@@ -2856,7 +3450,7 @@
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:5">
       <c r="A151" s="4">
         <v>46141</v>
       </c>
@@ -2869,7 +3463,7 @@
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:5">
       <c r="A152" s="4">
         <v>46142</v>
       </c>
@@ -2882,7 +3476,7 @@
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:5">
       <c r="A153" s="4">
         <v>46143</v>
       </c>
@@ -2895,7 +3489,7 @@
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:5">
       <c r="A154" s="4">
         <v>46144</v>
       </c>
@@ -2908,7 +3502,7 @@
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:5">
       <c r="A155" s="4">
         <v>46145</v>
       </c>
@@ -2921,7 +3515,7 @@
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:5">
       <c r="A156" s="4">
         <v>46146</v>
       </c>
@@ -2934,7 +3528,7 @@
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:5">
       <c r="A157" s="4">
         <v>46147</v>
       </c>
@@ -2947,7 +3541,7 @@
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:5">
       <c r="A158" s="4">
         <v>46148</v>
       </c>
@@ -2960,7 +3554,7 @@
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:5">
       <c r="A159" s="4">
         <v>46149</v>
       </c>
@@ -2973,7 +3567,7 @@
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:5">
       <c r="A160" s="4">
         <v>46150</v>
       </c>
@@ -2986,7 +3580,7 @@
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:5">
       <c r="A161" s="4">
         <v>46151</v>
       </c>
@@ -2999,7 +3593,7 @@
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:5">
       <c r="A162" s="4">
         <v>46152</v>
       </c>
@@ -3012,7 +3606,7 @@
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:5">
       <c r="A163" s="4">
         <v>46153</v>
       </c>
@@ -3025,7 +3619,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:5">
       <c r="A164" s="4">
         <v>46154</v>
       </c>
@@ -3038,7 +3632,7 @@
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:5">
       <c r="A165" s="4">
         <v>46155</v>
       </c>
@@ -3051,7 +3645,7 @@
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:5">
       <c r="A166" s="4">
         <v>46156</v>
       </c>
@@ -3064,7 +3658,7 @@
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:5">
       <c r="A167" s="4">
         <v>46157</v>
       </c>
@@ -3077,7 +3671,7 @@
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:5">
       <c r="A168" s="4">
         <v>46158</v>
       </c>
@@ -3090,7 +3684,7 @@
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:5">
       <c r="A169" s="4">
         <v>46159</v>
       </c>
@@ -3103,7 +3697,7 @@
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:5">
       <c r="A170" s="4">
         <v>46160</v>
       </c>
@@ -3116,7 +3710,7 @@
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:5">
       <c r="A171" s="4">
         <v>46161</v>
       </c>
@@ -3129,7 +3723,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:5">
       <c r="A172" s="4">
         <v>46162</v>
       </c>
@@ -3142,7 +3736,7 @@
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:5">
       <c r="A173" s="4">
         <v>46163</v>
       </c>
@@ -3155,7 +3749,7 @@
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:5">
       <c r="A174" s="4">
         <v>46164</v>
       </c>
@@ -3168,7 +3762,7 @@
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:5">
       <c r="A175" s="4">
         <v>46165</v>
       </c>
@@ -3181,7 +3775,7 @@
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:5">
       <c r="A176" s="4">
         <v>46166</v>
       </c>
@@ -3194,7 +3788,7 @@
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:5">
       <c r="A177" s="4">
         <v>46167</v>
       </c>
@@ -3207,7 +3801,7 @@
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:5">
       <c r="A178" s="4">
         <v>46168</v>
       </c>
@@ -3220,7 +3814,7 @@
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:5">
       <c r="A179" s="4">
         <v>46169</v>
       </c>
@@ -3233,7 +3827,7 @@
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:5">
       <c r="A180" s="4">
         <v>46170</v>
       </c>
@@ -3246,7 +3840,7 @@
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:5">
       <c r="A181" s="4">
         <v>46171</v>
       </c>
@@ -3259,7 +3853,7 @@
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:5">
       <c r="A182" s="4">
         <v>46172</v>
       </c>
@@ -3272,7 +3866,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:5">
       <c r="A183" s="4">
         <v>46173</v>
       </c>
@@ -3285,7 +3879,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:5">
       <c r="A184" s="4">
         <v>46174</v>
       </c>
@@ -3298,7 +3892,7 @@
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:5">
       <c r="A185" s="4">
         <v>46175</v>
       </c>
@@ -3311,7 +3905,7 @@
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:5">
       <c r="A186" s="4">
         <v>46176</v>
       </c>
@@ -3324,7 +3918,7 @@
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:5">
       <c r="A187" s="4">
         <v>46177</v>
       </c>
@@ -3337,7 +3931,7 @@
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:5">
       <c r="A188" s="4">
         <v>46178</v>
       </c>
@@ -3350,7 +3944,7 @@
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:5">
       <c r="A189" s="4">
         <v>46179</v>
       </c>
@@ -3363,7 +3957,7 @@
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:5">
       <c r="A190" s="4">
         <v>46180</v>
       </c>
@@ -3376,7 +3970,7 @@
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:5">
       <c r="A191" s="4">
         <v>46181</v>
       </c>
@@ -3389,7 +3983,7 @@
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:5">
       <c r="A192" s="4">
         <v>46182</v>
       </c>
@@ -3402,7 +3996,7 @@
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:5">
       <c r="A193" s="4">
         <v>46183</v>
       </c>
@@ -3415,7 +4009,7 @@
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:5">
       <c r="A194" s="4">
         <v>46184</v>
       </c>
@@ -3428,7 +4022,7 @@
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:5">
       <c r="A195" s="4">
         <v>46185</v>
       </c>
@@ -3441,7 +4035,7 @@
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:5">
       <c r="A196" s="4">
         <v>46186</v>
       </c>
@@ -3454,7 +4048,7 @@
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:5">
       <c r="A197" s="4">
         <v>46187</v>
       </c>
@@ -3467,7 +4061,7 @@
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:5">
       <c r="A198" s="4">
         <v>46188</v>
       </c>
@@ -3480,7 +4074,7 @@
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:5">
       <c r="A199" s="4">
         <v>46189</v>
       </c>
@@ -3493,7 +4087,7 @@
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:5">
       <c r="A200" s="4">
         <v>46190</v>
       </c>
@@ -3506,7 +4100,7 @@
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:5">
       <c r="A201" s="4">
         <v>46191</v>
       </c>
@@ -3519,7 +4113,7 @@
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:5">
       <c r="A202" s="4">
         <v>46192</v>
       </c>
@@ -3532,7 +4126,7 @@
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:5">
       <c r="A203" s="4">
         <v>46193</v>
       </c>
@@ -3545,7 +4139,7 @@
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:5">
       <c r="A204" s="4">
         <v>46194</v>
       </c>
@@ -3558,7 +4152,7 @@
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:5">
       <c r="A205" s="4">
         <v>46195</v>
       </c>
@@ -3571,7 +4165,7 @@
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:5">
       <c r="A206" s="4">
         <v>46196</v>
       </c>
@@ -3584,7 +4178,7 @@
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:5">
       <c r="A207" s="4">
         <v>46197</v>
       </c>
@@ -3597,7 +4191,7 @@
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:5">
       <c r="A208" s="4">
         <v>46198</v>
       </c>
@@ -3610,7 +4204,7 @@
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:5">
       <c r="A209" s="4">
         <v>46199</v>
       </c>
@@ -3623,7 +4217,7 @@
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:5">
       <c r="A210" s="4">
         <v>46200</v>
       </c>
@@ -3636,7 +4230,7 @@
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:5">
       <c r="A211" s="4">
         <v>46201</v>
       </c>
@@ -3649,7 +4243,7 @@
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:5">
       <c r="A212" s="4">
         <v>46202</v>
       </c>
@@ -3662,7 +4256,7 @@
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:5">
       <c r="A213" s="4">
         <v>46203</v>
       </c>
@@ -3675,7 +4269,7 @@
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:5">
       <c r="A214" s="4">
         <v>46204</v>
       </c>
@@ -3688,7 +4282,7 @@
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:5">
       <c r="A215" s="4">
         <v>46205</v>
       </c>
@@ -3701,7 +4295,7 @@
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:5">
       <c r="A216" s="4">
         <v>46206</v>
       </c>
@@ -3714,7 +4308,7 @@
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:5">
       <c r="A217" s="4">
         <v>46207</v>
       </c>
@@ -3727,7 +4321,7 @@
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:5">
       <c r="A218" s="4">
         <v>46208</v>
       </c>
@@ -3740,7 +4334,7 @@
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:5">
       <c r="A219" s="4">
         <v>46209</v>
       </c>
@@ -3753,7 +4347,7 @@
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:5">
       <c r="A220" s="4">
         <v>46210</v>
       </c>
@@ -3766,7 +4360,7 @@
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:5">
       <c r="A221" s="4">
         <v>46211</v>
       </c>
@@ -3779,7 +4373,7 @@
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:5">
       <c r="A222" s="4">
         <v>46212</v>
       </c>
@@ -3792,7 +4386,7 @@
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:5">
       <c r="A223" s="4">
         <v>46213</v>
       </c>
@@ -3805,7 +4399,7 @@
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:5">
       <c r="A224" s="4">
         <v>46214</v>
       </c>
@@ -3818,7 +4412,7 @@
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:5">
       <c r="A225" s="4">
         <v>46215</v>
       </c>
@@ -3831,7 +4425,7 @@
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:5">
       <c r="A226" s="4">
         <v>46216</v>
       </c>
@@ -3844,7 +4438,7 @@
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:5">
       <c r="A227" s="4">
         <v>46217</v>
       </c>
@@ -3857,7 +4451,7 @@
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:5">
       <c r="A228" s="4">
         <v>46218</v>
       </c>
@@ -3870,7 +4464,7 @@
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:5">
       <c r="A229" s="4">
         <v>46219</v>
       </c>
@@ -3883,7 +4477,7 @@
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:5">
       <c r="A230" s="4">
         <v>46220</v>
       </c>
@@ -3896,7 +4490,7 @@
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:5">
       <c r="A231" s="4">
         <v>46221</v>
       </c>
@@ -3909,7 +4503,7 @@
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:5">
       <c r="A232" s="4">
         <v>46222</v>
       </c>
@@ -3922,7 +4516,7 @@
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:5">
       <c r="A233" s="4">
         <v>46223</v>
       </c>
@@ -3935,7 +4529,7 @@
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:5">
       <c r="A234" s="4">
         <v>46224</v>
       </c>
@@ -3948,7 +4542,7 @@
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:5">
       <c r="A235" s="4">
         <v>46225</v>
       </c>
@@ -3961,7 +4555,7 @@
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:5">
       <c r="A236" s="4">
         <v>46226</v>
       </c>
@@ -3974,7 +4568,7 @@
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:5">
       <c r="A237" s="4">
         <v>46227</v>
       </c>
@@ -3987,7 +4581,7 @@
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:5">
       <c r="A238" s="4">
         <v>46228</v>
       </c>
@@ -4000,7 +4594,7 @@
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:5">
       <c r="A239" s="4">
         <v>46229</v>
       </c>
@@ -4013,7 +4607,7 @@
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:5">
       <c r="A240" s="4">
         <v>46230</v>
       </c>
@@ -4026,7 +4620,7 @@
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:5">
       <c r="A241" s="4">
         <v>46231</v>
       </c>
@@ -4039,7 +4633,7 @@
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:5">
       <c r="A242" s="4">
         <v>46232</v>
       </c>
@@ -4052,7 +4646,7 @@
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:5">
       <c r="A243" s="4">
         <v>46233</v>
       </c>
@@ -4065,7 +4659,7 @@
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:5">
       <c r="A244" s="4">
         <v>46234</v>
       </c>
@@ -4078,7 +4672,7 @@
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:5">
       <c r="A245" s="4">
         <v>46235</v>
       </c>
@@ -4091,7 +4685,7 @@
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:5">
       <c r="A246" s="4">
         <v>46236</v>
       </c>
@@ -4104,7 +4698,7 @@
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:5">
       <c r="A247" s="4">
         <v>46237</v>
       </c>
@@ -4117,7 +4711,7 @@
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:5">
       <c r="A248" s="4">
         <v>46238</v>
       </c>
@@ -4130,7 +4724,7 @@
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:5">
       <c r="A249" s="4">
         <v>46239</v>
       </c>
@@ -4143,7 +4737,7 @@
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:5">
       <c r="A250" s="4">
         <v>46240</v>
       </c>
@@ -4156,7 +4750,7 @@
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:5">
       <c r="A251" s="4">
         <v>46241</v>
       </c>
@@ -4169,7 +4763,7 @@
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:5">
       <c r="A252" s="4">
         <v>46242</v>
       </c>
@@ -4182,7 +4776,7 @@
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:5">
       <c r="A253" s="4">
         <v>46243</v>
       </c>
@@ -4195,7 +4789,7 @@
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:5">
       <c r="A254" s="4">
         <v>46244</v>
       </c>
@@ -4208,7 +4802,7 @@
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:5">
       <c r="A255" s="4">
         <v>46245</v>
       </c>
@@ -4221,7 +4815,7 @@
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:5">
       <c r="A256" s="4">
         <v>46246</v>
       </c>
@@ -4234,7 +4828,7 @@
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:5">
       <c r="A257" s="4">
         <v>46247</v>
       </c>
@@ -4247,7 +4841,7 @@
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:5">
       <c r="A258" s="4">
         <v>46248</v>
       </c>
@@ -4260,7 +4854,7 @@
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:5">
       <c r="A259" s="4">
         <v>46249</v>
       </c>
@@ -4273,7 +4867,7 @@
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:5">
       <c r="A260" s="4">
         <v>46250</v>
       </c>
@@ -4286,7 +4880,7 @@
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:5">
       <c r="A261" s="4">
         <v>46251</v>
       </c>
@@ -4299,7 +4893,7 @@
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:5">
       <c r="A262" s="4">
         <v>46252</v>
       </c>
@@ -4312,7 +4906,7 @@
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:5">
       <c r="A263" s="4">
         <v>46253</v>
       </c>
@@ -4325,7 +4919,7 @@
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:5">
       <c r="A264" s="4">
         <v>46254</v>
       </c>
@@ -4338,7 +4932,7 @@
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:5">
       <c r="A265" s="4">
         <v>46255</v>
       </c>
@@ -4351,7 +4945,7 @@
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:5">
       <c r="A266" s="4">
         <v>46256</v>
       </c>
@@ -4364,7 +4958,7 @@
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:5">
       <c r="A267" s="4">
         <v>46257</v>
       </c>
@@ -4377,7 +4971,7 @@
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:5">
       <c r="A268" s="4">
         <v>46258</v>
       </c>
@@ -4390,7 +4984,7 @@
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:5">
       <c r="A269" s="4">
         <v>46259</v>
       </c>
@@ -4403,7 +4997,7 @@
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:5">
       <c r="A270" s="4">
         <v>46260</v>
       </c>
@@ -4416,7 +5010,7 @@
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:5">
       <c r="A271" s="4">
         <v>46261</v>
       </c>
@@ -4429,7 +5023,7 @@
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:5">
       <c r="A272" s="4">
         <v>46262</v>
       </c>
@@ -4442,7 +5036,7 @@
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:5">
       <c r="A273" s="4">
         <v>46263</v>
       </c>
@@ -4455,7 +5049,7 @@
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:5">
       <c r="A274" s="4">
         <v>46264</v>
       </c>
@@ -4468,7 +5062,7 @@
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:5">
       <c r="A275" s="4">
         <v>46265</v>
       </c>
@@ -4481,7 +5075,7 @@
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:5">
       <c r="A276" s="4">
         <v>46266</v>
       </c>
@@ -4494,7 +5088,7 @@
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:5">
       <c r="A277" s="4">
         <v>46267</v>
       </c>
@@ -4507,7 +5101,7 @@
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:5">
       <c r="A278" s="4">
         <v>46268</v>
       </c>
@@ -4520,7 +5114,7 @@
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:5">
       <c r="A279" s="4">
         <v>46269</v>
       </c>
@@ -4533,7 +5127,7 @@
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:5">
       <c r="A280" s="4">
         <v>46270</v>
       </c>
@@ -4546,7 +5140,7 @@
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:5">
       <c r="A281" s="4">
         <v>46271</v>
       </c>
@@ -4559,7 +5153,7 @@
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:5">
       <c r="A282" s="4">
         <v>46272</v>
       </c>
@@ -4572,7 +5166,7 @@
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:5">
       <c r="A283" s="4">
         <v>46273</v>
       </c>
@@ -4585,7 +5179,7 @@
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:5">
       <c r="A284" s="4">
         <v>46274</v>
       </c>
@@ -4598,7 +5192,7 @@
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:5">
       <c r="A285" s="4">
         <v>46275</v>
       </c>
@@ -4611,7 +5205,7 @@
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:5">
       <c r="A286" s="4">
         <v>46276</v>
       </c>
@@ -4624,7 +5218,7 @@
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:5">
       <c r="A287" s="4">
         <v>46277</v>
       </c>
@@ -4637,7 +5231,7 @@
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:5">
       <c r="A288" s="4">
         <v>46278</v>
       </c>
@@ -4650,7 +5244,7 @@
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:5">
       <c r="A289" s="4">
         <v>46279</v>
       </c>
@@ -4663,7 +5257,7 @@
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:3">
       <c r="A290" s="1">
         <v>46280</v>
       </c>
@@ -4674,7 +5268,7 @@
         <v>330750</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:3">
       <c r="A291" s="1">
         <v>46281</v>
       </c>
@@ -4685,7 +5279,7 @@
         <v>271350</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:3">
       <c r="A292" s="1">
         <v>46282</v>
       </c>
@@ -4696,7 +5290,7 @@
         <v>248850</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:3">
       <c r="A293" s="1">
         <v>46283</v>
       </c>
@@ -4707,7 +5301,7 @@
         <v>250200</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:3">
       <c r="A294" s="1">
         <v>46284</v>
       </c>
@@ -4718,7 +5312,7 @@
         <v>268650</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:3">
       <c r="A295" s="1">
         <v>46285</v>
       </c>
@@ -4729,7 +5323,7 @@
         <v>458100</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:3">
       <c r="A296" s="1">
         <v>46286</v>
       </c>
@@ -4740,7 +5334,7 @@
         <v>271800</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:3">
       <c r="A297" s="1">
         <v>46287</v>
       </c>
@@ -4751,7 +5345,7 @@
         <v>190800</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:3">
       <c r="A298" s="1">
         <v>46288</v>
       </c>
@@ -4762,7 +5356,7 @@
         <v>239400</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:3">
       <c r="A299" s="1">
         <v>46289</v>
       </c>
@@ -4773,7 +5367,7 @@
         <v>215550</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:3">
       <c r="A300" s="1">
         <v>46290</v>
       </c>
@@ -4784,7 +5378,7 @@
         <v>295650</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:3">
       <c r="A301" s="1">
         <v>46291</v>
       </c>
@@ -4795,7 +5389,7 @@
         <v>262800</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:3">
       <c r="A302" s="1">
         <v>46292</v>
       </c>
@@ -4806,7 +5400,7 @@
         <v>324450</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:3">
       <c r="A303" s="1">
         <v>46293</v>
       </c>
@@ -4817,7 +5411,7 @@
         <v>227250</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:3">
       <c r="A304" s="1">
         <v>46294</v>
       </c>
@@ -4828,7 +5422,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:3">
       <c r="A305" s="1">
         <v>46295</v>
       </c>
@@ -4839,21 +5433,27 @@
         <v>241650</v>
       </c>
     </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B306" t="s">
+        <v>39</v>
+      </c>
+      <c r="C306">
+        <v>190350</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E305" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="5"/>
+  <autoFilter ref="A1:E305">
+    <extLst/>
+  </autoFilter>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B289">
+      <formula1>店舗マスタ!$A$2:$A$31</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B289</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$306</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,25 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,21 +236,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,21 +265,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,17 +303,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,46 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +452,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,43 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,37 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -581,16 +596,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,24 +627,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,28 +645,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5444,8 +5444,19 @@
         <v>190350</v>
       </c>
     </row>
+    <row r="307" spans="1:3">
+      <c r="A307" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B307" t="s">
+        <v>39</v>
+      </c>
+      <c r="C307">
+        <v>132750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E305">
+  <autoFilter ref="A1:E306">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$307</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -203,9 +203,92 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,31 +302,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,6 +326,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -272,78 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +452,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,133 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,71 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -662,9 +597,74 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5455,8 +5455,19 @@
         <v>132750</v>
       </c>
     </row>
+    <row r="308" spans="1:3">
+      <c r="A308" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B308" t="s">
+        <v>39</v>
+      </c>
+      <c r="C308">
+        <v>126450</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E306">
+  <autoFilter ref="A1:E307">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$308</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,9 +204,100 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,17 +310,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,77 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,21 +344,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,6 +470,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -404,73 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,37 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,32 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,17 +625,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +649,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5466,8 +5466,19 @@
         <v>126450</v>
       </c>
     </row>
+    <row r="309" spans="1:3">
+      <c r="A309" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B309" t="s">
+        <v>39</v>
+      </c>
+      <c r="C309">
+        <v>123750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E307">
+  <autoFilter ref="A1:E308">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$309</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,25 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,7 +229,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,38 +250,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,21 +280,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,9 +326,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -314,29 +337,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -368,25 +368,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +428,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,9 +597,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,19 +624,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,7 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5477,8 +5477,19 @@
         <v>123750</v>
       </c>
     </row>
+    <row r="310" spans="1:3">
+      <c r="A310" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B310" t="s">
+        <v>39</v>
+      </c>
+      <c r="C310">
+        <v>136350</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E308">
+  <autoFilter ref="A1:E309">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$310</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,121 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -219,121 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +398,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,10 +599,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -630,6 +630,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -649,22 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5488,8 +5488,19 @@
         <v>136350</v>
       </c>
     </row>
+    <row r="311" spans="1:3">
+      <c r="A311" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B311" t="s">
+        <v>39</v>
+      </c>
+      <c r="C311">
+        <v>114750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E309">
+  <autoFilter ref="A1:E310">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$311</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,17 +226,31 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,23 +262,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,7 +294,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,15 +317,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,7 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,109 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,12 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,15 +604,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -617,15 +615,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,6 +651,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,49 +692,49 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,89 +743,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5499,8 +5499,19 @@
         <v>114750</v>
       </c>
     </row>
+    <row r="312" spans="1:3">
+      <c r="A312" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B312" t="s">
+        <v>39</v>
+      </c>
+      <c r="C312">
+        <v>211950</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E310">
+  <autoFilter ref="A1:E311">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$312</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -226,21 +218,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,9 +270,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,9 +279,33 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -280,7 +319,15 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,54 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +434,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,43 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,15 +580,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -600,6 +591,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +625,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -634,28 +651,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E312"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5510,8 +5510,19 @@
         <v>211950</v>
       </c>
     </row>
+    <row r="313" spans="1:3">
+      <c r="A313" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B313" t="s">
+        <v>39</v>
+      </c>
+      <c r="C313">
+        <v>117900</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E311">
+  <autoFilter ref="A1:E312">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$313</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,15 +203,53 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,8 +262,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,14 +285,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -254,9 +300,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,13 +323,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -285,19 +331,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -306,44 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,103 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,21 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,21 +627,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -668,151 +644,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5521,8 +5521,19 @@
         <v>117900</v>
       </c>
     </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B314" t="s">
+        <v>39</v>
+      </c>
+      <c r="C314">
+        <v>157950</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E312">
+  <autoFilter ref="A1:E313">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$314</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -205,17 +205,39 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -227,7 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,42 +270,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -285,21 +278,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -315,32 +294,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +434,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,37 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,80 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,151 +594,225 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E314"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5532,8 +5532,19 @@
         <v>157950</v>
       </c>
     </row>
+    <row r="315" spans="1:3">
+      <c r="A315" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B315" t="s">
+        <v>39</v>
+      </c>
+      <c r="C315">
+        <v>118800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E313">
+  <autoFilter ref="A1:E314">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$315</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,17 +204,32 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,37 +241,16 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,40 +264,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,6 +286,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -333,17 +303,47 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,37 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +380,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,43 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -610,11 +595,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,34 +639,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5543,8 +5543,19 @@
         <v>118800</v>
       </c>
     </row>
+    <row r="316" spans="1:3">
+      <c r="A316" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B316" t="s">
+        <v>39</v>
+      </c>
+      <c r="C316">
+        <v>76500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E314">
+  <autoFilter ref="A1:E315">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$315</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$316</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,18 +203,25 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,24 +232,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,46 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,8 +271,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,11 +317,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,6 +334,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,21 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -639,8 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E317"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5554,8 +5554,19 @@
         <v>76500</v>
       </c>
     </row>
+    <row r="317" spans="1:3">
+      <c r="A317" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B317" t="s">
+        <v>39</v>
+      </c>
+      <c r="C317">
+        <v>121050</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E315">
+  <autoFilter ref="A1:E316">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$317</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,6 +219,43 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -233,7 +263,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,6 +285,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -255,19 +301,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -276,59 +313,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +328,22 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,133 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -597,11 +617,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,11 +639,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E317"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5565,8 +5565,19 @@
         <v>121050</v>
       </c>
     </row>
+    <row r="318" spans="1:3">
+      <c r="A318" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B318" t="s">
+        <v>39</v>
+      </c>
+      <c r="C318">
+        <v>121050</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E316">
+  <autoFilter ref="A1:E317">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$317</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$318</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,9 +204,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,21 +234,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,28 +256,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -277,6 +272,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -285,11 +295,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,7 +311,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,7 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,22 +344,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +404,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,73 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,15 +611,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,15 +630,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -635,6 +641,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,179 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5576,8 +5576,19 @@
         <v>121050</v>
       </c>
     </row>
+    <row r="319" spans="1:3">
+      <c r="A319" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B319" t="s">
+        <v>39</v>
+      </c>
+      <c r="C319">
+        <v>78750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E317">
+  <autoFilter ref="A1:E318">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$319</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,13 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -219,24 +212,45 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,14 +272,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -273,15 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,43 +301,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -342,6 +310,38 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +404,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,55 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,20 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,32 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,151 +639,180 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E320"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5587,8 +5587,19 @@
         <v>78750</v>
       </c>
     </row>
+    <row r="320" spans="1:3">
+      <c r="A320" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B320" t="s">
+        <v>39</v>
+      </c>
+      <c r="C320">
+        <v>147150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E318">
+  <autoFilter ref="A1:E319">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$320</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,6 +204,66 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,11 +271,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -227,7 +286,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,21 +317,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,36 +325,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,34 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,61 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,79 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +441,108 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +591,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,9 +645,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,54 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E320"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5598,8 +5598,19 @@
         <v>147150</v>
       </c>
     </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B321" t="s">
+        <v>39</v>
+      </c>
+      <c r="C321">
+        <v>216000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E319">
+  <autoFilter ref="A1:E320">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$321</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,33 +204,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -243,21 +220,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,21 +242,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,7 +258,67 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,23 +340,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,43 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,37 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +410,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,25 +464,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,6 +600,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -624,6 +641,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,177 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E322"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5609,8 +5609,19 @@
         <v>216000</v>
       </c>
     </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B322" t="s">
+        <v>39</v>
+      </c>
+      <c r="C322">
+        <v>83700</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E320">
+  <autoFilter ref="A1:E321">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$323</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,46 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,14 +257,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,14 +272,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,67 +288,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +317,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,25 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +434,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,61 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,10 +573,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -600,6 +598,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -616,16 +629,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5620,8 +5620,30 @@
         <v>83700</v>
       </c>
     </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B323" t="s">
+        <v>39</v>
+      </c>
+      <c r="C323">
+        <v>83700</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B324" t="s">
+        <v>39</v>
+      </c>
+      <c r="C324">
+        <v>177750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E321">
+  <autoFilter ref="A1:E323">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$324</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -218,10 +218,40 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -233,16 +263,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,8 +278,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,18 +331,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -321,29 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,25 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,6 +422,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -410,7 +446,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,79 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,11 +580,37 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,21 +639,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -643,27 +654,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E324"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5642,8 +5642,19 @@
         <v>177750</v>
       </c>
     </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B325" t="s">
+        <v>39</v>
+      </c>
+      <c r="C325">
+        <v>108000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E323">
+  <autoFilter ref="A1:E324">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$325</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,24 +204,40 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,14 +250,51 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,14 +310,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,69 +339,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +458,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -591,35 +624,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,21 +643,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,13 +657,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E325"/>
+  <dimension ref="A1:E326"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5653,8 +5653,19 @@
         <v>108000</v>
       </c>
     </row>
+    <row r="326" spans="1:3">
+      <c r="A326" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B326" t="s">
+        <v>39</v>
+      </c>
+      <c r="C326">
+        <v>95400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E324">
+  <autoFilter ref="A1:E325">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$326</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,23 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,26 +219,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,15 +235,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,22 +250,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,7 +265,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +310,40 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +452,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,9 +636,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,43 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E326"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5664,8 +5664,19 @@
         <v>95400</v>
       </c>
     </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B327" t="s">
+        <v>39</v>
+      </c>
+      <c r="C327">
+        <v>225000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E325">
+  <autoFilter ref="A1:E326">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$327</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -205,7 +205,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,30 +281,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -266,20 +296,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,6 +309,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -301,47 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,25 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +452,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +488,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -586,15 +601,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -606,6 +612,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,48 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5675,8 +5675,19 @@
         <v>225000</v>
       </c>
     </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B328" t="s">
+        <v>39</v>
+      </c>
+      <c r="C328">
+        <v>175950</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E326">
+  <autoFilter ref="A1:E327">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$328</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,17 +203,32 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,9 +242,40 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,6 +288,28 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -257,91 +325,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +410,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,50 +634,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -668,151 +657,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E329"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5686,8 +5686,19 @@
         <v>175950</v>
       </c>
     </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B329" t="s">
+        <v>39</v>
+      </c>
+      <c r="C329">
+        <v>108000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E327">
+  <autoFilter ref="A1:E328">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$329</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,96 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,44 +308,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -272,78 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,43 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,85 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,50 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,15 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -658,6 +610,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -668,164 +635,197 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E329"/>
+  <dimension ref="A1:E330"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5697,8 +5697,19 @@
         <v>108000</v>
       </c>
     </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B330" t="s">
+        <v>39</v>
+      </c>
+      <c r="C330">
+        <v>80550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E328">
+  <autoFilter ref="A1:E329">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$331</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,120 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -219,81 +333,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -304,46 +344,6 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,17 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,17 +648,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E330"/>
+  <dimension ref="A1:E332"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5708,8 +5708,30 @@
         <v>80550</v>
       </c>
     </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B331" t="s">
+        <v>39</v>
+      </c>
+      <c r="C331">
+        <v>80550</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B332" t="s">
+        <v>39</v>
+      </c>
+      <c r="C332">
+        <v>188550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E329">
+  <autoFilter ref="A1:E331">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$332</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,32 +203,75 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,15 +285,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,85 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +416,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,8 +573,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -591,6 +593,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,32 +640,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -648,8 +648,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E332"/>
+  <dimension ref="A1:E333"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5730,8 +5730,19 @@
         <v>188550</v>
       </c>
     </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B333" t="s">
+        <v>39</v>
+      </c>
+      <c r="C333">
+        <v>185850</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E331">
+  <autoFilter ref="A1:E332">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$333</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,45 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,22 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,8 +278,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,10 +325,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,52 +344,6 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,25 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,31 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -600,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,6 +610,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -632,24 +650,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E333"/>
+  <dimension ref="A1:E334"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5741,8 +5741,19 @@
         <v>185850</v>
       </c>
     </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B334" t="s">
+        <v>39</v>
+      </c>
+      <c r="C334">
+        <v>145800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E332">
+  <autoFilter ref="A1:E333">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$334</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,39 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,41 +248,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,7 +264,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,9 +278,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,29 +294,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,8 +309,32 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +476,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -582,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,29 +612,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +649,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E334"/>
+  <dimension ref="A1:E335"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5752,8 +5752,19 @@
         <v>145800</v>
       </c>
     </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B335" t="s">
+        <v>39</v>
+      </c>
+      <c r="C335">
+        <v>85500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E333">
+  <autoFilter ref="A1:E334">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$335</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,10 +204,24 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,7 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,15 +248,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,7 +280,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,60 +289,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +303,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +458,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,22 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,6 +619,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -648,184 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E335"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5763,8 +5763,19 @@
         <v>85500</v>
       </c>
     </row>
+    <row r="336" spans="1:3">
+      <c r="A336" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B336" t="s">
+        <v>39</v>
+      </c>
+      <c r="C336">
+        <v>74250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E334">
+  <autoFilter ref="A1:E335">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$336</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -203,8 +203,38 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -225,32 +255,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,13 +277,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -279,8 +285,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,40 +302,17 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +328,22 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,85 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,15 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -619,27 +627,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -648,8 +639,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +659,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E337"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5774,8 +5774,19 @@
         <v>74250</v>
       </c>
     </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B337" t="s">
+        <v>39</v>
+      </c>
+      <c r="C337">
+        <v>158400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E335">
+  <autoFilter ref="A1:E336">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ストーリーセゾン.xlsx
+++ b/dashboard/data/incoming/ストーリーセゾン.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$336</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$337</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
@@ -203,16 +203,82 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,8 +292,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,60 +325,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +446,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,43 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,26 +573,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,18 +621,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +649,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E337"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -5785,8 +5785,19 @@
         <v>158400</v>
       </c>
     </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B338" t="s">
+        <v>39</v>
+      </c>
+      <c r="C338">
+        <v>108000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E336">
+  <autoFilter ref="A1:E337">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
